--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="353">
   <si>
     <t>Date</t>
   </si>
@@ -500,6 +500,9 @@
     <t>Expressobeans Poster Link</t>
   </si>
   <si>
+    <t>Stock Image</t>
+  </si>
+  <si>
     <t>Gary Baseman</t>
   </si>
   <si>
@@ -509,24 +512,36 @@
     <t>https://expressobeans.com/public/detail.php/123494</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1vLdapZu2Oj-jWqdahQWtxtTh6grXWBK6/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Gerald Scarfe</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/151915</t>
   </si>
   <si>
-    <t>Kii Arens</t>
+    <t>https://drive.google.com/file/d/1WHemrT9ldrXhN-D_Ddouo92zj4kF7swm/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Rob Sheridan, Russell Mills</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/179172</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/15JpqRB4rJhrhJrA67Kk8mu6RidC1UBRA/view?usp=drive_link</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arens, Kii, Plastic Jesus </t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/186961</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1xuLmHvGKSXCHMIoQ0Qei1UGtdZ5O_TEj/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Brad Klausen</t>
   </si>
   <si>
@@ -536,18 +551,27 @@
     <t>https://expressobeans.com/public/detail.php/194219</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1Cdr6HCwHruHIvXDnshMWKLxGb07QuRnk/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Ames Brothers</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/194934</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1_oSRhhUR8OqSshawfmYXLAim5Y6mrY2v/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Rob Jones</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/196278</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1ytGWzHsqf1bMSDgZQ6EdKPkTP7yUZK02/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Sket One</t>
   </si>
   <si>
@@ -560,6 +584,9 @@
     <t>https://expressobeans.com/public/detail.php/208452</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1fFctIb_RYxTDxFhpjmRfX3N5MCyJTUs0/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Todd Slater</t>
   </si>
   <si>
@@ -569,39 +596,60 @@
     <t>https://expressobeans.com/public/detail.php/211539</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1wSPyeKU5t347PxeDocOEEpUf2FiRU94R/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Jared Connor</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/212319</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1ruJQUS42sO_n4WtttnHkIg90wic236iH/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Pale Horse</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/218675</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1CqmCXx4HVZFyi98cYws081u3fTw5-ifw/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Adi Granov</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/222040</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1sHsEgQd5SEVy0ngM7jzkQzTXS2MqGhye/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Gregg Gordon</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/225691</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1Y-Rpnb-BhEi6cnj8J-uJogItdZFhIAUv/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/240144</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1PfmnWHFKHA7TM8jfN1qCFZu8CgT336J2/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Adam Jones</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/290999</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/10huhLiaF_EBaakEdrYtrVzj_yuwA0Dso/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Unknown</t>
   </si>
   <si>
@@ -617,12 +665,18 @@
     <t>https://expressobeans.com/public/detail.php/244301</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1AFKuZc-0h-a6uiglL4r-vTAZoB3GYe3q/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Angryblue (Justin Kamerer)</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/253928</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1MJPtKpbN45L5b8EpBhMFl-s3789-61Z4/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Emek</t>
   </si>
   <si>
@@ -632,30 +686,54 @@
     <t>https://expressobeans.com/public/detail.php/247251</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1tLUsltydRdYEiv3OVKAUo0bcdzsNMbC2/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kPWEuHbBVO5WY0bVVtJmgsYnXOdbMmnf/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/281506</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1PPm8DH6HuJc3qBh95sAEMEBWcD5kEjiw/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Ian Williams</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/265755</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1TZUjbOZ_7HrEDyJ_1v2nGCOYtYgN4dd_/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Jamie Koala</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/323469</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1ibuMP3F31TlkCcjDhlvYIBcrpgBf2keG/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ybLG2V639yGEIcgELiSucG-yuBQ-EdfP/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/274618</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1uJjbTBnu3vgkQgB_YDUOIfsLBwRsz9zl/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Erica Williams</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/273538</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1cn8nnnrlL9PkWDtAgC7uucUu3dTCOYaq/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Hatch Show Print</t>
   </si>
   <si>
@@ -665,18 +743,30 @@
     <t>https://expressobeans.com/public/detail.php/306265</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1GroJCI6_OBNmhVnTqDncCUxnzMuHwyuN/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Arian Buhler</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1ZcoDdTTyDQQRnSoGEHZSjDaQRhlPDjAr/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/280905</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/12moXxf74fYWjuf1YwoBGsqk01ZPicn0k/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Allen Williams</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/280401</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1UZFdLC1G8ylHU4sEAp9hDnHJs-4V3cPf/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Chet Zar</t>
   </si>
   <si>
@@ -686,183 +776,291 @@
     <t>https://expressobeans.com/public/detail.php/280931</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1v2LsCmM9fvl_W3gFnQR1q11_4Q3bVS32/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Dominic Hailstone</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/280944</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1h0-gV-COgeHT2trdlb5i_LeEzbob2Twj/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Landland</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/306381</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1hOUd3Ho8E8iMix8Dartijjph-2xK_2zv/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Robert Banach</t>
   </si>
   <si>
-    <t>Angryblue</t>
+    <t>https://drive.google.com/file/d/1kkLJ28wGH1QLr1Mhv0Fn_aqW_AsXts0z/view?usp=drive_link</t>
   </si>
   <si>
     <t>Official / TBD</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1ThrtMznodlRzPz4TmMpZWiu4VJMVVczV/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/302663</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/10aeSKg2MIn5nFuMERoEYVHpvs59nagtC/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Frank Frazetta</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/303923</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1fQ1sE7GsXJt5ygB_s_zhKMdHUN6ExaHQ/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Alex Grey</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/304419</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/14HljZ2q6ElxzwE4Hm0NAIpnVUBOyStET/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>John Crawford</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/319934</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1HxIRaudrAUcywZePbxbVi_S6D7Sxa521/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Michael Hacker</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/306690</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1htrKPNVj-S0rzMDKVHaDxXbavqFV7r-R/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Virgil Abloh / Official</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/307864</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1IaMV1J12N4wARQE3GhHl4F1JbjDClc2_/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Official / Zoran Bihac (Creative Dir)</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/309873</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1YKlNPfvCOIDbwIV2qWq627nBLtYyME6m/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/309569</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/13LX2SWcSuzT7_LA8EqPttebbhNVVIhU8/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11oBTGgWQYNDDksZWyi-0gVYj1MHQ7r-0/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Alex Kuno</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/314300</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/16fjtNAhMmh7uSzxS3s_SBquUFb2e_Gwm/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Squindo</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/316748</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1JS85U6pJgzgzHWbnnpEA1cZm1-EWHtki/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/316749</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/11rXvBpw_IEvRafv7j6rcaAGOQFMEhkUC/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Studio/Official</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/318464</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/16Fx-YdHD426RyHt8cDAkEsENznw1pTOl/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Travis Gillan</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/318753</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1fgrwQihWRHbUsj7phoWI3lnKoEc03CRQ/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Miles Johnston</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/323237</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1KEydOB85Nhf8o6zV5j2q3wE3-oaPRV2W/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Richard Biffle</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/317772</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1pgCttfdwE6PwjzaH6qunpp7G6zAaCCow/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Liz Passerieux</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/321059</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1B1ZRIn_c32uVblQk97RAft4zB-XkYcy6/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Sty8eQ06_Xbqos0F4MdU4W_i7NlC8ZEB/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Korin Faught</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/321675</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/14znodZhEdb_9jUMVy6sDkm86lnKXcQjH/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Zoltron</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/322555</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/17pqvG9lxO-l0Vdtn75W3BHycXa83q5wL/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Zeb Love</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/322934</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1Qkpq7hT7UIqar7whgNWj_qigUOHFoe-R/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Mark Dean Veca</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/322926</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/13KIgofdy7hwVwK_6fqCTQOGHMEyZQVXk/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Logan Schmitt</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1qJxf2GjitO6wOgkHzzwx-Q98aBYH4b7w/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Burrito Breath</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/324915</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1dQOUEbXdmdukUbg1XXcAN6VNQS4gdDTJ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kyyIotG2C77JYkdTB4Syp89Sz7uRr31q/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>DABSMYLA</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/331952</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1nhnWVdsZGFIYWxQGq15GNVykvmGD7HzK/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Don Pendleton</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/332084</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1gg5tC0lsj8zRQwzL5Q0-B5KJBMIjwmAC/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Miles Tsang</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/332464</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1THs_y6kRcVTGqyDzchULz_i9ZYh4FPgH/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>NC Winters</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/332529</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/17obLPftp_3RHHG5aOhpIzfHetQ0UWplM/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1awJQBEATeuaBSgz4H96upvKVQruDakRX/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Peel it back</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/334688</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1Y4fr0EWZpdKN7RAhC7iOQt28ajYHQ6Hs/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Boop a Doop</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/339059</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1EnNoXeBEvJKLqF6oI9aqfkhm0VS9z5d7/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>AVVT/PTTN</t>
   </si>
   <si>
@@ -873,6 +1071,9 @@
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/339352</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1t0V2HQrDpkYGYF8XyljYkxtAdmIzeFDj/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -4090,6 +4291,9 @@
       <c r="O1" s="1" t="s">
         <v>160</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7">
@@ -4099,7 +4303,7 @@
         <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>123</v>
@@ -4108,7 +4312,7 @@
         <v>81</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>143</v>
@@ -4132,7 +4336,10 @@
         <v>10</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -4143,7 +4350,7 @@
         <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>106</v>
@@ -4174,7 +4381,10 @@
         <v>10</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="4">
@@ -4185,7 +4395,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
@@ -4216,7 +4426,10 @@
         <v>10</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="5">
@@ -4227,7 +4440,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
@@ -4258,7 +4471,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="6">
@@ -4269,7 +4485,7 @@
         <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>100</v>
@@ -4294,7 +4510,7 @@
         <v>19</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>104</v>
@@ -4303,7 +4519,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="7">
@@ -4314,7 +4533,7 @@
         <v>136</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>137</v>
@@ -4345,7 +4564,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="8">
@@ -4356,7 +4578,7 @@
         <v>112</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>106</v>
@@ -4387,7 +4609,10 @@
         <v>10</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="9">
@@ -4398,7 +4623,7 @@
         <v>140</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>106</v>
@@ -4407,7 +4632,7 @@
         <v>81</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>141</v>
@@ -4425,7 +4650,7 @@
         <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>104</v>
@@ -4434,7 +4659,10 @@
         <v>10</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -4445,7 +4673,7 @@
         <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>106</v>
@@ -4454,7 +4682,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>114</v>
@@ -4478,7 +4706,10 @@
         <v>10</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -4489,7 +4720,7 @@
         <v>140</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
@@ -4520,7 +4751,10 @@
         <v>10</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -4531,7 +4765,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>38</v>
@@ -4565,7 +4799,10 @@
         <v>10</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -4576,7 +4813,7 @@
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>38</v>
@@ -4607,7 +4844,10 @@
         <v>10</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>189</v>
+        <v>201</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="14">
@@ -4618,7 +4858,7 @@
         <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>14</v>
@@ -4649,7 +4889,10 @@
         <v>10</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>191</v>
+        <v>204</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -4660,7 +4903,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>106</v>
@@ -4691,7 +4934,10 @@
         <v>10</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>192</v>
+        <v>206</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="16">
@@ -4702,7 +4948,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>64</v>
@@ -4736,7 +4982,10 @@
         <v>10</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="17">
@@ -4747,7 +4996,7 @@
         <v>54</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>64</v>
@@ -4757,7 +5006,7 @@
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>17</v>
@@ -4772,11 +5021,14 @@
         <v>19</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="N17" s="10"/>
       <c r="O17" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="18">
@@ -4784,10 +5036,10 @@
         <v>42958.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>72</v>
@@ -4821,7 +5073,10 @@
         <v>10</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>199</v>
+        <v>215</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="19">
@@ -4832,7 +5087,7 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>106</v>
@@ -4863,7 +5118,10 @@
         <v>10</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>201</v>
+        <v>218</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="20">
@@ -4874,10 +5132,10 @@
         <v>80</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>35</v>
@@ -4905,7 +5163,10 @@
         <v>10</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>204</v>
+        <v>222</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="21">
@@ -4916,7 +5177,7 @@
         <v>132</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>32</v>
@@ -4946,6 +5207,9 @@
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="P21" s="8" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7">
@@ -4955,7 +5219,7 @@
         <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>32</v>
@@ -4986,7 +5250,10 @@
         <v>10</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>205</v>
+        <v>225</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="23">
@@ -4997,7 +5264,7 @@
         <v>91</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>106</v>
@@ -5028,7 +5295,10 @@
         <v>10</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>207</v>
+        <v>228</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="24">
@@ -5039,7 +5309,7 @@
         <v>118</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>38</v>
@@ -5073,7 +5343,10 @@
         <v>10</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>209</v>
+        <v>231</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="25">
@@ -5111,6 +5384,9 @@
       <c r="N25" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="P25" s="8" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7">
@@ -5120,7 +5396,7 @@
         <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>14</v>
@@ -5151,7 +5427,10 @@
         <v>10</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>210</v>
+        <v>234</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="27">
@@ -5162,7 +5441,7 @@
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>14</v>
@@ -5193,7 +5472,10 @@
         <v>10</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>212</v>
+        <v>237</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="28">
@@ -5204,7 +5486,7 @@
         <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>14</v>
@@ -5243,7 +5525,7 @@
         <v>133</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>134</v>
@@ -5274,7 +5556,10 @@
         <v>10</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>215</v>
+        <v>241</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="30">
@@ -5282,10 +5567,10 @@
         <v>43733.0</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>38</v>
@@ -5318,6 +5603,9 @@
       <c r="N30" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="P30" s="8" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7">
@@ -5327,7 +5615,7 @@
         <v>54</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>123</v>
@@ -5361,7 +5649,10 @@
         <v>10</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>217</v>
+        <v>245</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="32">
@@ -5372,7 +5663,7 @@
         <v>54</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>14</v>
@@ -5406,7 +5697,10 @@
         <v>10</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>219</v>
+        <v>248</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="33">
@@ -5417,7 +5711,7 @@
         <v>54</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>126</v>
@@ -5442,7 +5736,7 @@
         <v>18</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>104</v>
@@ -5451,7 +5745,10 @@
         <v>10</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="34">
@@ -5462,7 +5759,7 @@
         <v>54</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>29</v>
@@ -5493,7 +5790,10 @@
         <v>10</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>224</v>
+        <v>255</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="35">
@@ -5504,7 +5804,7 @@
         <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>88</v>
@@ -5546,7 +5846,7 @@
         <v>62</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>14</v>
@@ -5577,7 +5877,10 @@
         <v>10</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>226</v>
+        <v>258</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="37">
@@ -5585,10 +5888,10 @@
         <v>44468.0</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>14</v>
@@ -5618,6 +5921,9 @@
       <c r="N37" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="P37" s="3" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7">
@@ -5627,7 +5933,7 @@
         <v>51</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>52</v>
@@ -5658,6 +5964,9 @@
       </c>
       <c r="N38" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="39">
@@ -5668,7 +5977,7 @@
         <v>84</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>14</v>
@@ -5699,7 +6008,10 @@
         <v>10</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>230</v>
+        <v>264</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="40">
@@ -5710,7 +6022,7 @@
         <v>54</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>128</v>
@@ -5744,7 +6056,10 @@
         <v>10</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>232</v>
+        <v>267</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="41">
@@ -5755,7 +6070,7 @@
         <v>54</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>131</v>
@@ -5786,7 +6101,10 @@
         <v>10</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>234</v>
+        <v>270</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="42">
@@ -5797,7 +6115,7 @@
         <v>58</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>14</v>
@@ -5828,7 +6146,10 @@
         <v>10</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>236</v>
+        <v>273</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="43">
@@ -5839,7 +6160,7 @@
         <v>58</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>14</v>
@@ -5870,7 +6191,10 @@
         <v>10</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>236</v>
+        <v>273</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="44">
@@ -5881,7 +6205,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>43</v>
@@ -5914,7 +6238,10 @@
         <v>10</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>238</v>
+        <v>276</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="45">
@@ -5925,7 +6252,7 @@
         <v>76</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>14</v>
@@ -5956,7 +6283,10 @@
         <v>10</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>240</v>
+        <v>279</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="46">
@@ -5967,7 +6297,7 @@
         <v>92</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>93</v>
@@ -5998,7 +6328,10 @@
         <v>10</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>242</v>
+        <v>282</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="47">
@@ -6009,7 +6342,7 @@
         <v>41</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>38</v>
@@ -6040,7 +6373,10 @@
         <v>10</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>243</v>
+        <v>284</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="48">
@@ -6051,7 +6387,7 @@
         <v>51</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>52</v>
@@ -6082,6 +6418,9 @@
       </c>
       <c r="N48" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="P48" s="8" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="49">
@@ -6092,7 +6431,7 @@
         <v>54</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>52</v>
@@ -6123,7 +6462,10 @@
         <v>10</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>245</v>
+        <v>288</v>
+      </c>
+      <c r="P49" s="8" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="50">
@@ -6134,7 +6476,7 @@
         <v>37</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>46</v>
@@ -6168,7 +6510,10 @@
         <v>10</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
+      </c>
+      <c r="P50" s="8" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="51">
@@ -6179,7 +6524,7 @@
         <v>37</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>46</v>
@@ -6213,7 +6558,10 @@
         <v>10</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>248</v>
+        <v>293</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="52">
@@ -6224,7 +6572,7 @@
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>29</v>
@@ -6256,7 +6604,10 @@
         <v>10</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>250</v>
+        <v>296</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="53">
@@ -6267,7 +6618,7 @@
         <v>13</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>14</v>
@@ -6300,7 +6651,10 @@
         <v>10</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>252</v>
+        <v>299</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="54">
@@ -6311,7 +6665,7 @@
         <v>13</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>14</v>
@@ -6342,7 +6696,10 @@
         <v>10</v>
       </c>
       <c r="O54" s="8" t="s">
-        <v>254</v>
+        <v>302</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="55">
@@ -6353,7 +6710,7 @@
         <v>42</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>14</v>
@@ -6384,7 +6741,10 @@
         <v>10</v>
       </c>
       <c r="O55" s="8" t="s">
-        <v>256</v>
+        <v>305</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="56">
@@ -6395,7 +6755,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>38</v>
@@ -6426,7 +6786,10 @@
         <v>10</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>258</v>
+        <v>308</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="57">
@@ -6437,7 +6800,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>38</v>
@@ -6468,7 +6831,10 @@
         <v>10</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>258</v>
+        <v>308</v>
+      </c>
+      <c r="P57" s="8" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="58">
@@ -6479,7 +6845,7 @@
         <v>54</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>29</v>
@@ -6506,7 +6872,10 @@
         <v>104</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>260</v>
+        <v>312</v>
+      </c>
+      <c r="P58" s="8" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="59">
@@ -6517,7 +6886,7 @@
         <v>36</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>14</v>
@@ -6548,7 +6917,10 @@
         <v>10</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>262</v>
+        <v>315</v>
+      </c>
+      <c r="P59" s="8" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="60">
@@ -6559,7 +6931,7 @@
         <v>41</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>14</v>
@@ -6593,7 +6965,10 @@
         <v>10</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>264</v>
+        <v>318</v>
+      </c>
+      <c r="P60" s="8" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="61">
@@ -6604,7 +6979,7 @@
         <v>36</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>14</v>
@@ -6634,7 +7009,10 @@
         <v>104</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>266</v>
+        <v>321</v>
+      </c>
+      <c r="P61" s="8" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="62">
@@ -6645,7 +7023,7 @@
         <v>31</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>32</v>
@@ -6676,6 +7054,9 @@
       </c>
       <c r="N62" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="P62" s="8" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="63">
@@ -6686,7 +7067,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>14</v>
@@ -6719,7 +7100,10 @@
         <v>10</v>
       </c>
       <c r="O63" s="8" t="s">
-        <v>269</v>
+        <v>326</v>
+      </c>
+      <c r="P63" s="8" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="64">
@@ -6730,7 +7114,7 @@
         <v>24</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>14</v>
@@ -6740,7 +7124,7 @@
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>17</v>
@@ -6761,7 +7145,10 @@
         <v>10</v>
       </c>
       <c r="O64" s="8" t="s">
-        <v>269</v>
+        <v>326</v>
+      </c>
+      <c r="P64" s="8" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="65">
@@ -6772,7 +7159,7 @@
         <v>98</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>14</v>
@@ -6802,7 +7189,10 @@
         <v>10</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>271</v>
+        <v>330</v>
+      </c>
+      <c r="P65" s="8" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="66">
@@ -6813,7 +7203,7 @@
         <v>91</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>14</v>
@@ -6844,7 +7234,10 @@
         <v>10</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>273</v>
+        <v>333</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="67">
@@ -6855,7 +7248,7 @@
         <v>37</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>38</v>
@@ -6889,7 +7282,10 @@
         <v>10</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>275</v>
+        <v>336</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="68">
@@ -6900,7 +7296,7 @@
         <v>37</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>276</v>
+        <v>338</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>38</v>
@@ -6931,7 +7327,10 @@
         <v>10</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>277</v>
+        <v>339</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="69">
@@ -6942,7 +7341,7 @@
         <v>94</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>46</v>
@@ -6972,6 +7371,9 @@
       <c r="N69" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="P69" s="3" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7">
@@ -6981,7 +7383,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>14</v>
@@ -6990,7 +7392,7 @@
         <v>35</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>16</v>
@@ -7017,7 +7419,10 @@
         <v>10</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>279</v>
+        <v>343</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="71">
@@ -7028,7 +7433,7 @@
         <v>41</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>43</v>
@@ -7064,7 +7469,10 @@
         <v>10</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>281</v>
+        <v>346</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="72">
@@ -7072,10 +7480,10 @@
         <v>46129.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>282</v>
+        <v>348</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>88</v>
@@ -7085,7 +7493,7 @@
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>17</v>
@@ -7106,7 +7514,10 @@
         <v>10</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>285</v>
+        <v>351</v>
+      </c>
+      <c r="P72" s="8" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="73">
@@ -9916,134 +10327,203 @@
   <hyperlinks>
     <hyperlink r:id="rId1" ref="N2"/>
     <hyperlink r:id="rId2" ref="O2"/>
-    <hyperlink r:id="rId3" ref="N3"/>
-    <hyperlink r:id="rId4" ref="O3"/>
-    <hyperlink r:id="rId5" ref="N4"/>
-    <hyperlink r:id="rId6" ref="O4"/>
-    <hyperlink r:id="rId7" ref="N5"/>
-    <hyperlink r:id="rId8" ref="O5"/>
-    <hyperlink r:id="rId9" ref="N6"/>
-    <hyperlink r:id="rId10" ref="O6"/>
-    <hyperlink r:id="rId11" ref="N7"/>
-    <hyperlink r:id="rId12" ref="O7"/>
-    <hyperlink r:id="rId13" ref="N8"/>
-    <hyperlink r:id="rId14" ref="O8"/>
-    <hyperlink r:id="rId15" ref="N9"/>
-    <hyperlink r:id="rId16" ref="O9"/>
-    <hyperlink r:id="rId17" ref="N10"/>
-    <hyperlink r:id="rId18" ref="O10"/>
-    <hyperlink r:id="rId19" ref="N11"/>
-    <hyperlink r:id="rId20" ref="O11"/>
-    <hyperlink r:id="rId21" ref="N12"/>
-    <hyperlink r:id="rId22" ref="O12"/>
-    <hyperlink r:id="rId23" ref="N13"/>
-    <hyperlink r:id="rId24" ref="O13"/>
-    <hyperlink r:id="rId25" ref="N14"/>
-    <hyperlink r:id="rId26" ref="O14"/>
-    <hyperlink r:id="rId27" ref="N15"/>
-    <hyperlink r:id="rId28" ref="O15"/>
-    <hyperlink r:id="rId29" ref="N16"/>
-    <hyperlink r:id="rId30" ref="O16"/>
-    <hyperlink r:id="rId31" ref="O17"/>
-    <hyperlink r:id="rId32" ref="N18"/>
-    <hyperlink r:id="rId33" ref="O18"/>
-    <hyperlink r:id="rId34" ref="N19"/>
-    <hyperlink r:id="rId35" ref="O19"/>
-    <hyperlink r:id="rId36" ref="N20"/>
-    <hyperlink r:id="rId37" ref="O20"/>
-    <hyperlink r:id="rId38" ref="N21"/>
-    <hyperlink r:id="rId39" ref="N22"/>
-    <hyperlink r:id="rId40" ref="O22"/>
-    <hyperlink r:id="rId41" ref="N23"/>
-    <hyperlink r:id="rId42" ref="O23"/>
-    <hyperlink r:id="rId43" ref="N24"/>
-    <hyperlink r:id="rId44" ref="O24"/>
-    <hyperlink r:id="rId45" ref="N25"/>
-    <hyperlink r:id="rId46" ref="N26"/>
-    <hyperlink r:id="rId47" ref="O26"/>
-    <hyperlink r:id="rId48" ref="N27"/>
-    <hyperlink r:id="rId49" ref="O27"/>
-    <hyperlink r:id="rId50" ref="N28"/>
-    <hyperlink r:id="rId51" ref="N29"/>
-    <hyperlink r:id="rId52" ref="O29"/>
-    <hyperlink r:id="rId53" ref="N30"/>
-    <hyperlink r:id="rId54" ref="N31"/>
-    <hyperlink r:id="rId55" ref="O31"/>
-    <hyperlink r:id="rId56" ref="N32"/>
-    <hyperlink r:id="rId57" ref="O32"/>
-    <hyperlink r:id="rId58" ref="N33"/>
-    <hyperlink r:id="rId59" ref="O33"/>
-    <hyperlink r:id="rId60" ref="N34"/>
-    <hyperlink r:id="rId61" ref="O34"/>
-    <hyperlink r:id="rId62" ref="N35"/>
-    <hyperlink r:id="rId63" ref="N36"/>
-    <hyperlink r:id="rId64" ref="O36"/>
-    <hyperlink r:id="rId65" ref="N37"/>
-    <hyperlink r:id="rId66" ref="N38"/>
-    <hyperlink r:id="rId67" ref="N39"/>
-    <hyperlink r:id="rId68" ref="O39"/>
-    <hyperlink r:id="rId69" ref="N40"/>
-    <hyperlink r:id="rId70" ref="O40"/>
-    <hyperlink r:id="rId71" ref="N41"/>
-    <hyperlink r:id="rId72" ref="O41"/>
-    <hyperlink r:id="rId73" ref="N42"/>
-    <hyperlink r:id="rId74" ref="O42"/>
-    <hyperlink r:id="rId75" ref="N43"/>
-    <hyperlink r:id="rId76" ref="O43"/>
-    <hyperlink r:id="rId77" ref="N44"/>
-    <hyperlink r:id="rId78" ref="O44"/>
-    <hyperlink r:id="rId79" ref="N45"/>
-    <hyperlink r:id="rId80" ref="O45"/>
-    <hyperlink r:id="rId81" ref="N46"/>
-    <hyperlink r:id="rId82" ref="O46"/>
-    <hyperlink r:id="rId83" ref="N47"/>
-    <hyperlink r:id="rId84" ref="O47"/>
-    <hyperlink r:id="rId85" ref="N48"/>
-    <hyperlink r:id="rId86" ref="N49"/>
-    <hyperlink r:id="rId87" ref="O49"/>
-    <hyperlink r:id="rId88" ref="N50"/>
-    <hyperlink r:id="rId89" ref="O50"/>
-    <hyperlink r:id="rId90" ref="N51"/>
-    <hyperlink r:id="rId91" ref="O51"/>
-    <hyperlink r:id="rId92" ref="N52"/>
-    <hyperlink r:id="rId93" ref="O52"/>
-    <hyperlink r:id="rId94" ref="N53"/>
-    <hyperlink r:id="rId95" ref="O53"/>
-    <hyperlink r:id="rId96" ref="N54"/>
-    <hyperlink r:id="rId97" ref="O54"/>
-    <hyperlink r:id="rId98" ref="N55"/>
-    <hyperlink r:id="rId99" ref="O55"/>
-    <hyperlink r:id="rId100" ref="N56"/>
-    <hyperlink r:id="rId101" ref="O56"/>
-    <hyperlink r:id="rId102" ref="N57"/>
-    <hyperlink r:id="rId103" ref="O57"/>
-    <hyperlink r:id="rId104" ref="O58"/>
-    <hyperlink r:id="rId105" ref="N59"/>
-    <hyperlink r:id="rId106" ref="O59"/>
-    <hyperlink r:id="rId107" ref="N60"/>
-    <hyperlink r:id="rId108" ref="O60"/>
-    <hyperlink r:id="rId109" ref="O61"/>
-    <hyperlink r:id="rId110" ref="N62"/>
-    <hyperlink r:id="rId111" ref="N63"/>
-    <hyperlink r:id="rId112" ref="O63"/>
-    <hyperlink r:id="rId113" ref="N64"/>
-    <hyperlink r:id="rId114" ref="O64"/>
-    <hyperlink r:id="rId115" ref="N65"/>
-    <hyperlink r:id="rId116" ref="O65"/>
-    <hyperlink r:id="rId117" ref="N66"/>
-    <hyperlink r:id="rId118" ref="O66"/>
-    <hyperlink r:id="rId119" ref="N67"/>
-    <hyperlink r:id="rId120" ref="O67"/>
-    <hyperlink r:id="rId121" ref="N68"/>
-    <hyperlink r:id="rId122" ref="O68"/>
-    <hyperlink r:id="rId123" ref="N69"/>
-    <hyperlink r:id="rId124" ref="N70"/>
-    <hyperlink r:id="rId125" ref="O70"/>
-    <hyperlink r:id="rId126" ref="N71"/>
-    <hyperlink r:id="rId127" ref="O71"/>
-    <hyperlink r:id="rId128" ref="N72"/>
-    <hyperlink r:id="rId129" ref="O72"/>
+    <hyperlink r:id="rId3" ref="P2"/>
+    <hyperlink r:id="rId4" ref="N3"/>
+    <hyperlink r:id="rId5" ref="O3"/>
+    <hyperlink r:id="rId6" ref="P3"/>
+    <hyperlink r:id="rId7" ref="N4"/>
+    <hyperlink r:id="rId8" ref="O4"/>
+    <hyperlink r:id="rId9" ref="P4"/>
+    <hyperlink r:id="rId10" ref="N5"/>
+    <hyperlink r:id="rId11" ref="O5"/>
+    <hyperlink r:id="rId12" ref="P5"/>
+    <hyperlink r:id="rId13" ref="N6"/>
+    <hyperlink r:id="rId14" ref="O6"/>
+    <hyperlink r:id="rId15" ref="P6"/>
+    <hyperlink r:id="rId16" ref="N7"/>
+    <hyperlink r:id="rId17" ref="O7"/>
+    <hyperlink r:id="rId18" ref="P7"/>
+    <hyperlink r:id="rId19" ref="N8"/>
+    <hyperlink r:id="rId20" ref="O8"/>
+    <hyperlink r:id="rId21" ref="P8"/>
+    <hyperlink r:id="rId22" ref="N9"/>
+    <hyperlink r:id="rId23" ref="O9"/>
+    <hyperlink r:id="rId24" ref="P9"/>
+    <hyperlink r:id="rId25" ref="N10"/>
+    <hyperlink r:id="rId26" ref="O10"/>
+    <hyperlink r:id="rId27" ref="P10"/>
+    <hyperlink r:id="rId28" ref="N11"/>
+    <hyperlink r:id="rId29" ref="O11"/>
+    <hyperlink r:id="rId30" ref="P11"/>
+    <hyperlink r:id="rId31" ref="N12"/>
+    <hyperlink r:id="rId32" ref="O12"/>
+    <hyperlink r:id="rId33" ref="P12"/>
+    <hyperlink r:id="rId34" ref="N13"/>
+    <hyperlink r:id="rId35" ref="O13"/>
+    <hyperlink r:id="rId36" ref="P13"/>
+    <hyperlink r:id="rId37" ref="N14"/>
+    <hyperlink r:id="rId38" ref="O14"/>
+    <hyperlink r:id="rId39" ref="P14"/>
+    <hyperlink r:id="rId40" ref="N15"/>
+    <hyperlink r:id="rId41" ref="O15"/>
+    <hyperlink r:id="rId42" ref="P15"/>
+    <hyperlink r:id="rId43" ref="N16"/>
+    <hyperlink r:id="rId44" ref="O16"/>
+    <hyperlink r:id="rId45" ref="P16"/>
+    <hyperlink r:id="rId46" ref="O17"/>
+    <hyperlink r:id="rId47" ref="P17"/>
+    <hyperlink r:id="rId48" ref="N18"/>
+    <hyperlink r:id="rId49" ref="O18"/>
+    <hyperlink r:id="rId50" ref="P18"/>
+    <hyperlink r:id="rId51" ref="N19"/>
+    <hyperlink r:id="rId52" ref="O19"/>
+    <hyperlink r:id="rId53" ref="P19"/>
+    <hyperlink r:id="rId54" ref="N20"/>
+    <hyperlink r:id="rId55" ref="O20"/>
+    <hyperlink r:id="rId56" ref="P20"/>
+    <hyperlink r:id="rId57" ref="N21"/>
+    <hyperlink r:id="rId58" ref="P21"/>
+    <hyperlink r:id="rId59" ref="N22"/>
+    <hyperlink r:id="rId60" ref="O22"/>
+    <hyperlink r:id="rId61" ref="P22"/>
+    <hyperlink r:id="rId62" ref="N23"/>
+    <hyperlink r:id="rId63" ref="O23"/>
+    <hyperlink r:id="rId64" ref="P23"/>
+    <hyperlink r:id="rId65" ref="N24"/>
+    <hyperlink r:id="rId66" ref="O24"/>
+    <hyperlink r:id="rId67" ref="P24"/>
+    <hyperlink r:id="rId68" ref="N25"/>
+    <hyperlink r:id="rId69" ref="P25"/>
+    <hyperlink r:id="rId70" ref="N26"/>
+    <hyperlink r:id="rId71" ref="O26"/>
+    <hyperlink r:id="rId72" ref="P26"/>
+    <hyperlink r:id="rId73" ref="N27"/>
+    <hyperlink r:id="rId74" ref="O27"/>
+    <hyperlink r:id="rId75" ref="P27"/>
+    <hyperlink r:id="rId76" ref="N28"/>
+    <hyperlink r:id="rId77" ref="N29"/>
+    <hyperlink r:id="rId78" ref="O29"/>
+    <hyperlink r:id="rId79" ref="P29"/>
+    <hyperlink r:id="rId80" ref="N30"/>
+    <hyperlink r:id="rId81" ref="P30"/>
+    <hyperlink r:id="rId82" ref="N31"/>
+    <hyperlink r:id="rId83" ref="O31"/>
+    <hyperlink r:id="rId84" ref="P31"/>
+    <hyperlink r:id="rId85" ref="N32"/>
+    <hyperlink r:id="rId86" ref="O32"/>
+    <hyperlink r:id="rId87" ref="P32"/>
+    <hyperlink r:id="rId88" ref="N33"/>
+    <hyperlink r:id="rId89" ref="O33"/>
+    <hyperlink r:id="rId90" ref="P33"/>
+    <hyperlink r:id="rId91" ref="N34"/>
+    <hyperlink r:id="rId92" ref="O34"/>
+    <hyperlink r:id="rId93" ref="P34"/>
+    <hyperlink r:id="rId94" ref="N35"/>
+    <hyperlink r:id="rId95" ref="N36"/>
+    <hyperlink r:id="rId96" ref="O36"/>
+    <hyperlink r:id="rId97" ref="P36"/>
+    <hyperlink r:id="rId98" ref="N37"/>
+    <hyperlink r:id="rId99" ref="P37"/>
+    <hyperlink r:id="rId100" ref="N38"/>
+    <hyperlink r:id="rId101" ref="P38"/>
+    <hyperlink r:id="rId102" ref="N39"/>
+    <hyperlink r:id="rId103" ref="O39"/>
+    <hyperlink r:id="rId104" ref="P39"/>
+    <hyperlink r:id="rId105" ref="N40"/>
+    <hyperlink r:id="rId106" ref="O40"/>
+    <hyperlink r:id="rId107" ref="P40"/>
+    <hyperlink r:id="rId108" ref="N41"/>
+    <hyperlink r:id="rId109" ref="O41"/>
+    <hyperlink r:id="rId110" ref="P41"/>
+    <hyperlink r:id="rId111" ref="N42"/>
+    <hyperlink r:id="rId112" ref="O42"/>
+    <hyperlink r:id="rId113" ref="P42"/>
+    <hyperlink r:id="rId114" ref="N43"/>
+    <hyperlink r:id="rId115" ref="O43"/>
+    <hyperlink r:id="rId116" ref="P43"/>
+    <hyperlink r:id="rId117" ref="N44"/>
+    <hyperlink r:id="rId118" ref="O44"/>
+    <hyperlink r:id="rId119" ref="P44"/>
+    <hyperlink r:id="rId120" ref="N45"/>
+    <hyperlink r:id="rId121" ref="O45"/>
+    <hyperlink r:id="rId122" ref="P45"/>
+    <hyperlink r:id="rId123" ref="N46"/>
+    <hyperlink r:id="rId124" ref="O46"/>
+    <hyperlink r:id="rId125" ref="P46"/>
+    <hyperlink r:id="rId126" ref="N47"/>
+    <hyperlink r:id="rId127" ref="O47"/>
+    <hyperlink r:id="rId128" ref="P47"/>
+    <hyperlink r:id="rId129" ref="N48"/>
+    <hyperlink r:id="rId130" ref="P48"/>
+    <hyperlink r:id="rId131" ref="N49"/>
+    <hyperlink r:id="rId132" ref="O49"/>
+    <hyperlink r:id="rId133" ref="P49"/>
+    <hyperlink r:id="rId134" ref="N50"/>
+    <hyperlink r:id="rId135" ref="O50"/>
+    <hyperlink r:id="rId136" ref="P50"/>
+    <hyperlink r:id="rId137" ref="N51"/>
+    <hyperlink r:id="rId138" ref="O51"/>
+    <hyperlink r:id="rId139" ref="P51"/>
+    <hyperlink r:id="rId140" ref="N52"/>
+    <hyperlink r:id="rId141" ref="O52"/>
+    <hyperlink r:id="rId142" ref="P52"/>
+    <hyperlink r:id="rId143" ref="N53"/>
+    <hyperlink r:id="rId144" ref="O53"/>
+    <hyperlink r:id="rId145" ref="P53"/>
+    <hyperlink r:id="rId146" ref="N54"/>
+    <hyperlink r:id="rId147" ref="O54"/>
+    <hyperlink r:id="rId148" ref="P54"/>
+    <hyperlink r:id="rId149" ref="N55"/>
+    <hyperlink r:id="rId150" ref="O55"/>
+    <hyperlink r:id="rId151" ref="P55"/>
+    <hyperlink r:id="rId152" ref="N56"/>
+    <hyperlink r:id="rId153" ref="O56"/>
+    <hyperlink r:id="rId154" ref="P56"/>
+    <hyperlink r:id="rId155" ref="N57"/>
+    <hyperlink r:id="rId156" ref="O57"/>
+    <hyperlink r:id="rId157" ref="P57"/>
+    <hyperlink r:id="rId158" ref="O58"/>
+    <hyperlink r:id="rId159" ref="P58"/>
+    <hyperlink r:id="rId160" ref="N59"/>
+    <hyperlink r:id="rId161" ref="O59"/>
+    <hyperlink r:id="rId162" ref="P59"/>
+    <hyperlink r:id="rId163" ref="N60"/>
+    <hyperlink r:id="rId164" ref="O60"/>
+    <hyperlink r:id="rId165" ref="P60"/>
+    <hyperlink r:id="rId166" ref="O61"/>
+    <hyperlink r:id="rId167" ref="P61"/>
+    <hyperlink r:id="rId168" ref="N62"/>
+    <hyperlink r:id="rId169" ref="P62"/>
+    <hyperlink r:id="rId170" ref="N63"/>
+    <hyperlink r:id="rId171" ref="O63"/>
+    <hyperlink r:id="rId172" ref="P63"/>
+    <hyperlink r:id="rId173" ref="N64"/>
+    <hyperlink r:id="rId174" ref="O64"/>
+    <hyperlink r:id="rId175" ref="P64"/>
+    <hyperlink r:id="rId176" ref="N65"/>
+    <hyperlink r:id="rId177" ref="O65"/>
+    <hyperlink r:id="rId178" ref="P65"/>
+    <hyperlink r:id="rId179" ref="N66"/>
+    <hyperlink r:id="rId180" ref="O66"/>
+    <hyperlink r:id="rId181" ref="P66"/>
+    <hyperlink r:id="rId182" ref="N67"/>
+    <hyperlink r:id="rId183" ref="O67"/>
+    <hyperlink r:id="rId184" ref="P67"/>
+    <hyperlink r:id="rId185" ref="N68"/>
+    <hyperlink r:id="rId186" ref="O68"/>
+    <hyperlink r:id="rId187" ref="P68"/>
+    <hyperlink r:id="rId188" ref="N69"/>
+    <hyperlink r:id="rId189" ref="P69"/>
+    <hyperlink r:id="rId190" ref="N70"/>
+    <hyperlink r:id="rId191" ref="O70"/>
+    <hyperlink r:id="rId192" ref="P70"/>
+    <hyperlink r:id="rId193" ref="N71"/>
+    <hyperlink r:id="rId194" ref="O71"/>
+    <hyperlink r:id="rId195" ref="P71"/>
+    <hyperlink r:id="rId196" ref="N72"/>
+    <hyperlink r:id="rId197" ref="O72"/>
+    <hyperlink r:id="rId198" ref="P72"/>
   </hyperlinks>
-  <drawing r:id="rId130"/>
+  <drawing r:id="rId199"/>
 </worksheet>
 </file>
--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="353">
   <si>
     <t>Date</t>
   </si>
@@ -1135,7 +1135,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1168,6 +1168,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -7510,9 +7513,7 @@
       <c r="M72" s="1">
         <v>39.0</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="N72" s="12"/>
       <c r="O72" s="3" t="s">
         <v>351</v>
       </c>
@@ -7521,2806 +7522,2806 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="12"/>
+      <c r="A73" s="13"/>
     </row>
     <row r="74">
-      <c r="A74" s="12"/>
+      <c r="A74" s="13"/>
     </row>
     <row r="75">
-      <c r="A75" s="12"/>
+      <c r="A75" s="13"/>
     </row>
     <row r="76">
-      <c r="A76" s="12"/>
+      <c r="A76" s="13"/>
     </row>
     <row r="77">
-      <c r="A77" s="12"/>
+      <c r="A77" s="13"/>
     </row>
     <row r="78">
-      <c r="A78" s="12"/>
+      <c r="A78" s="13"/>
     </row>
     <row r="79">
-      <c r="A79" s="12"/>
+      <c r="A79" s="13"/>
     </row>
     <row r="80">
-      <c r="A80" s="12"/>
+      <c r="A80" s="13"/>
     </row>
     <row r="81">
-      <c r="A81" s="12"/>
+      <c r="A81" s="13"/>
     </row>
     <row r="82">
-      <c r="A82" s="12"/>
+      <c r="A82" s="13"/>
     </row>
     <row r="83">
-      <c r="A83" s="12"/>
+      <c r="A83" s="13"/>
     </row>
     <row r="84">
-      <c r="A84" s="12"/>
+      <c r="A84" s="13"/>
     </row>
     <row r="85">
-      <c r="A85" s="12"/>
+      <c r="A85" s="13"/>
     </row>
     <row r="86">
-      <c r="A86" s="12"/>
+      <c r="A86" s="13"/>
     </row>
     <row r="87">
-      <c r="A87" s="12"/>
+      <c r="A87" s="13"/>
     </row>
     <row r="88">
-      <c r="A88" s="12"/>
+      <c r="A88" s="13"/>
     </row>
     <row r="89">
-      <c r="A89" s="12"/>
+      <c r="A89" s="13"/>
     </row>
     <row r="90">
-      <c r="A90" s="12"/>
+      <c r="A90" s="13"/>
     </row>
     <row r="91">
-      <c r="A91" s="12"/>
+      <c r="A91" s="13"/>
     </row>
     <row r="92">
-      <c r="A92" s="12"/>
+      <c r="A92" s="13"/>
     </row>
     <row r="93">
-      <c r="A93" s="12"/>
+      <c r="A93" s="13"/>
     </row>
     <row r="94">
-      <c r="A94" s="12"/>
+      <c r="A94" s="13"/>
     </row>
     <row r="95">
-      <c r="A95" s="12"/>
+      <c r="A95" s="13"/>
     </row>
     <row r="96">
-      <c r="A96" s="12"/>
+      <c r="A96" s="13"/>
     </row>
     <row r="97">
-      <c r="A97" s="12"/>
+      <c r="A97" s="13"/>
     </row>
     <row r="98">
-      <c r="A98" s="12"/>
+      <c r="A98" s="13"/>
     </row>
     <row r="99">
-      <c r="A99" s="12"/>
+      <c r="A99" s="13"/>
     </row>
     <row r="100">
-      <c r="A100" s="12"/>
+      <c r="A100" s="13"/>
     </row>
     <row r="101">
-      <c r="A101" s="12"/>
+      <c r="A101" s="13"/>
     </row>
     <row r="102">
-      <c r="A102" s="12"/>
+      <c r="A102" s="13"/>
     </row>
     <row r="103">
-      <c r="A103" s="12"/>
+      <c r="A103" s="13"/>
     </row>
     <row r="104">
-      <c r="A104" s="12"/>
+      <c r="A104" s="13"/>
     </row>
     <row r="105">
-      <c r="A105" s="12"/>
+      <c r="A105" s="13"/>
     </row>
     <row r="106">
-      <c r="A106" s="12"/>
+      <c r="A106" s="13"/>
     </row>
     <row r="107">
-      <c r="A107" s="12"/>
+      <c r="A107" s="13"/>
     </row>
     <row r="108">
-      <c r="A108" s="12"/>
+      <c r="A108" s="13"/>
     </row>
     <row r="109">
-      <c r="A109" s="12"/>
+      <c r="A109" s="13"/>
     </row>
     <row r="110">
-      <c r="A110" s="12"/>
+      <c r="A110" s="13"/>
     </row>
     <row r="111">
-      <c r="A111" s="12"/>
+      <c r="A111" s="13"/>
     </row>
     <row r="112">
-      <c r="A112" s="12"/>
+      <c r="A112" s="13"/>
     </row>
     <row r="113">
-      <c r="A113" s="12"/>
+      <c r="A113" s="13"/>
     </row>
     <row r="114">
-      <c r="A114" s="12"/>
+      <c r="A114" s="13"/>
     </row>
     <row r="115">
-      <c r="A115" s="12"/>
+      <c r="A115" s="13"/>
     </row>
     <row r="116">
-      <c r="A116" s="12"/>
+      <c r="A116" s="13"/>
     </row>
     <row r="117">
-      <c r="A117" s="12"/>
+      <c r="A117" s="13"/>
     </row>
     <row r="118">
-      <c r="A118" s="12"/>
+      <c r="A118" s="13"/>
     </row>
     <row r="119">
-      <c r="A119" s="12"/>
+      <c r="A119" s="13"/>
     </row>
     <row r="120">
-      <c r="A120" s="12"/>
+      <c r="A120" s="13"/>
     </row>
     <row r="121">
-      <c r="A121" s="12"/>
+      <c r="A121" s="13"/>
     </row>
     <row r="122">
-      <c r="A122" s="12"/>
+      <c r="A122" s="13"/>
     </row>
     <row r="123">
-      <c r="A123" s="12"/>
+      <c r="A123" s="13"/>
     </row>
     <row r="124">
-      <c r="A124" s="12"/>
+      <c r="A124" s="13"/>
     </row>
     <row r="125">
-      <c r="A125" s="12"/>
+      <c r="A125" s="13"/>
     </row>
     <row r="126">
-      <c r="A126" s="12"/>
+      <c r="A126" s="13"/>
     </row>
     <row r="127">
-      <c r="A127" s="12"/>
+      <c r="A127" s="13"/>
     </row>
     <row r="128">
-      <c r="A128" s="12"/>
+      <c r="A128" s="13"/>
     </row>
     <row r="129">
-      <c r="A129" s="12"/>
+      <c r="A129" s="13"/>
     </row>
     <row r="130">
-      <c r="A130" s="12"/>
+      <c r="A130" s="13"/>
     </row>
     <row r="131">
-      <c r="A131" s="12"/>
+      <c r="A131" s="13"/>
     </row>
     <row r="132">
-      <c r="A132" s="12"/>
+      <c r="A132" s="13"/>
     </row>
     <row r="133">
-      <c r="A133" s="12"/>
+      <c r="A133" s="13"/>
     </row>
     <row r="134">
-      <c r="A134" s="12"/>
+      <c r="A134" s="13"/>
     </row>
     <row r="135">
-      <c r="A135" s="12"/>
+      <c r="A135" s="13"/>
     </row>
     <row r="136">
-      <c r="A136" s="12"/>
+      <c r="A136" s="13"/>
     </row>
     <row r="137">
-      <c r="A137" s="12"/>
+      <c r="A137" s="13"/>
     </row>
     <row r="138">
-      <c r="A138" s="12"/>
+      <c r="A138" s="13"/>
     </row>
     <row r="139">
-      <c r="A139" s="12"/>
+      <c r="A139" s="13"/>
     </row>
     <row r="140">
-      <c r="A140" s="12"/>
+      <c r="A140" s="13"/>
     </row>
     <row r="141">
-      <c r="A141" s="12"/>
+      <c r="A141" s="13"/>
     </row>
     <row r="142">
-      <c r="A142" s="12"/>
+      <c r="A142" s="13"/>
     </row>
     <row r="143">
-      <c r="A143" s="12"/>
+      <c r="A143" s="13"/>
     </row>
     <row r="144">
-      <c r="A144" s="12"/>
+      <c r="A144" s="13"/>
     </row>
     <row r="145">
-      <c r="A145" s="12"/>
+      <c r="A145" s="13"/>
     </row>
     <row r="146">
-      <c r="A146" s="12"/>
+      <c r="A146" s="13"/>
     </row>
     <row r="147">
-      <c r="A147" s="12"/>
+      <c r="A147" s="13"/>
     </row>
     <row r="148">
-      <c r="A148" s="12"/>
+      <c r="A148" s="13"/>
     </row>
     <row r="149">
-      <c r="A149" s="12"/>
+      <c r="A149" s="13"/>
     </row>
     <row r="150">
-      <c r="A150" s="12"/>
+      <c r="A150" s="13"/>
     </row>
     <row r="151">
-      <c r="A151" s="12"/>
+      <c r="A151" s="13"/>
     </row>
     <row r="152">
-      <c r="A152" s="12"/>
+      <c r="A152" s="13"/>
     </row>
     <row r="153">
-      <c r="A153" s="12"/>
+      <c r="A153" s="13"/>
     </row>
     <row r="154">
-      <c r="A154" s="12"/>
+      <c r="A154" s="13"/>
     </row>
     <row r="155">
-      <c r="A155" s="12"/>
+      <c r="A155" s="13"/>
     </row>
     <row r="156">
-      <c r="A156" s="12"/>
+      <c r="A156" s="13"/>
     </row>
     <row r="157">
-      <c r="A157" s="12"/>
+      <c r="A157" s="13"/>
     </row>
     <row r="158">
-      <c r="A158" s="12"/>
+      <c r="A158" s="13"/>
     </row>
     <row r="159">
-      <c r="A159" s="12"/>
+      <c r="A159" s="13"/>
     </row>
     <row r="160">
-      <c r="A160" s="12"/>
+      <c r="A160" s="13"/>
     </row>
     <row r="161">
-      <c r="A161" s="12"/>
+      <c r="A161" s="13"/>
     </row>
     <row r="162">
-      <c r="A162" s="12"/>
+      <c r="A162" s="13"/>
     </row>
     <row r="163">
-      <c r="A163" s="12"/>
+      <c r="A163" s="13"/>
     </row>
     <row r="164">
-      <c r="A164" s="12"/>
+      <c r="A164" s="13"/>
     </row>
     <row r="165">
-      <c r="A165" s="12"/>
+      <c r="A165" s="13"/>
     </row>
     <row r="166">
-      <c r="A166" s="12"/>
+      <c r="A166" s="13"/>
     </row>
     <row r="167">
-      <c r="A167" s="12"/>
+      <c r="A167" s="13"/>
     </row>
     <row r="168">
-      <c r="A168" s="12"/>
+      <c r="A168" s="13"/>
     </row>
     <row r="169">
-      <c r="A169" s="12"/>
+      <c r="A169" s="13"/>
     </row>
     <row r="170">
-      <c r="A170" s="12"/>
+      <c r="A170" s="13"/>
     </row>
     <row r="171">
-      <c r="A171" s="12"/>
+      <c r="A171" s="13"/>
     </row>
     <row r="172">
-      <c r="A172" s="12"/>
+      <c r="A172" s="13"/>
     </row>
     <row r="173">
-      <c r="A173" s="12"/>
+      <c r="A173" s="13"/>
     </row>
     <row r="174">
-      <c r="A174" s="12"/>
+      <c r="A174" s="13"/>
     </row>
     <row r="175">
-      <c r="A175" s="12"/>
+      <c r="A175" s="13"/>
     </row>
     <row r="176">
-      <c r="A176" s="12"/>
+      <c r="A176" s="13"/>
     </row>
     <row r="177">
-      <c r="A177" s="12"/>
+      <c r="A177" s="13"/>
     </row>
     <row r="178">
-      <c r="A178" s="12"/>
+      <c r="A178" s="13"/>
     </row>
     <row r="179">
-      <c r="A179" s="12"/>
+      <c r="A179" s="13"/>
     </row>
     <row r="180">
-      <c r="A180" s="12"/>
+      <c r="A180" s="13"/>
     </row>
     <row r="181">
-      <c r="A181" s="12"/>
+      <c r="A181" s="13"/>
     </row>
     <row r="182">
-      <c r="A182" s="12"/>
+      <c r="A182" s="13"/>
     </row>
     <row r="183">
-      <c r="A183" s="12"/>
+      <c r="A183" s="13"/>
     </row>
     <row r="184">
-      <c r="A184" s="12"/>
+      <c r="A184" s="13"/>
     </row>
     <row r="185">
-      <c r="A185" s="12"/>
+      <c r="A185" s="13"/>
     </row>
     <row r="186">
-      <c r="A186" s="12"/>
+      <c r="A186" s="13"/>
     </row>
     <row r="187">
-      <c r="A187" s="12"/>
+      <c r="A187" s="13"/>
     </row>
     <row r="188">
-      <c r="A188" s="12"/>
+      <c r="A188" s="13"/>
     </row>
     <row r="189">
-      <c r="A189" s="12"/>
+      <c r="A189" s="13"/>
     </row>
     <row r="190">
-      <c r="A190" s="12"/>
+      <c r="A190" s="13"/>
     </row>
     <row r="191">
-      <c r="A191" s="12"/>
+      <c r="A191" s="13"/>
     </row>
     <row r="192">
-      <c r="A192" s="12"/>
+      <c r="A192" s="13"/>
     </row>
     <row r="193">
-      <c r="A193" s="12"/>
+      <c r="A193" s="13"/>
     </row>
     <row r="194">
-      <c r="A194" s="12"/>
+      <c r="A194" s="13"/>
     </row>
     <row r="195">
-      <c r="A195" s="12"/>
+      <c r="A195" s="13"/>
     </row>
     <row r="196">
-      <c r="A196" s="12"/>
+      <c r="A196" s="13"/>
     </row>
     <row r="197">
-      <c r="A197" s="12"/>
+      <c r="A197" s="13"/>
     </row>
     <row r="198">
-      <c r="A198" s="12"/>
+      <c r="A198" s="13"/>
     </row>
     <row r="199">
-      <c r="A199" s="12"/>
+      <c r="A199" s="13"/>
     </row>
     <row r="200">
-      <c r="A200" s="12"/>
+      <c r="A200" s="13"/>
     </row>
     <row r="201">
-      <c r="A201" s="12"/>
+      <c r="A201" s="13"/>
     </row>
     <row r="202">
-      <c r="A202" s="12"/>
+      <c r="A202" s="13"/>
     </row>
     <row r="203">
-      <c r="A203" s="12"/>
+      <c r="A203" s="13"/>
     </row>
     <row r="204">
-      <c r="A204" s="12"/>
+      <c r="A204" s="13"/>
     </row>
     <row r="205">
-      <c r="A205" s="12"/>
+      <c r="A205" s="13"/>
     </row>
     <row r="206">
-      <c r="A206" s="12"/>
+      <c r="A206" s="13"/>
     </row>
     <row r="207">
-      <c r="A207" s="12"/>
+      <c r="A207" s="13"/>
     </row>
     <row r="208">
-      <c r="A208" s="12"/>
+      <c r="A208" s="13"/>
     </row>
     <row r="209">
-      <c r="A209" s="12"/>
+      <c r="A209" s="13"/>
     </row>
     <row r="210">
-      <c r="A210" s="12"/>
+      <c r="A210" s="13"/>
     </row>
     <row r="211">
-      <c r="A211" s="12"/>
+      <c r="A211" s="13"/>
     </row>
     <row r="212">
-      <c r="A212" s="12"/>
+      <c r="A212" s="13"/>
     </row>
     <row r="213">
-      <c r="A213" s="12"/>
+      <c r="A213" s="13"/>
     </row>
     <row r="214">
-      <c r="A214" s="12"/>
+      <c r="A214" s="13"/>
     </row>
     <row r="215">
-      <c r="A215" s="12"/>
+      <c r="A215" s="13"/>
     </row>
     <row r="216">
-      <c r="A216" s="12"/>
+      <c r="A216" s="13"/>
     </row>
     <row r="217">
-      <c r="A217" s="12"/>
+      <c r="A217" s="13"/>
     </row>
     <row r="218">
-      <c r="A218" s="12"/>
+      <c r="A218" s="13"/>
     </row>
     <row r="219">
-      <c r="A219" s="12"/>
+      <c r="A219" s="13"/>
     </row>
     <row r="220">
-      <c r="A220" s="12"/>
+      <c r="A220" s="13"/>
     </row>
     <row r="221">
-      <c r="A221" s="12"/>
+      <c r="A221" s="13"/>
     </row>
     <row r="222">
-      <c r="A222" s="12"/>
+      <c r="A222" s="13"/>
     </row>
     <row r="223">
-      <c r="A223" s="12"/>
+      <c r="A223" s="13"/>
     </row>
     <row r="224">
-      <c r="A224" s="12"/>
+      <c r="A224" s="13"/>
     </row>
     <row r="225">
-      <c r="A225" s="12"/>
+      <c r="A225" s="13"/>
     </row>
     <row r="226">
-      <c r="A226" s="12"/>
+      <c r="A226" s="13"/>
     </row>
     <row r="227">
-      <c r="A227" s="12"/>
+      <c r="A227" s="13"/>
     </row>
     <row r="228">
-      <c r="A228" s="12"/>
+      <c r="A228" s="13"/>
     </row>
     <row r="229">
-      <c r="A229" s="12"/>
+      <c r="A229" s="13"/>
     </row>
     <row r="230">
-      <c r="A230" s="12"/>
+      <c r="A230" s="13"/>
     </row>
     <row r="231">
-      <c r="A231" s="12"/>
+      <c r="A231" s="13"/>
     </row>
     <row r="232">
-      <c r="A232" s="12"/>
+      <c r="A232" s="13"/>
     </row>
     <row r="233">
-      <c r="A233" s="12"/>
+      <c r="A233" s="13"/>
     </row>
     <row r="234">
-      <c r="A234" s="12"/>
+      <c r="A234" s="13"/>
     </row>
     <row r="235">
-      <c r="A235" s="12"/>
+      <c r="A235" s="13"/>
     </row>
     <row r="236">
-      <c r="A236" s="12"/>
+      <c r="A236" s="13"/>
     </row>
     <row r="237">
-      <c r="A237" s="12"/>
+      <c r="A237" s="13"/>
     </row>
     <row r="238">
-      <c r="A238" s="12"/>
+      <c r="A238" s="13"/>
     </row>
     <row r="239">
-      <c r="A239" s="12"/>
+      <c r="A239" s="13"/>
     </row>
     <row r="240">
-      <c r="A240" s="12"/>
+      <c r="A240" s="13"/>
     </row>
     <row r="241">
-      <c r="A241" s="12"/>
+      <c r="A241" s="13"/>
     </row>
     <row r="242">
-      <c r="A242" s="12"/>
+      <c r="A242" s="13"/>
     </row>
     <row r="243">
-      <c r="A243" s="12"/>
+      <c r="A243" s="13"/>
     </row>
     <row r="244">
-      <c r="A244" s="12"/>
+      <c r="A244" s="13"/>
     </row>
     <row r="245">
-      <c r="A245" s="12"/>
+      <c r="A245" s="13"/>
     </row>
     <row r="246">
-      <c r="A246" s="12"/>
+      <c r="A246" s="13"/>
     </row>
     <row r="247">
-      <c r="A247" s="12"/>
+      <c r="A247" s="13"/>
     </row>
     <row r="248">
-      <c r="A248" s="12"/>
+      <c r="A248" s="13"/>
     </row>
     <row r="249">
-      <c r="A249" s="12"/>
+      <c r="A249" s="13"/>
     </row>
     <row r="250">
-      <c r="A250" s="12"/>
+      <c r="A250" s="13"/>
     </row>
     <row r="251">
-      <c r="A251" s="12"/>
+      <c r="A251" s="13"/>
     </row>
     <row r="252">
-      <c r="A252" s="12"/>
+      <c r="A252" s="13"/>
     </row>
     <row r="253">
-      <c r="A253" s="12"/>
+      <c r="A253" s="13"/>
     </row>
     <row r="254">
-      <c r="A254" s="12"/>
+      <c r="A254" s="13"/>
     </row>
     <row r="255">
-      <c r="A255" s="12"/>
+      <c r="A255" s="13"/>
     </row>
     <row r="256">
-      <c r="A256" s="12"/>
+      <c r="A256" s="13"/>
     </row>
     <row r="257">
-      <c r="A257" s="12"/>
+      <c r="A257" s="13"/>
     </row>
     <row r="258">
-      <c r="A258" s="12"/>
+      <c r="A258" s="13"/>
     </row>
     <row r="259">
-      <c r="A259" s="12"/>
+      <c r="A259" s="13"/>
     </row>
     <row r="260">
-      <c r="A260" s="12"/>
+      <c r="A260" s="13"/>
     </row>
     <row r="261">
-      <c r="A261" s="12"/>
+      <c r="A261" s="13"/>
     </row>
     <row r="262">
-      <c r="A262" s="12"/>
+      <c r="A262" s="13"/>
     </row>
     <row r="263">
-      <c r="A263" s="12"/>
+      <c r="A263" s="13"/>
     </row>
     <row r="264">
-      <c r="A264" s="12"/>
+      <c r="A264" s="13"/>
     </row>
     <row r="265">
-      <c r="A265" s="12"/>
+      <c r="A265" s="13"/>
     </row>
     <row r="266">
-      <c r="A266" s="12"/>
+      <c r="A266" s="13"/>
     </row>
     <row r="267">
-      <c r="A267" s="12"/>
+      <c r="A267" s="13"/>
     </row>
     <row r="268">
-      <c r="A268" s="12"/>
+      <c r="A268" s="13"/>
     </row>
     <row r="269">
-      <c r="A269" s="12"/>
+      <c r="A269" s="13"/>
     </row>
     <row r="270">
-      <c r="A270" s="12"/>
+      <c r="A270" s="13"/>
     </row>
     <row r="271">
-      <c r="A271" s="12"/>
+      <c r="A271" s="13"/>
     </row>
     <row r="272">
-      <c r="A272" s="12"/>
+      <c r="A272" s="13"/>
     </row>
     <row r="273">
-      <c r="A273" s="12"/>
+      <c r="A273" s="13"/>
     </row>
     <row r="274">
-      <c r="A274" s="12"/>
+      <c r="A274" s="13"/>
     </row>
     <row r="275">
-      <c r="A275" s="12"/>
+      <c r="A275" s="13"/>
     </row>
     <row r="276">
-      <c r="A276" s="12"/>
+      <c r="A276" s="13"/>
     </row>
     <row r="277">
-      <c r="A277" s="12"/>
+      <c r="A277" s="13"/>
     </row>
     <row r="278">
-      <c r="A278" s="12"/>
+      <c r="A278" s="13"/>
     </row>
     <row r="279">
-      <c r="A279" s="12"/>
+      <c r="A279" s="13"/>
     </row>
     <row r="280">
-      <c r="A280" s="12"/>
+      <c r="A280" s="13"/>
     </row>
     <row r="281">
-      <c r="A281" s="12"/>
+      <c r="A281" s="13"/>
     </row>
     <row r="282">
-      <c r="A282" s="12"/>
+      <c r="A282" s="13"/>
     </row>
     <row r="283">
-      <c r="A283" s="12"/>
+      <c r="A283" s="13"/>
     </row>
     <row r="284">
-      <c r="A284" s="12"/>
+      <c r="A284" s="13"/>
     </row>
     <row r="285">
-      <c r="A285" s="12"/>
+      <c r="A285" s="13"/>
     </row>
     <row r="286">
-      <c r="A286" s="12"/>
+      <c r="A286" s="13"/>
     </row>
     <row r="287">
-      <c r="A287" s="12"/>
+      <c r="A287" s="13"/>
     </row>
     <row r="288">
-      <c r="A288" s="12"/>
+      <c r="A288" s="13"/>
     </row>
     <row r="289">
-      <c r="A289" s="12"/>
+      <c r="A289" s="13"/>
     </row>
     <row r="290">
-      <c r="A290" s="12"/>
+      <c r="A290" s="13"/>
     </row>
     <row r="291">
-      <c r="A291" s="12"/>
+      <c r="A291" s="13"/>
     </row>
     <row r="292">
-      <c r="A292" s="12"/>
+      <c r="A292" s="13"/>
     </row>
     <row r="293">
-      <c r="A293" s="12"/>
+      <c r="A293" s="13"/>
     </row>
     <row r="294">
-      <c r="A294" s="12"/>
+      <c r="A294" s="13"/>
     </row>
     <row r="295">
-      <c r="A295" s="12"/>
+      <c r="A295" s="13"/>
     </row>
     <row r="296">
-      <c r="A296" s="12"/>
+      <c r="A296" s="13"/>
     </row>
     <row r="297">
-      <c r="A297" s="12"/>
+      <c r="A297" s="13"/>
     </row>
     <row r="298">
-      <c r="A298" s="12"/>
+      <c r="A298" s="13"/>
     </row>
     <row r="299">
-      <c r="A299" s="12"/>
+      <c r="A299" s="13"/>
     </row>
     <row r="300">
-      <c r="A300" s="12"/>
+      <c r="A300" s="13"/>
     </row>
     <row r="301">
-      <c r="A301" s="12"/>
+      <c r="A301" s="13"/>
     </row>
     <row r="302">
-      <c r="A302" s="12"/>
+      <c r="A302" s="13"/>
     </row>
     <row r="303">
-      <c r="A303" s="12"/>
+      <c r="A303" s="13"/>
     </row>
     <row r="304">
-      <c r="A304" s="12"/>
+      <c r="A304" s="13"/>
     </row>
     <row r="305">
-      <c r="A305" s="12"/>
+      <c r="A305" s="13"/>
     </row>
     <row r="306">
-      <c r="A306" s="12"/>
+      <c r="A306" s="13"/>
     </row>
     <row r="307">
-      <c r="A307" s="12"/>
+      <c r="A307" s="13"/>
     </row>
     <row r="308">
-      <c r="A308" s="12"/>
+      <c r="A308" s="13"/>
     </row>
     <row r="309">
-      <c r="A309" s="12"/>
+      <c r="A309" s="13"/>
     </row>
     <row r="310">
-      <c r="A310" s="12"/>
+      <c r="A310" s="13"/>
     </row>
     <row r="311">
-      <c r="A311" s="12"/>
+      <c r="A311" s="13"/>
     </row>
     <row r="312">
-      <c r="A312" s="12"/>
+      <c r="A312" s="13"/>
     </row>
     <row r="313">
-      <c r="A313" s="12"/>
+      <c r="A313" s="13"/>
     </row>
     <row r="314">
-      <c r="A314" s="12"/>
+      <c r="A314" s="13"/>
     </row>
     <row r="315">
-      <c r="A315" s="12"/>
+      <c r="A315" s="13"/>
     </row>
     <row r="316">
-      <c r="A316" s="12"/>
+      <c r="A316" s="13"/>
     </row>
     <row r="317">
-      <c r="A317" s="12"/>
+      <c r="A317" s="13"/>
     </row>
     <row r="318">
-      <c r="A318" s="12"/>
+      <c r="A318" s="13"/>
     </row>
     <row r="319">
-      <c r="A319" s="12"/>
+      <c r="A319" s="13"/>
     </row>
     <row r="320">
-      <c r="A320" s="12"/>
+      <c r="A320" s="13"/>
     </row>
     <row r="321">
-      <c r="A321" s="12"/>
+      <c r="A321" s="13"/>
     </row>
     <row r="322">
-      <c r="A322" s="12"/>
+      <c r="A322" s="13"/>
     </row>
     <row r="323">
-      <c r="A323" s="12"/>
+      <c r="A323" s="13"/>
     </row>
     <row r="324">
-      <c r="A324" s="12"/>
+      <c r="A324" s="13"/>
     </row>
     <row r="325">
-      <c r="A325" s="12"/>
+      <c r="A325" s="13"/>
     </row>
     <row r="326">
-      <c r="A326" s="12"/>
+      <c r="A326" s="13"/>
     </row>
     <row r="327">
-      <c r="A327" s="12"/>
+      <c r="A327" s="13"/>
     </row>
     <row r="328">
-      <c r="A328" s="12"/>
+      <c r="A328" s="13"/>
     </row>
     <row r="329">
-      <c r="A329" s="12"/>
+      <c r="A329" s="13"/>
     </row>
     <row r="330">
-      <c r="A330" s="12"/>
+      <c r="A330" s="13"/>
     </row>
     <row r="331">
-      <c r="A331" s="12"/>
+      <c r="A331" s="13"/>
     </row>
     <row r="332">
-      <c r="A332" s="12"/>
+      <c r="A332" s="13"/>
     </row>
     <row r="333">
-      <c r="A333" s="12"/>
+      <c r="A333" s="13"/>
     </row>
     <row r="334">
-      <c r="A334" s="12"/>
+      <c r="A334" s="13"/>
     </row>
     <row r="335">
-      <c r="A335" s="12"/>
+      <c r="A335" s="13"/>
     </row>
     <row r="336">
-      <c r="A336" s="12"/>
+      <c r="A336" s="13"/>
     </row>
     <row r="337">
-      <c r="A337" s="12"/>
+      <c r="A337" s="13"/>
     </row>
     <row r="338">
-      <c r="A338" s="12"/>
+      <c r="A338" s="13"/>
     </row>
     <row r="339">
-      <c r="A339" s="12"/>
+      <c r="A339" s="13"/>
     </row>
     <row r="340">
-      <c r="A340" s="12"/>
+      <c r="A340" s="13"/>
     </row>
     <row r="341">
-      <c r="A341" s="12"/>
+      <c r="A341" s="13"/>
     </row>
     <row r="342">
-      <c r="A342" s="12"/>
+      <c r="A342" s="13"/>
     </row>
     <row r="343">
-      <c r="A343" s="12"/>
+      <c r="A343" s="13"/>
     </row>
     <row r="344">
-      <c r="A344" s="12"/>
+      <c r="A344" s="13"/>
     </row>
     <row r="345">
-      <c r="A345" s="12"/>
+      <c r="A345" s="13"/>
     </row>
     <row r="346">
-      <c r="A346" s="12"/>
+      <c r="A346" s="13"/>
     </row>
     <row r="347">
-      <c r="A347" s="12"/>
+      <c r="A347" s="13"/>
     </row>
     <row r="348">
-      <c r="A348" s="12"/>
+      <c r="A348" s="13"/>
     </row>
     <row r="349">
-      <c r="A349" s="12"/>
+      <c r="A349" s="13"/>
     </row>
     <row r="350">
-      <c r="A350" s="12"/>
+      <c r="A350" s="13"/>
     </row>
     <row r="351">
-      <c r="A351" s="12"/>
+      <c r="A351" s="13"/>
     </row>
     <row r="352">
-      <c r="A352" s="12"/>
+      <c r="A352" s="13"/>
     </row>
     <row r="353">
-      <c r="A353" s="12"/>
+      <c r="A353" s="13"/>
     </row>
     <row r="354">
-      <c r="A354" s="12"/>
+      <c r="A354" s="13"/>
     </row>
     <row r="355">
-      <c r="A355" s="12"/>
+      <c r="A355" s="13"/>
     </row>
     <row r="356">
-      <c r="A356" s="12"/>
+      <c r="A356" s="13"/>
     </row>
     <row r="357">
-      <c r="A357" s="12"/>
+      <c r="A357" s="13"/>
     </row>
     <row r="358">
-      <c r="A358" s="12"/>
+      <c r="A358" s="13"/>
     </row>
     <row r="359">
-      <c r="A359" s="12"/>
+      <c r="A359" s="13"/>
     </row>
     <row r="360">
-      <c r="A360" s="12"/>
+      <c r="A360" s="13"/>
     </row>
     <row r="361">
-      <c r="A361" s="12"/>
+      <c r="A361" s="13"/>
     </row>
     <row r="362">
-      <c r="A362" s="12"/>
+      <c r="A362" s="13"/>
     </row>
     <row r="363">
-      <c r="A363" s="12"/>
+      <c r="A363" s="13"/>
     </row>
     <row r="364">
-      <c r="A364" s="12"/>
+      <c r="A364" s="13"/>
     </row>
     <row r="365">
-      <c r="A365" s="12"/>
+      <c r="A365" s="13"/>
     </row>
     <row r="366">
-      <c r="A366" s="12"/>
+      <c r="A366" s="13"/>
     </row>
     <row r="367">
-      <c r="A367" s="12"/>
+      <c r="A367" s="13"/>
     </row>
     <row r="368">
-      <c r="A368" s="12"/>
+      <c r="A368" s="13"/>
     </row>
     <row r="369">
-      <c r="A369" s="12"/>
+      <c r="A369" s="13"/>
     </row>
     <row r="370">
-      <c r="A370" s="12"/>
+      <c r="A370" s="13"/>
     </row>
     <row r="371">
-      <c r="A371" s="12"/>
+      <c r="A371" s="13"/>
     </row>
     <row r="372">
-      <c r="A372" s="12"/>
+      <c r="A372" s="13"/>
     </row>
     <row r="373">
-      <c r="A373" s="12"/>
+      <c r="A373" s="13"/>
     </row>
     <row r="374">
-      <c r="A374" s="12"/>
+      <c r="A374" s="13"/>
     </row>
     <row r="375">
-      <c r="A375" s="12"/>
+      <c r="A375" s="13"/>
     </row>
     <row r="376">
-      <c r="A376" s="12"/>
+      <c r="A376" s="13"/>
     </row>
     <row r="377">
-      <c r="A377" s="12"/>
+      <c r="A377" s="13"/>
     </row>
     <row r="378">
-      <c r="A378" s="12"/>
+      <c r="A378" s="13"/>
     </row>
     <row r="379">
-      <c r="A379" s="12"/>
+      <c r="A379" s="13"/>
     </row>
     <row r="380">
-      <c r="A380" s="12"/>
+      <c r="A380" s="13"/>
     </row>
     <row r="381">
-      <c r="A381" s="12"/>
+      <c r="A381" s="13"/>
     </row>
     <row r="382">
-      <c r="A382" s="12"/>
+      <c r="A382" s="13"/>
     </row>
     <row r="383">
-      <c r="A383" s="12"/>
+      <c r="A383" s="13"/>
     </row>
     <row r="384">
-      <c r="A384" s="12"/>
+      <c r="A384" s="13"/>
     </row>
     <row r="385">
-      <c r="A385" s="12"/>
+      <c r="A385" s="13"/>
     </row>
     <row r="386">
-      <c r="A386" s="12"/>
+      <c r="A386" s="13"/>
     </row>
     <row r="387">
-      <c r="A387" s="12"/>
+      <c r="A387" s="13"/>
     </row>
     <row r="388">
-      <c r="A388" s="12"/>
+      <c r="A388" s="13"/>
     </row>
     <row r="389">
-      <c r="A389" s="12"/>
+      <c r="A389" s="13"/>
     </row>
     <row r="390">
-      <c r="A390" s="12"/>
+      <c r="A390" s="13"/>
     </row>
     <row r="391">
-      <c r="A391" s="12"/>
+      <c r="A391" s="13"/>
     </row>
     <row r="392">
-      <c r="A392" s="12"/>
+      <c r="A392" s="13"/>
     </row>
     <row r="393">
-      <c r="A393" s="12"/>
+      <c r="A393" s="13"/>
     </row>
     <row r="394">
-      <c r="A394" s="12"/>
+      <c r="A394" s="13"/>
     </row>
     <row r="395">
-      <c r="A395" s="12"/>
+      <c r="A395" s="13"/>
     </row>
     <row r="396">
-      <c r="A396" s="12"/>
+      <c r="A396" s="13"/>
     </row>
     <row r="397">
-      <c r="A397" s="12"/>
+      <c r="A397" s="13"/>
     </row>
     <row r="398">
-      <c r="A398" s="12"/>
+      <c r="A398" s="13"/>
     </row>
     <row r="399">
-      <c r="A399" s="12"/>
+      <c r="A399" s="13"/>
     </row>
     <row r="400">
-      <c r="A400" s="12"/>
+      <c r="A400" s="13"/>
     </row>
     <row r="401">
-      <c r="A401" s="12"/>
+      <c r="A401" s="13"/>
     </row>
     <row r="402">
-      <c r="A402" s="12"/>
+      <c r="A402" s="13"/>
     </row>
     <row r="403">
-      <c r="A403" s="12"/>
+      <c r="A403" s="13"/>
     </row>
     <row r="404">
-      <c r="A404" s="12"/>
+      <c r="A404" s="13"/>
     </row>
     <row r="405">
-      <c r="A405" s="12"/>
+      <c r="A405" s="13"/>
     </row>
     <row r="406">
-      <c r="A406" s="12"/>
+      <c r="A406" s="13"/>
     </row>
     <row r="407">
-      <c r="A407" s="12"/>
+      <c r="A407" s="13"/>
     </row>
     <row r="408">
-      <c r="A408" s="12"/>
+      <c r="A408" s="13"/>
     </row>
     <row r="409">
-      <c r="A409" s="12"/>
+      <c r="A409" s="13"/>
     </row>
     <row r="410">
-      <c r="A410" s="12"/>
+      <c r="A410" s="13"/>
     </row>
     <row r="411">
-      <c r="A411" s="12"/>
+      <c r="A411" s="13"/>
     </row>
     <row r="412">
-      <c r="A412" s="12"/>
+      <c r="A412" s="13"/>
     </row>
     <row r="413">
-      <c r="A413" s="12"/>
+      <c r="A413" s="13"/>
     </row>
     <row r="414">
-      <c r="A414" s="12"/>
+      <c r="A414" s="13"/>
     </row>
     <row r="415">
-      <c r="A415" s="12"/>
+      <c r="A415" s="13"/>
     </row>
     <row r="416">
-      <c r="A416" s="12"/>
+      <c r="A416" s="13"/>
     </row>
     <row r="417">
-      <c r="A417" s="12"/>
+      <c r="A417" s="13"/>
     </row>
     <row r="418">
-      <c r="A418" s="12"/>
+      <c r="A418" s="13"/>
     </row>
     <row r="419">
-      <c r="A419" s="12"/>
+      <c r="A419" s="13"/>
     </row>
     <row r="420">
-      <c r="A420" s="12"/>
+      <c r="A420" s="13"/>
     </row>
     <row r="421">
-      <c r="A421" s="12"/>
+      <c r="A421" s="13"/>
     </row>
     <row r="422">
-      <c r="A422" s="12"/>
+      <c r="A422" s="13"/>
     </row>
     <row r="423">
-      <c r="A423" s="12"/>
+      <c r="A423" s="13"/>
     </row>
     <row r="424">
-      <c r="A424" s="12"/>
+      <c r="A424" s="13"/>
     </row>
     <row r="425">
-      <c r="A425" s="12"/>
+      <c r="A425" s="13"/>
     </row>
     <row r="426">
-      <c r="A426" s="12"/>
+      <c r="A426" s="13"/>
     </row>
     <row r="427">
-      <c r="A427" s="12"/>
+      <c r="A427" s="13"/>
     </row>
     <row r="428">
-      <c r="A428" s="12"/>
+      <c r="A428" s="13"/>
     </row>
     <row r="429">
-      <c r="A429" s="12"/>
+      <c r="A429" s="13"/>
     </row>
     <row r="430">
-      <c r="A430" s="12"/>
+      <c r="A430" s="13"/>
     </row>
     <row r="431">
-      <c r="A431" s="12"/>
+      <c r="A431" s="13"/>
     </row>
     <row r="432">
-      <c r="A432" s="12"/>
+      <c r="A432" s="13"/>
     </row>
     <row r="433">
-      <c r="A433" s="12"/>
+      <c r="A433" s="13"/>
     </row>
     <row r="434">
-      <c r="A434" s="12"/>
+      <c r="A434" s="13"/>
     </row>
     <row r="435">
-      <c r="A435" s="12"/>
+      <c r="A435" s="13"/>
     </row>
     <row r="436">
-      <c r="A436" s="12"/>
+      <c r="A436" s="13"/>
     </row>
     <row r="437">
-      <c r="A437" s="12"/>
+      <c r="A437" s="13"/>
     </row>
     <row r="438">
-      <c r="A438" s="12"/>
+      <c r="A438" s="13"/>
     </row>
     <row r="439">
-      <c r="A439" s="12"/>
+      <c r="A439" s="13"/>
     </row>
     <row r="440">
-      <c r="A440" s="12"/>
+      <c r="A440" s="13"/>
     </row>
     <row r="441">
-      <c r="A441" s="12"/>
+      <c r="A441" s="13"/>
     </row>
     <row r="442">
-      <c r="A442" s="12"/>
+      <c r="A442" s="13"/>
     </row>
     <row r="443">
-      <c r="A443" s="12"/>
+      <c r="A443" s="13"/>
     </row>
     <row r="444">
-      <c r="A444" s="12"/>
+      <c r="A444" s="13"/>
     </row>
     <row r="445">
-      <c r="A445" s="12"/>
+      <c r="A445" s="13"/>
     </row>
     <row r="446">
-      <c r="A446" s="12"/>
+      <c r="A446" s="13"/>
     </row>
     <row r="447">
-      <c r="A447" s="12"/>
+      <c r="A447" s="13"/>
     </row>
     <row r="448">
-      <c r="A448" s="12"/>
+      <c r="A448" s="13"/>
     </row>
     <row r="449">
-      <c r="A449" s="12"/>
+      <c r="A449" s="13"/>
     </row>
     <row r="450">
-      <c r="A450" s="12"/>
+      <c r="A450" s="13"/>
     </row>
     <row r="451">
-      <c r="A451" s="12"/>
+      <c r="A451" s="13"/>
     </row>
     <row r="452">
-      <c r="A452" s="12"/>
+      <c r="A452" s="13"/>
     </row>
     <row r="453">
-      <c r="A453" s="12"/>
+      <c r="A453" s="13"/>
     </row>
     <row r="454">
-      <c r="A454" s="12"/>
+      <c r="A454" s="13"/>
     </row>
     <row r="455">
-      <c r="A455" s="12"/>
+      <c r="A455" s="13"/>
     </row>
     <row r="456">
-      <c r="A456" s="12"/>
+      <c r="A456" s="13"/>
     </row>
     <row r="457">
-      <c r="A457" s="12"/>
+      <c r="A457" s="13"/>
     </row>
     <row r="458">
-      <c r="A458" s="12"/>
+      <c r="A458" s="13"/>
     </row>
     <row r="459">
-      <c r="A459" s="12"/>
+      <c r="A459" s="13"/>
     </row>
     <row r="460">
-      <c r="A460" s="12"/>
+      <c r="A460" s="13"/>
     </row>
     <row r="461">
-      <c r="A461" s="12"/>
+      <c r="A461" s="13"/>
     </row>
     <row r="462">
-      <c r="A462" s="12"/>
+      <c r="A462" s="13"/>
     </row>
     <row r="463">
-      <c r="A463" s="12"/>
+      <c r="A463" s="13"/>
     </row>
     <row r="464">
-      <c r="A464" s="12"/>
+      <c r="A464" s="13"/>
     </row>
     <row r="465">
-      <c r="A465" s="12"/>
+      <c r="A465" s="13"/>
     </row>
     <row r="466">
-      <c r="A466" s="12"/>
+      <c r="A466" s="13"/>
     </row>
     <row r="467">
-      <c r="A467" s="12"/>
+      <c r="A467" s="13"/>
     </row>
     <row r="468">
-      <c r="A468" s="12"/>
+      <c r="A468" s="13"/>
     </row>
     <row r="469">
-      <c r="A469" s="12"/>
+      <c r="A469" s="13"/>
     </row>
     <row r="470">
-      <c r="A470" s="12"/>
+      <c r="A470" s="13"/>
     </row>
     <row r="471">
-      <c r="A471" s="12"/>
+      <c r="A471" s="13"/>
     </row>
     <row r="472">
-      <c r="A472" s="12"/>
+      <c r="A472" s="13"/>
     </row>
     <row r="473">
-      <c r="A473" s="12"/>
+      <c r="A473" s="13"/>
     </row>
     <row r="474">
-      <c r="A474" s="12"/>
+      <c r="A474" s="13"/>
     </row>
     <row r="475">
-      <c r="A475" s="12"/>
+      <c r="A475" s="13"/>
     </row>
     <row r="476">
-      <c r="A476" s="12"/>
+      <c r="A476" s="13"/>
     </row>
     <row r="477">
-      <c r="A477" s="12"/>
+      <c r="A477" s="13"/>
     </row>
     <row r="478">
-      <c r="A478" s="12"/>
+      <c r="A478" s="13"/>
     </row>
     <row r="479">
-      <c r="A479" s="12"/>
+      <c r="A479" s="13"/>
     </row>
     <row r="480">
-      <c r="A480" s="12"/>
+      <c r="A480" s="13"/>
     </row>
     <row r="481">
-      <c r="A481" s="12"/>
+      <c r="A481" s="13"/>
     </row>
     <row r="482">
-      <c r="A482" s="12"/>
+      <c r="A482" s="13"/>
     </row>
     <row r="483">
-      <c r="A483" s="12"/>
+      <c r="A483" s="13"/>
     </row>
     <row r="484">
-      <c r="A484" s="12"/>
+      <c r="A484" s="13"/>
     </row>
     <row r="485">
-      <c r="A485" s="12"/>
+      <c r="A485" s="13"/>
     </row>
     <row r="486">
-      <c r="A486" s="12"/>
+      <c r="A486" s="13"/>
     </row>
     <row r="487">
-      <c r="A487" s="12"/>
+      <c r="A487" s="13"/>
     </row>
     <row r="488">
-      <c r="A488" s="12"/>
+      <c r="A488" s="13"/>
     </row>
     <row r="489">
-      <c r="A489" s="12"/>
+      <c r="A489" s="13"/>
     </row>
     <row r="490">
-      <c r="A490" s="12"/>
+      <c r="A490" s="13"/>
     </row>
     <row r="491">
-      <c r="A491" s="12"/>
+      <c r="A491" s="13"/>
     </row>
     <row r="492">
-      <c r="A492" s="12"/>
+      <c r="A492" s="13"/>
     </row>
     <row r="493">
-      <c r="A493" s="12"/>
+      <c r="A493" s="13"/>
     </row>
     <row r="494">
-      <c r="A494" s="12"/>
+      <c r="A494" s="13"/>
     </row>
     <row r="495">
-      <c r="A495" s="12"/>
+      <c r="A495" s="13"/>
     </row>
     <row r="496">
-      <c r="A496" s="12"/>
+      <c r="A496" s="13"/>
     </row>
     <row r="497">
-      <c r="A497" s="12"/>
+      <c r="A497" s="13"/>
     </row>
     <row r="498">
-      <c r="A498" s="12"/>
+      <c r="A498" s="13"/>
     </row>
     <row r="499">
-      <c r="A499" s="12"/>
+      <c r="A499" s="13"/>
     </row>
     <row r="500">
-      <c r="A500" s="12"/>
+      <c r="A500" s="13"/>
     </row>
     <row r="501">
-      <c r="A501" s="12"/>
+      <c r="A501" s="13"/>
     </row>
     <row r="502">
-      <c r="A502" s="12"/>
+      <c r="A502" s="13"/>
     </row>
     <row r="503">
-      <c r="A503" s="12"/>
+      <c r="A503" s="13"/>
     </row>
     <row r="504">
-      <c r="A504" s="12"/>
+      <c r="A504" s="13"/>
     </row>
     <row r="505">
-      <c r="A505" s="12"/>
+      <c r="A505" s="13"/>
     </row>
     <row r="506">
-      <c r="A506" s="12"/>
+      <c r="A506" s="13"/>
     </row>
     <row r="507">
-      <c r="A507" s="12"/>
+      <c r="A507" s="13"/>
     </row>
     <row r="508">
-      <c r="A508" s="12"/>
+      <c r="A508" s="13"/>
     </row>
     <row r="509">
-      <c r="A509" s="12"/>
+      <c r="A509" s="13"/>
     </row>
     <row r="510">
-      <c r="A510" s="12"/>
+      <c r="A510" s="13"/>
     </row>
     <row r="511">
-      <c r="A511" s="12"/>
+      <c r="A511" s="13"/>
     </row>
     <row r="512">
-      <c r="A512" s="12"/>
+      <c r="A512" s="13"/>
     </row>
     <row r="513">
-      <c r="A513" s="12"/>
+      <c r="A513" s="13"/>
     </row>
     <row r="514">
-      <c r="A514" s="12"/>
+      <c r="A514" s="13"/>
     </row>
     <row r="515">
-      <c r="A515" s="12"/>
+      <c r="A515" s="13"/>
     </row>
     <row r="516">
-      <c r="A516" s="12"/>
+      <c r="A516" s="13"/>
     </row>
     <row r="517">
-      <c r="A517" s="12"/>
+      <c r="A517" s="13"/>
     </row>
     <row r="518">
-      <c r="A518" s="12"/>
+      <c r="A518" s="13"/>
     </row>
     <row r="519">
-      <c r="A519" s="12"/>
+      <c r="A519" s="13"/>
     </row>
     <row r="520">
-      <c r="A520" s="12"/>
+      <c r="A520" s="13"/>
     </row>
     <row r="521">
-      <c r="A521" s="12"/>
+      <c r="A521" s="13"/>
     </row>
     <row r="522">
-      <c r="A522" s="12"/>
+      <c r="A522" s="13"/>
     </row>
     <row r="523">
-      <c r="A523" s="12"/>
+      <c r="A523" s="13"/>
     </row>
     <row r="524">
-      <c r="A524" s="12"/>
+      <c r="A524" s="13"/>
     </row>
     <row r="525">
-      <c r="A525" s="12"/>
+      <c r="A525" s="13"/>
     </row>
     <row r="526">
-      <c r="A526" s="12"/>
+      <c r="A526" s="13"/>
     </row>
     <row r="527">
-      <c r="A527" s="12"/>
+      <c r="A527" s="13"/>
     </row>
     <row r="528">
-      <c r="A528" s="12"/>
+      <c r="A528" s="13"/>
     </row>
     <row r="529">
-      <c r="A529" s="12"/>
+      <c r="A529" s="13"/>
     </row>
     <row r="530">
-      <c r="A530" s="12"/>
+      <c r="A530" s="13"/>
     </row>
     <row r="531">
-      <c r="A531" s="12"/>
+      <c r="A531" s="13"/>
     </row>
     <row r="532">
-      <c r="A532" s="12"/>
+      <c r="A532" s="13"/>
     </row>
     <row r="533">
-      <c r="A533" s="12"/>
+      <c r="A533" s="13"/>
     </row>
     <row r="534">
-      <c r="A534" s="12"/>
+      <c r="A534" s="13"/>
     </row>
     <row r="535">
-      <c r="A535" s="12"/>
+      <c r="A535" s="13"/>
     </row>
     <row r="536">
-      <c r="A536" s="12"/>
+      <c r="A536" s="13"/>
     </row>
     <row r="537">
-      <c r="A537" s="12"/>
+      <c r="A537" s="13"/>
     </row>
     <row r="538">
-      <c r="A538" s="12"/>
+      <c r="A538" s="13"/>
     </row>
     <row r="539">
-      <c r="A539" s="12"/>
+      <c r="A539" s="13"/>
     </row>
     <row r="540">
-      <c r="A540" s="12"/>
+      <c r="A540" s="13"/>
     </row>
     <row r="541">
-      <c r="A541" s="12"/>
+      <c r="A541" s="13"/>
     </row>
     <row r="542">
-      <c r="A542" s="12"/>
+      <c r="A542" s="13"/>
     </row>
     <row r="543">
-      <c r="A543" s="12"/>
+      <c r="A543" s="13"/>
     </row>
     <row r="544">
-      <c r="A544" s="12"/>
+      <c r="A544" s="13"/>
     </row>
     <row r="545">
-      <c r="A545" s="12"/>
+      <c r="A545" s="13"/>
     </row>
     <row r="546">
-      <c r="A546" s="12"/>
+      <c r="A546" s="13"/>
     </row>
     <row r="547">
-      <c r="A547" s="12"/>
+      <c r="A547" s="13"/>
     </row>
     <row r="548">
-      <c r="A548" s="12"/>
+      <c r="A548" s="13"/>
     </row>
     <row r="549">
-      <c r="A549" s="12"/>
+      <c r="A549" s="13"/>
     </row>
     <row r="550">
-      <c r="A550" s="12"/>
+      <c r="A550" s="13"/>
     </row>
     <row r="551">
-      <c r="A551" s="12"/>
+      <c r="A551" s="13"/>
     </row>
     <row r="552">
-      <c r="A552" s="12"/>
+      <c r="A552" s="13"/>
     </row>
     <row r="553">
-      <c r="A553" s="12"/>
+      <c r="A553" s="13"/>
     </row>
     <row r="554">
-      <c r="A554" s="12"/>
+      <c r="A554" s="13"/>
     </row>
     <row r="555">
-      <c r="A555" s="12"/>
+      <c r="A555" s="13"/>
     </row>
     <row r="556">
-      <c r="A556" s="12"/>
+      <c r="A556" s="13"/>
     </row>
     <row r="557">
-      <c r="A557" s="12"/>
+      <c r="A557" s="13"/>
     </row>
     <row r="558">
-      <c r="A558" s="12"/>
+      <c r="A558" s="13"/>
     </row>
     <row r="559">
-      <c r="A559" s="12"/>
+      <c r="A559" s="13"/>
     </row>
     <row r="560">
-      <c r="A560" s="12"/>
+      <c r="A560" s="13"/>
     </row>
     <row r="561">
-      <c r="A561" s="12"/>
+      <c r="A561" s="13"/>
     </row>
     <row r="562">
-      <c r="A562" s="12"/>
+      <c r="A562" s="13"/>
     </row>
     <row r="563">
-      <c r="A563" s="12"/>
+      <c r="A563" s="13"/>
     </row>
     <row r="564">
-      <c r="A564" s="12"/>
+      <c r="A564" s="13"/>
     </row>
     <row r="565">
-      <c r="A565" s="12"/>
+      <c r="A565" s="13"/>
     </row>
     <row r="566">
-      <c r="A566" s="12"/>
+      <c r="A566" s="13"/>
     </row>
     <row r="567">
-      <c r="A567" s="12"/>
+      <c r="A567" s="13"/>
     </row>
     <row r="568">
-      <c r="A568" s="12"/>
+      <c r="A568" s="13"/>
     </row>
     <row r="569">
-      <c r="A569" s="12"/>
+      <c r="A569" s="13"/>
     </row>
     <row r="570">
-      <c r="A570" s="12"/>
+      <c r="A570" s="13"/>
     </row>
     <row r="571">
-      <c r="A571" s="12"/>
+      <c r="A571" s="13"/>
     </row>
     <row r="572">
-      <c r="A572" s="12"/>
+      <c r="A572" s="13"/>
     </row>
     <row r="573">
-      <c r="A573" s="12"/>
+      <c r="A573" s="13"/>
     </row>
     <row r="574">
-      <c r="A574" s="12"/>
+      <c r="A574" s="13"/>
     </row>
     <row r="575">
-      <c r="A575" s="12"/>
+      <c r="A575" s="13"/>
     </row>
     <row r="576">
-      <c r="A576" s="12"/>
+      <c r="A576" s="13"/>
     </row>
     <row r="577">
-      <c r="A577" s="12"/>
+      <c r="A577" s="13"/>
     </row>
     <row r="578">
-      <c r="A578" s="12"/>
+      <c r="A578" s="13"/>
     </row>
     <row r="579">
-      <c r="A579" s="12"/>
+      <c r="A579" s="13"/>
     </row>
     <row r="580">
-      <c r="A580" s="12"/>
+      <c r="A580" s="13"/>
     </row>
     <row r="581">
-      <c r="A581" s="12"/>
+      <c r="A581" s="13"/>
     </row>
     <row r="582">
-      <c r="A582" s="12"/>
+      <c r="A582" s="13"/>
     </row>
     <row r="583">
-      <c r="A583" s="12"/>
+      <c r="A583" s="13"/>
     </row>
     <row r="584">
-      <c r="A584" s="12"/>
+      <c r="A584" s="13"/>
     </row>
     <row r="585">
-      <c r="A585" s="12"/>
+      <c r="A585" s="13"/>
     </row>
     <row r="586">
-      <c r="A586" s="12"/>
+      <c r="A586" s="13"/>
     </row>
     <row r="587">
-      <c r="A587" s="12"/>
+      <c r="A587" s="13"/>
     </row>
     <row r="588">
-      <c r="A588" s="12"/>
+      <c r="A588" s="13"/>
     </row>
     <row r="589">
-      <c r="A589" s="12"/>
+      <c r="A589" s="13"/>
     </row>
     <row r="590">
-      <c r="A590" s="12"/>
+      <c r="A590" s="13"/>
     </row>
     <row r="591">
-      <c r="A591" s="12"/>
+      <c r="A591" s="13"/>
     </row>
     <row r="592">
-      <c r="A592" s="12"/>
+      <c r="A592" s="13"/>
     </row>
     <row r="593">
-      <c r="A593" s="12"/>
+      <c r="A593" s="13"/>
     </row>
     <row r="594">
-      <c r="A594" s="12"/>
+      <c r="A594" s="13"/>
     </row>
     <row r="595">
-      <c r="A595" s="12"/>
+      <c r="A595" s="13"/>
     </row>
     <row r="596">
-      <c r="A596" s="12"/>
+      <c r="A596" s="13"/>
     </row>
     <row r="597">
-      <c r="A597" s="12"/>
+      <c r="A597" s="13"/>
     </row>
     <row r="598">
-      <c r="A598" s="12"/>
+      <c r="A598" s="13"/>
     </row>
     <row r="599">
-      <c r="A599" s="12"/>
+      <c r="A599" s="13"/>
     </row>
     <row r="600">
-      <c r="A600" s="12"/>
+      <c r="A600" s="13"/>
     </row>
     <row r="601">
-      <c r="A601" s="12"/>
+      <c r="A601" s="13"/>
     </row>
     <row r="602">
-      <c r="A602" s="12"/>
+      <c r="A602" s="13"/>
     </row>
     <row r="603">
-      <c r="A603" s="12"/>
+      <c r="A603" s="13"/>
     </row>
     <row r="604">
-      <c r="A604" s="12"/>
+      <c r="A604" s="13"/>
     </row>
     <row r="605">
-      <c r="A605" s="12"/>
+      <c r="A605" s="13"/>
     </row>
     <row r="606">
-      <c r="A606" s="12"/>
+      <c r="A606" s="13"/>
     </row>
     <row r="607">
-      <c r="A607" s="12"/>
+      <c r="A607" s="13"/>
     </row>
     <row r="608">
-      <c r="A608" s="12"/>
+      <c r="A608" s="13"/>
     </row>
     <row r="609">
-      <c r="A609" s="12"/>
+      <c r="A609" s="13"/>
     </row>
     <row r="610">
-      <c r="A610" s="12"/>
+      <c r="A610" s="13"/>
     </row>
     <row r="611">
-      <c r="A611" s="12"/>
+      <c r="A611" s="13"/>
     </row>
     <row r="612">
-      <c r="A612" s="12"/>
+      <c r="A612" s="13"/>
     </row>
     <row r="613">
-      <c r="A613" s="12"/>
+      <c r="A613" s="13"/>
     </row>
     <row r="614">
-      <c r="A614" s="12"/>
+      <c r="A614" s="13"/>
     </row>
     <row r="615">
-      <c r="A615" s="12"/>
+      <c r="A615" s="13"/>
     </row>
     <row r="616">
-      <c r="A616" s="12"/>
+      <c r="A616" s="13"/>
     </row>
     <row r="617">
-      <c r="A617" s="12"/>
+      <c r="A617" s="13"/>
     </row>
     <row r="618">
-      <c r="A618" s="12"/>
+      <c r="A618" s="13"/>
     </row>
     <row r="619">
-      <c r="A619" s="12"/>
+      <c r="A619" s="13"/>
     </row>
     <row r="620">
-      <c r="A620" s="12"/>
+      <c r="A620" s="13"/>
     </row>
     <row r="621">
-      <c r="A621" s="12"/>
+      <c r="A621" s="13"/>
     </row>
     <row r="622">
-      <c r="A622" s="12"/>
+      <c r="A622" s="13"/>
     </row>
     <row r="623">
-      <c r="A623" s="12"/>
+      <c r="A623" s="13"/>
     </row>
     <row r="624">
-      <c r="A624" s="12"/>
+      <c r="A624" s="13"/>
     </row>
     <row r="625">
-      <c r="A625" s="12"/>
+      <c r="A625" s="13"/>
     </row>
     <row r="626">
-      <c r="A626" s="12"/>
+      <c r="A626" s="13"/>
     </row>
     <row r="627">
-      <c r="A627" s="12"/>
+      <c r="A627" s="13"/>
     </row>
     <row r="628">
-      <c r="A628" s="12"/>
+      <c r="A628" s="13"/>
     </row>
     <row r="629">
-      <c r="A629" s="12"/>
+      <c r="A629" s="13"/>
     </row>
     <row r="630">
-      <c r="A630" s="12"/>
+      <c r="A630" s="13"/>
     </row>
     <row r="631">
-      <c r="A631" s="12"/>
+      <c r="A631" s="13"/>
     </row>
     <row r="632">
-      <c r="A632" s="12"/>
+      <c r="A632" s="13"/>
     </row>
     <row r="633">
-      <c r="A633" s="12"/>
+      <c r="A633" s="13"/>
     </row>
     <row r="634">
-      <c r="A634" s="12"/>
+      <c r="A634" s="13"/>
     </row>
     <row r="635">
-      <c r="A635" s="12"/>
+      <c r="A635" s="13"/>
     </row>
     <row r="636">
-      <c r="A636" s="12"/>
+      <c r="A636" s="13"/>
     </row>
     <row r="637">
-      <c r="A637" s="12"/>
+      <c r="A637" s="13"/>
     </row>
     <row r="638">
-      <c r="A638" s="12"/>
+      <c r="A638" s="13"/>
     </row>
     <row r="639">
-      <c r="A639" s="12"/>
+      <c r="A639" s="13"/>
     </row>
     <row r="640">
-      <c r="A640" s="12"/>
+      <c r="A640" s="13"/>
     </row>
     <row r="641">
-      <c r="A641" s="12"/>
+      <c r="A641" s="13"/>
     </row>
     <row r="642">
-      <c r="A642" s="12"/>
+      <c r="A642" s="13"/>
     </row>
     <row r="643">
-      <c r="A643" s="12"/>
+      <c r="A643" s="13"/>
     </row>
     <row r="644">
-      <c r="A644" s="12"/>
+      <c r="A644" s="13"/>
     </row>
     <row r="645">
-      <c r="A645" s="12"/>
+      <c r="A645" s="13"/>
     </row>
     <row r="646">
-      <c r="A646" s="12"/>
+      <c r="A646" s="13"/>
     </row>
     <row r="647">
-      <c r="A647" s="12"/>
+      <c r="A647" s="13"/>
     </row>
     <row r="648">
-      <c r="A648" s="12"/>
+      <c r="A648" s="13"/>
     </row>
     <row r="649">
-      <c r="A649" s="12"/>
+      <c r="A649" s="13"/>
     </row>
     <row r="650">
-      <c r="A650" s="12"/>
+      <c r="A650" s="13"/>
     </row>
     <row r="651">
-      <c r="A651" s="12"/>
+      <c r="A651" s="13"/>
     </row>
     <row r="652">
-      <c r="A652" s="12"/>
+      <c r="A652" s="13"/>
     </row>
     <row r="653">
-      <c r="A653" s="12"/>
+      <c r="A653" s="13"/>
     </row>
     <row r="654">
-      <c r="A654" s="12"/>
+      <c r="A654" s="13"/>
     </row>
     <row r="655">
-      <c r="A655" s="12"/>
+      <c r="A655" s="13"/>
     </row>
     <row r="656">
-      <c r="A656" s="12"/>
+      <c r="A656" s="13"/>
     </row>
     <row r="657">
-      <c r="A657" s="12"/>
+      <c r="A657" s="13"/>
     </row>
     <row r="658">
-      <c r="A658" s="12"/>
+      <c r="A658" s="13"/>
     </row>
     <row r="659">
-      <c r="A659" s="12"/>
+      <c r="A659" s="13"/>
     </row>
     <row r="660">
-      <c r="A660" s="12"/>
+      <c r="A660" s="13"/>
     </row>
     <row r="661">
-      <c r="A661" s="12"/>
+      <c r="A661" s="13"/>
     </row>
     <row r="662">
-      <c r="A662" s="12"/>
+      <c r="A662" s="13"/>
     </row>
     <row r="663">
-      <c r="A663" s="12"/>
+      <c r="A663" s="13"/>
     </row>
     <row r="664">
-      <c r="A664" s="12"/>
+      <c r="A664" s="13"/>
     </row>
     <row r="665">
-      <c r="A665" s="12"/>
+      <c r="A665" s="13"/>
     </row>
     <row r="666">
-      <c r="A666" s="12"/>
+      <c r="A666" s="13"/>
     </row>
     <row r="667">
-      <c r="A667" s="12"/>
+      <c r="A667" s="13"/>
     </row>
     <row r="668">
-      <c r="A668" s="12"/>
+      <c r="A668" s="13"/>
     </row>
     <row r="669">
-      <c r="A669" s="12"/>
+      <c r="A669" s="13"/>
     </row>
     <row r="670">
-      <c r="A670" s="12"/>
+      <c r="A670" s="13"/>
     </row>
     <row r="671">
-      <c r="A671" s="12"/>
+      <c r="A671" s="13"/>
     </row>
     <row r="672">
-      <c r="A672" s="12"/>
+      <c r="A672" s="13"/>
     </row>
     <row r="673">
-      <c r="A673" s="12"/>
+      <c r="A673" s="13"/>
     </row>
     <row r="674">
-      <c r="A674" s="12"/>
+      <c r="A674" s="13"/>
     </row>
     <row r="675">
-      <c r="A675" s="12"/>
+      <c r="A675" s="13"/>
     </row>
     <row r="676">
-      <c r="A676" s="12"/>
+      <c r="A676" s="13"/>
     </row>
     <row r="677">
-      <c r="A677" s="12"/>
+      <c r="A677" s="13"/>
     </row>
     <row r="678">
-      <c r="A678" s="12"/>
+      <c r="A678" s="13"/>
     </row>
     <row r="679">
-      <c r="A679" s="12"/>
+      <c r="A679" s="13"/>
     </row>
     <row r="680">
-      <c r="A680" s="12"/>
+      <c r="A680" s="13"/>
     </row>
     <row r="681">
-      <c r="A681" s="12"/>
+      <c r="A681" s="13"/>
     </row>
     <row r="682">
-      <c r="A682" s="12"/>
+      <c r="A682" s="13"/>
     </row>
     <row r="683">
-      <c r="A683" s="12"/>
+      <c r="A683" s="13"/>
     </row>
     <row r="684">
-      <c r="A684" s="12"/>
+      <c r="A684" s="13"/>
     </row>
     <row r="685">
-      <c r="A685" s="12"/>
+      <c r="A685" s="13"/>
     </row>
     <row r="686">
-      <c r="A686" s="12"/>
+      <c r="A686" s="13"/>
     </row>
     <row r="687">
-      <c r="A687" s="12"/>
+      <c r="A687" s="13"/>
     </row>
     <row r="688">
-      <c r="A688" s="12"/>
+      <c r="A688" s="13"/>
     </row>
     <row r="689">
-      <c r="A689" s="12"/>
+      <c r="A689" s="13"/>
     </row>
     <row r="690">
-      <c r="A690" s="12"/>
+      <c r="A690" s="13"/>
     </row>
     <row r="691">
-      <c r="A691" s="12"/>
+      <c r="A691" s="13"/>
     </row>
     <row r="692">
-      <c r="A692" s="12"/>
+      <c r="A692" s="13"/>
     </row>
     <row r="693">
-      <c r="A693" s="12"/>
+      <c r="A693" s="13"/>
     </row>
     <row r="694">
-      <c r="A694" s="12"/>
+      <c r="A694" s="13"/>
     </row>
     <row r="695">
-      <c r="A695" s="12"/>
+      <c r="A695" s="13"/>
     </row>
     <row r="696">
-      <c r="A696" s="12"/>
+      <c r="A696" s="13"/>
     </row>
     <row r="697">
-      <c r="A697" s="12"/>
+      <c r="A697" s="13"/>
     </row>
     <row r="698">
-      <c r="A698" s="12"/>
+      <c r="A698" s="13"/>
     </row>
     <row r="699">
-      <c r="A699" s="12"/>
+      <c r="A699" s="13"/>
     </row>
     <row r="700">
-      <c r="A700" s="12"/>
+      <c r="A700" s="13"/>
     </row>
     <row r="701">
-      <c r="A701" s="12"/>
+      <c r="A701" s="13"/>
     </row>
     <row r="702">
-      <c r="A702" s="12"/>
+      <c r="A702" s="13"/>
     </row>
     <row r="703">
-      <c r="A703" s="12"/>
+      <c r="A703" s="13"/>
     </row>
     <row r="704">
-      <c r="A704" s="12"/>
+      <c r="A704" s="13"/>
     </row>
     <row r="705">
-      <c r="A705" s="12"/>
+      <c r="A705" s="13"/>
     </row>
     <row r="706">
-      <c r="A706" s="12"/>
+      <c r="A706" s="13"/>
     </row>
     <row r="707">
-      <c r="A707" s="12"/>
+      <c r="A707" s="13"/>
     </row>
     <row r="708">
-      <c r="A708" s="12"/>
+      <c r="A708" s="13"/>
     </row>
     <row r="709">
-      <c r="A709" s="12"/>
+      <c r="A709" s="13"/>
     </row>
     <row r="710">
-      <c r="A710" s="12"/>
+      <c r="A710" s="13"/>
     </row>
     <row r="711">
-      <c r="A711" s="12"/>
+      <c r="A711" s="13"/>
     </row>
     <row r="712">
-      <c r="A712" s="12"/>
+      <c r="A712" s="13"/>
     </row>
     <row r="713">
-      <c r="A713" s="12"/>
+      <c r="A713" s="13"/>
     </row>
     <row r="714">
-      <c r="A714" s="12"/>
+      <c r="A714" s="13"/>
     </row>
     <row r="715">
-      <c r="A715" s="12"/>
+      <c r="A715" s="13"/>
     </row>
     <row r="716">
-      <c r="A716" s="12"/>
+      <c r="A716" s="13"/>
     </row>
     <row r="717">
-      <c r="A717" s="12"/>
+      <c r="A717" s="13"/>
     </row>
     <row r="718">
-      <c r="A718" s="12"/>
+      <c r="A718" s="13"/>
     </row>
     <row r="719">
-      <c r="A719" s="12"/>
+      <c r="A719" s="13"/>
     </row>
     <row r="720">
-      <c r="A720" s="12"/>
+      <c r="A720" s="13"/>
     </row>
     <row r="721">
-      <c r="A721" s="12"/>
+      <c r="A721" s="13"/>
     </row>
     <row r="722">
-      <c r="A722" s="12"/>
+      <c r="A722" s="13"/>
     </row>
     <row r="723">
-      <c r="A723" s="12"/>
+      <c r="A723" s="13"/>
     </row>
     <row r="724">
-      <c r="A724" s="12"/>
+      <c r="A724" s="13"/>
     </row>
     <row r="725">
-      <c r="A725" s="12"/>
+      <c r="A725" s="13"/>
     </row>
     <row r="726">
-      <c r="A726" s="12"/>
+      <c r="A726" s="13"/>
     </row>
     <row r="727">
-      <c r="A727" s="12"/>
+      <c r="A727" s="13"/>
     </row>
     <row r="728">
-      <c r="A728" s="12"/>
+      <c r="A728" s="13"/>
     </row>
     <row r="729">
-      <c r="A729" s="12"/>
+      <c r="A729" s="13"/>
     </row>
     <row r="730">
-      <c r="A730" s="12"/>
+      <c r="A730" s="13"/>
     </row>
     <row r="731">
-      <c r="A731" s="12"/>
+      <c r="A731" s="13"/>
     </row>
     <row r="732">
-      <c r="A732" s="12"/>
+      <c r="A732" s="13"/>
     </row>
     <row r="733">
-      <c r="A733" s="12"/>
+      <c r="A733" s="13"/>
     </row>
     <row r="734">
-      <c r="A734" s="12"/>
+      <c r="A734" s="13"/>
     </row>
     <row r="735">
-      <c r="A735" s="12"/>
+      <c r="A735" s="13"/>
     </row>
     <row r="736">
-      <c r="A736" s="12"/>
+      <c r="A736" s="13"/>
     </row>
     <row r="737">
-      <c r="A737" s="12"/>
+      <c r="A737" s="13"/>
     </row>
     <row r="738">
-      <c r="A738" s="12"/>
+      <c r="A738" s="13"/>
     </row>
     <row r="739">
-      <c r="A739" s="12"/>
+      <c r="A739" s="13"/>
     </row>
     <row r="740">
-      <c r="A740" s="12"/>
+      <c r="A740" s="13"/>
     </row>
     <row r="741">
-      <c r="A741" s="12"/>
+      <c r="A741" s="13"/>
     </row>
     <row r="742">
-      <c r="A742" s="12"/>
+      <c r="A742" s="13"/>
     </row>
     <row r="743">
-      <c r="A743" s="12"/>
+      <c r="A743" s="13"/>
     </row>
     <row r="744">
-      <c r="A744" s="12"/>
+      <c r="A744" s="13"/>
     </row>
     <row r="745">
-      <c r="A745" s="12"/>
+      <c r="A745" s="13"/>
     </row>
     <row r="746">
-      <c r="A746" s="12"/>
+      <c r="A746" s="13"/>
     </row>
     <row r="747">
-      <c r="A747" s="12"/>
+      <c r="A747" s="13"/>
     </row>
     <row r="748">
-      <c r="A748" s="12"/>
+      <c r="A748" s="13"/>
     </row>
     <row r="749">
-      <c r="A749" s="12"/>
+      <c r="A749" s="13"/>
     </row>
     <row r="750">
-      <c r="A750" s="12"/>
+      <c r="A750" s="13"/>
     </row>
     <row r="751">
-      <c r="A751" s="12"/>
+      <c r="A751" s="13"/>
     </row>
     <row r="752">
-      <c r="A752" s="12"/>
+      <c r="A752" s="13"/>
     </row>
     <row r="753">
-      <c r="A753" s="12"/>
+      <c r="A753" s="13"/>
     </row>
     <row r="754">
-      <c r="A754" s="12"/>
+      <c r="A754" s="13"/>
     </row>
     <row r="755">
-      <c r="A755" s="12"/>
+      <c r="A755" s="13"/>
     </row>
     <row r="756">
-      <c r="A756" s="12"/>
+      <c r="A756" s="13"/>
     </row>
     <row r="757">
-      <c r="A757" s="12"/>
+      <c r="A757" s="13"/>
     </row>
     <row r="758">
-      <c r="A758" s="12"/>
+      <c r="A758" s="13"/>
     </row>
     <row r="759">
-      <c r="A759" s="12"/>
+      <c r="A759" s="13"/>
     </row>
     <row r="760">
-      <c r="A760" s="12"/>
+      <c r="A760" s="13"/>
     </row>
     <row r="761">
-      <c r="A761" s="12"/>
+      <c r="A761" s="13"/>
     </row>
     <row r="762">
-      <c r="A762" s="12"/>
+      <c r="A762" s="13"/>
     </row>
     <row r="763">
-      <c r="A763" s="12"/>
+      <c r="A763" s="13"/>
     </row>
     <row r="764">
-      <c r="A764" s="12"/>
+      <c r="A764" s="13"/>
     </row>
     <row r="765">
-      <c r="A765" s="12"/>
+      <c r="A765" s="13"/>
     </row>
     <row r="766">
-      <c r="A766" s="12"/>
+      <c r="A766" s="13"/>
     </row>
     <row r="767">
-      <c r="A767" s="12"/>
+      <c r="A767" s="13"/>
     </row>
     <row r="768">
-      <c r="A768" s="12"/>
+      <c r="A768" s="13"/>
     </row>
     <row r="769">
-      <c r="A769" s="12"/>
+      <c r="A769" s="13"/>
     </row>
     <row r="770">
-      <c r="A770" s="12"/>
+      <c r="A770" s="13"/>
     </row>
     <row r="771">
-      <c r="A771" s="12"/>
+      <c r="A771" s="13"/>
     </row>
     <row r="772">
-      <c r="A772" s="12"/>
+      <c r="A772" s="13"/>
     </row>
     <row r="773">
-      <c r="A773" s="12"/>
+      <c r="A773" s="13"/>
     </row>
     <row r="774">
-      <c r="A774" s="12"/>
+      <c r="A774" s="13"/>
     </row>
     <row r="775">
-      <c r="A775" s="12"/>
+      <c r="A775" s="13"/>
     </row>
     <row r="776">
-      <c r="A776" s="12"/>
+      <c r="A776" s="13"/>
     </row>
     <row r="777">
-      <c r="A777" s="12"/>
+      <c r="A777" s="13"/>
     </row>
     <row r="778">
-      <c r="A778" s="12"/>
+      <c r="A778" s="13"/>
     </row>
     <row r="779">
-      <c r="A779" s="12"/>
+      <c r="A779" s="13"/>
     </row>
     <row r="780">
-      <c r="A780" s="12"/>
+      <c r="A780" s="13"/>
     </row>
     <row r="781">
-      <c r="A781" s="12"/>
+      <c r="A781" s="13"/>
     </row>
     <row r="782">
-      <c r="A782" s="12"/>
+      <c r="A782" s="13"/>
     </row>
     <row r="783">
-      <c r="A783" s="12"/>
+      <c r="A783" s="13"/>
     </row>
     <row r="784">
-      <c r="A784" s="12"/>
+      <c r="A784" s="13"/>
     </row>
     <row r="785">
-      <c r="A785" s="12"/>
+      <c r="A785" s="13"/>
     </row>
     <row r="786">
-      <c r="A786" s="12"/>
+      <c r="A786" s="13"/>
     </row>
     <row r="787">
-      <c r="A787" s="12"/>
+      <c r="A787" s="13"/>
     </row>
     <row r="788">
-      <c r="A788" s="12"/>
+      <c r="A788" s="13"/>
     </row>
     <row r="789">
-      <c r="A789" s="12"/>
+      <c r="A789" s="13"/>
     </row>
     <row r="790">
-      <c r="A790" s="12"/>
+      <c r="A790" s="13"/>
     </row>
     <row r="791">
-      <c r="A791" s="12"/>
+      <c r="A791" s="13"/>
     </row>
     <row r="792">
-      <c r="A792" s="12"/>
+      <c r="A792" s="13"/>
     </row>
     <row r="793">
-      <c r="A793" s="12"/>
+      <c r="A793" s="13"/>
     </row>
     <row r="794">
-      <c r="A794" s="12"/>
+      <c r="A794" s="13"/>
     </row>
     <row r="795">
-      <c r="A795" s="12"/>
+      <c r="A795" s="13"/>
     </row>
     <row r="796">
-      <c r="A796" s="12"/>
+      <c r="A796" s="13"/>
     </row>
     <row r="797">
-      <c r="A797" s="12"/>
+      <c r="A797" s="13"/>
     </row>
     <row r="798">
-      <c r="A798" s="12"/>
+      <c r="A798" s="13"/>
     </row>
     <row r="799">
-      <c r="A799" s="12"/>
+      <c r="A799" s="13"/>
     </row>
     <row r="800">
-      <c r="A800" s="12"/>
+      <c r="A800" s="13"/>
     </row>
     <row r="801">
-      <c r="A801" s="12"/>
+      <c r="A801" s="13"/>
     </row>
     <row r="802">
-      <c r="A802" s="12"/>
+      <c r="A802" s="13"/>
     </row>
     <row r="803">
-      <c r="A803" s="12"/>
+      <c r="A803" s="13"/>
     </row>
     <row r="804">
-      <c r="A804" s="12"/>
+      <c r="A804" s="13"/>
     </row>
     <row r="805">
-      <c r="A805" s="12"/>
+      <c r="A805" s="13"/>
     </row>
     <row r="806">
-      <c r="A806" s="12"/>
+      <c r="A806" s="13"/>
     </row>
     <row r="807">
-      <c r="A807" s="12"/>
+      <c r="A807" s="13"/>
     </row>
     <row r="808">
-      <c r="A808" s="12"/>
+      <c r="A808" s="13"/>
     </row>
     <row r="809">
-      <c r="A809" s="12"/>
+      <c r="A809" s="13"/>
     </row>
     <row r="810">
-      <c r="A810" s="12"/>
+      <c r="A810" s="13"/>
     </row>
     <row r="811">
-      <c r="A811" s="12"/>
+      <c r="A811" s="13"/>
     </row>
     <row r="812">
-      <c r="A812" s="12"/>
+      <c r="A812" s="13"/>
     </row>
     <row r="813">
-      <c r="A813" s="12"/>
+      <c r="A813" s="13"/>
     </row>
     <row r="814">
-      <c r="A814" s="12"/>
+      <c r="A814" s="13"/>
     </row>
     <row r="815">
-      <c r="A815" s="12"/>
+      <c r="A815" s="13"/>
     </row>
     <row r="816">
-      <c r="A816" s="12"/>
+      <c r="A816" s="13"/>
     </row>
     <row r="817">
-      <c r="A817" s="12"/>
+      <c r="A817" s="13"/>
     </row>
     <row r="818">
-      <c r="A818" s="12"/>
+      <c r="A818" s="13"/>
     </row>
     <row r="819">
-      <c r="A819" s="12"/>
+      <c r="A819" s="13"/>
     </row>
     <row r="820">
-      <c r="A820" s="12"/>
+      <c r="A820" s="13"/>
     </row>
     <row r="821">
-      <c r="A821" s="12"/>
+      <c r="A821" s="13"/>
     </row>
     <row r="822">
-      <c r="A822" s="12"/>
+      <c r="A822" s="13"/>
     </row>
     <row r="823">
-      <c r="A823" s="12"/>
+      <c r="A823" s="13"/>
     </row>
     <row r="824">
-      <c r="A824" s="12"/>
+      <c r="A824" s="13"/>
     </row>
     <row r="825">
-      <c r="A825" s="12"/>
+      <c r="A825" s="13"/>
     </row>
     <row r="826">
-      <c r="A826" s="12"/>
+      <c r="A826" s="13"/>
     </row>
     <row r="827">
-      <c r="A827" s="12"/>
+      <c r="A827" s="13"/>
     </row>
     <row r="828">
-      <c r="A828" s="12"/>
+      <c r="A828" s="13"/>
     </row>
     <row r="829">
-      <c r="A829" s="12"/>
+      <c r="A829" s="13"/>
     </row>
     <row r="830">
-      <c r="A830" s="12"/>
+      <c r="A830" s="13"/>
     </row>
     <row r="831">
-      <c r="A831" s="12"/>
+      <c r="A831" s="13"/>
     </row>
     <row r="832">
-      <c r="A832" s="12"/>
+      <c r="A832" s="13"/>
     </row>
     <row r="833">
-      <c r="A833" s="12"/>
+      <c r="A833" s="13"/>
     </row>
     <row r="834">
-      <c r="A834" s="12"/>
+      <c r="A834" s="13"/>
     </row>
     <row r="835">
-      <c r="A835" s="12"/>
+      <c r="A835" s="13"/>
     </row>
     <row r="836">
-      <c r="A836" s="12"/>
+      <c r="A836" s="13"/>
     </row>
     <row r="837">
-      <c r="A837" s="12"/>
+      <c r="A837" s="13"/>
     </row>
     <row r="838">
-      <c r="A838" s="12"/>
+      <c r="A838" s="13"/>
     </row>
     <row r="839">
-      <c r="A839" s="12"/>
+      <c r="A839" s="13"/>
     </row>
     <row r="840">
-      <c r="A840" s="12"/>
+      <c r="A840" s="13"/>
     </row>
     <row r="841">
-      <c r="A841" s="12"/>
+      <c r="A841" s="13"/>
     </row>
     <row r="842">
-      <c r="A842" s="12"/>
+      <c r="A842" s="13"/>
     </row>
     <row r="843">
-      <c r="A843" s="12"/>
+      <c r="A843" s="13"/>
     </row>
     <row r="844">
-      <c r="A844" s="12"/>
+      <c r="A844" s="13"/>
     </row>
     <row r="845">
-      <c r="A845" s="12"/>
+      <c r="A845" s="13"/>
     </row>
     <row r="846">
-      <c r="A846" s="12"/>
+      <c r="A846" s="13"/>
     </row>
     <row r="847">
-      <c r="A847" s="12"/>
+      <c r="A847" s="13"/>
     </row>
     <row r="848">
-      <c r="A848" s="12"/>
+      <c r="A848" s="13"/>
     </row>
     <row r="849">
-      <c r="A849" s="12"/>
+      <c r="A849" s="13"/>
     </row>
     <row r="850">
-      <c r="A850" s="12"/>
+      <c r="A850" s="13"/>
     </row>
     <row r="851">
-      <c r="A851" s="12"/>
+      <c r="A851" s="13"/>
     </row>
     <row r="852">
-      <c r="A852" s="12"/>
+      <c r="A852" s="13"/>
     </row>
     <row r="853">
-      <c r="A853" s="12"/>
+      <c r="A853" s="13"/>
     </row>
     <row r="854">
-      <c r="A854" s="12"/>
+      <c r="A854" s="13"/>
     </row>
     <row r="855">
-      <c r="A855" s="12"/>
+      <c r="A855" s="13"/>
     </row>
     <row r="856">
-      <c r="A856" s="12"/>
+      <c r="A856" s="13"/>
     </row>
     <row r="857">
-      <c r="A857" s="12"/>
+      <c r="A857" s="13"/>
     </row>
     <row r="858">
-      <c r="A858" s="12"/>
+      <c r="A858" s="13"/>
     </row>
     <row r="859">
-      <c r="A859" s="12"/>
+      <c r="A859" s="13"/>
     </row>
     <row r="860">
-      <c r="A860" s="12"/>
+      <c r="A860" s="13"/>
     </row>
     <row r="861">
-      <c r="A861" s="12"/>
+      <c r="A861" s="13"/>
     </row>
     <row r="862">
-      <c r="A862" s="12"/>
+      <c r="A862" s="13"/>
     </row>
     <row r="863">
-      <c r="A863" s="12"/>
+      <c r="A863" s="13"/>
     </row>
     <row r="864">
-      <c r="A864" s="12"/>
+      <c r="A864" s="13"/>
     </row>
     <row r="865">
-      <c r="A865" s="12"/>
+      <c r="A865" s="13"/>
     </row>
     <row r="866">
-      <c r="A866" s="12"/>
+      <c r="A866" s="13"/>
     </row>
     <row r="867">
-      <c r="A867" s="12"/>
+      <c r="A867" s="13"/>
     </row>
     <row r="868">
-      <c r="A868" s="12"/>
+      <c r="A868" s="13"/>
     </row>
     <row r="869">
-      <c r="A869" s="12"/>
+      <c r="A869" s="13"/>
     </row>
     <row r="870">
-      <c r="A870" s="12"/>
+      <c r="A870" s="13"/>
     </row>
     <row r="871">
-      <c r="A871" s="12"/>
+      <c r="A871" s="13"/>
     </row>
     <row r="872">
-      <c r="A872" s="12"/>
+      <c r="A872" s="13"/>
     </row>
     <row r="873">
-      <c r="A873" s="12"/>
+      <c r="A873" s="13"/>
     </row>
     <row r="874">
-      <c r="A874" s="12"/>
+      <c r="A874" s="13"/>
     </row>
     <row r="875">
-      <c r="A875" s="12"/>
+      <c r="A875" s="13"/>
     </row>
     <row r="876">
-      <c r="A876" s="12"/>
+      <c r="A876" s="13"/>
     </row>
     <row r="877">
-      <c r="A877" s="12"/>
+      <c r="A877" s="13"/>
     </row>
     <row r="878">
-      <c r="A878" s="12"/>
+      <c r="A878" s="13"/>
     </row>
     <row r="879">
-      <c r="A879" s="12"/>
+      <c r="A879" s="13"/>
     </row>
     <row r="880">
-      <c r="A880" s="12"/>
+      <c r="A880" s="13"/>
     </row>
     <row r="881">
-      <c r="A881" s="12"/>
+      <c r="A881" s="13"/>
     </row>
     <row r="882">
-      <c r="A882" s="12"/>
+      <c r="A882" s="13"/>
     </row>
     <row r="883">
-      <c r="A883" s="12"/>
+      <c r="A883" s="13"/>
     </row>
     <row r="884">
-      <c r="A884" s="12"/>
+      <c r="A884" s="13"/>
     </row>
     <row r="885">
-      <c r="A885" s="12"/>
+      <c r="A885" s="13"/>
     </row>
     <row r="886">
-      <c r="A886" s="12"/>
+      <c r="A886" s="13"/>
     </row>
     <row r="887">
-      <c r="A887" s="12"/>
+      <c r="A887" s="13"/>
     </row>
     <row r="888">
-      <c r="A888" s="12"/>
+      <c r="A888" s="13"/>
     </row>
     <row r="889">
-      <c r="A889" s="12"/>
+      <c r="A889" s="13"/>
     </row>
     <row r="890">
-      <c r="A890" s="12"/>
+      <c r="A890" s="13"/>
     </row>
     <row r="891">
-      <c r="A891" s="12"/>
+      <c r="A891" s="13"/>
     </row>
     <row r="892">
-      <c r="A892" s="12"/>
+      <c r="A892" s="13"/>
     </row>
     <row r="893">
-      <c r="A893" s="12"/>
+      <c r="A893" s="13"/>
     </row>
     <row r="894">
-      <c r="A894" s="12"/>
+      <c r="A894" s="13"/>
     </row>
     <row r="895">
-      <c r="A895" s="12"/>
+      <c r="A895" s="13"/>
     </row>
     <row r="896">
-      <c r="A896" s="12"/>
+      <c r="A896" s="13"/>
     </row>
     <row r="897">
-      <c r="A897" s="12"/>
+      <c r="A897" s="13"/>
     </row>
     <row r="898">
-      <c r="A898" s="12"/>
+      <c r="A898" s="13"/>
     </row>
     <row r="899">
-      <c r="A899" s="12"/>
+      <c r="A899" s="13"/>
     </row>
     <row r="900">
-      <c r="A900" s="12"/>
+      <c r="A900" s="13"/>
     </row>
     <row r="901">
-      <c r="A901" s="12"/>
+      <c r="A901" s="13"/>
     </row>
     <row r="902">
-      <c r="A902" s="12"/>
+      <c r="A902" s="13"/>
     </row>
     <row r="903">
-      <c r="A903" s="12"/>
+      <c r="A903" s="13"/>
     </row>
     <row r="904">
-      <c r="A904" s="12"/>
+      <c r="A904" s="13"/>
     </row>
     <row r="905">
-      <c r="A905" s="12"/>
+      <c r="A905" s="13"/>
     </row>
     <row r="906">
-      <c r="A906" s="12"/>
+      <c r="A906" s="13"/>
     </row>
     <row r="907">
-      <c r="A907" s="12"/>
+      <c r="A907" s="13"/>
     </row>
     <row r="908">
-      <c r="A908" s="12"/>
+      <c r="A908" s="13"/>
     </row>
     <row r="909">
-      <c r="A909" s="12"/>
+      <c r="A909" s="13"/>
     </row>
     <row r="910">
-      <c r="A910" s="12"/>
+      <c r="A910" s="13"/>
     </row>
     <row r="911">
-      <c r="A911" s="12"/>
+      <c r="A911" s="13"/>
     </row>
     <row r="912">
-      <c r="A912" s="12"/>
+      <c r="A912" s="13"/>
     </row>
     <row r="913">
-      <c r="A913" s="12"/>
+      <c r="A913" s="13"/>
     </row>
     <row r="914">
-      <c r="A914" s="12"/>
+      <c r="A914" s="13"/>
     </row>
     <row r="915">
-      <c r="A915" s="12"/>
+      <c r="A915" s="13"/>
     </row>
     <row r="916">
-      <c r="A916" s="12"/>
+      <c r="A916" s="13"/>
     </row>
     <row r="917">
-      <c r="A917" s="12"/>
+      <c r="A917" s="13"/>
     </row>
     <row r="918">
-      <c r="A918" s="12"/>
+      <c r="A918" s="13"/>
     </row>
     <row r="919">
-      <c r="A919" s="12"/>
+      <c r="A919" s="13"/>
     </row>
     <row r="920">
-      <c r="A920" s="12"/>
+      <c r="A920" s="13"/>
     </row>
     <row r="921">
-      <c r="A921" s="12"/>
+      <c r="A921" s="13"/>
     </row>
     <row r="922">
-      <c r="A922" s="12"/>
+      <c r="A922" s="13"/>
     </row>
     <row r="923">
-      <c r="A923" s="12"/>
+      <c r="A923" s="13"/>
     </row>
     <row r="924">
-      <c r="A924" s="12"/>
+      <c r="A924" s="13"/>
     </row>
     <row r="925">
-      <c r="A925" s="12"/>
+      <c r="A925" s="13"/>
     </row>
     <row r="926">
-      <c r="A926" s="12"/>
+      <c r="A926" s="13"/>
     </row>
     <row r="927">
-      <c r="A927" s="12"/>
+      <c r="A927" s="13"/>
     </row>
     <row r="928">
-      <c r="A928" s="12"/>
+      <c r="A928" s="13"/>
     </row>
     <row r="929">
-      <c r="A929" s="12"/>
+      <c r="A929" s="13"/>
     </row>
     <row r="930">
-      <c r="A930" s="12"/>
+      <c r="A930" s="13"/>
     </row>
     <row r="931">
-      <c r="A931" s="12"/>
+      <c r="A931" s="13"/>
     </row>
     <row r="932">
-      <c r="A932" s="12"/>
+      <c r="A932" s="13"/>
     </row>
     <row r="933">
-      <c r="A933" s="12"/>
+      <c r="A933" s="13"/>
     </row>
     <row r="934">
-      <c r="A934" s="12"/>
+      <c r="A934" s="13"/>
     </row>
     <row r="935">
-      <c r="A935" s="12"/>
+      <c r="A935" s="13"/>
     </row>
     <row r="936">
-      <c r="A936" s="12"/>
+      <c r="A936" s="13"/>
     </row>
     <row r="937">
-      <c r="A937" s="12"/>
+      <c r="A937" s="13"/>
     </row>
     <row r="938">
-      <c r="A938" s="12"/>
+      <c r="A938" s="13"/>
     </row>
     <row r="939">
-      <c r="A939" s="12"/>
+      <c r="A939" s="13"/>
     </row>
     <row r="940">
-      <c r="A940" s="12"/>
+      <c r="A940" s="13"/>
     </row>
     <row r="941">
-      <c r="A941" s="12"/>
+      <c r="A941" s="13"/>
     </row>
     <row r="942">
-      <c r="A942" s="12"/>
+      <c r="A942" s="13"/>
     </row>
     <row r="943">
-      <c r="A943" s="12"/>
+      <c r="A943" s="13"/>
     </row>
     <row r="944">
-      <c r="A944" s="12"/>
+      <c r="A944" s="13"/>
     </row>
     <row r="945">
-      <c r="A945" s="12"/>
+      <c r="A945" s="13"/>
     </row>
     <row r="946">
-      <c r="A946" s="12"/>
+      <c r="A946" s="13"/>
     </row>
     <row r="947">
-      <c r="A947" s="12"/>
+      <c r="A947" s="13"/>
     </row>
     <row r="948">
-      <c r="A948" s="12"/>
+      <c r="A948" s="13"/>
     </row>
     <row r="949">
-      <c r="A949" s="12"/>
+      <c r="A949" s="13"/>
     </row>
     <row r="950">
-      <c r="A950" s="12"/>
+      <c r="A950" s="13"/>
     </row>
     <row r="951">
-      <c r="A951" s="12"/>
+      <c r="A951" s="13"/>
     </row>
     <row r="952">
-      <c r="A952" s="12"/>
+      <c r="A952" s="13"/>
     </row>
     <row r="953">
-      <c r="A953" s="12"/>
+      <c r="A953" s="13"/>
     </row>
     <row r="954">
-      <c r="A954" s="12"/>
+      <c r="A954" s="13"/>
     </row>
     <row r="955">
-      <c r="A955" s="12"/>
+      <c r="A955" s="13"/>
     </row>
     <row r="956">
-      <c r="A956" s="12"/>
+      <c r="A956" s="13"/>
     </row>
     <row r="957">
-      <c r="A957" s="12"/>
+      <c r="A957" s="13"/>
     </row>
     <row r="958">
-      <c r="A958" s="12"/>
+      <c r="A958" s="13"/>
     </row>
     <row r="959">
-      <c r="A959" s="12"/>
+      <c r="A959" s="13"/>
     </row>
     <row r="960">
-      <c r="A960" s="12"/>
+      <c r="A960" s="13"/>
     </row>
     <row r="961">
-      <c r="A961" s="12"/>
+      <c r="A961" s="13"/>
     </row>
     <row r="962">
-      <c r="A962" s="12"/>
+      <c r="A962" s="13"/>
     </row>
     <row r="963">
-      <c r="A963" s="12"/>
+      <c r="A963" s="13"/>
     </row>
     <row r="964">
-      <c r="A964" s="12"/>
+      <c r="A964" s="13"/>
     </row>
     <row r="965">
-      <c r="A965" s="12"/>
+      <c r="A965" s="13"/>
     </row>
     <row r="966">
-      <c r="A966" s="12"/>
+      <c r="A966" s="13"/>
     </row>
     <row r="967">
-      <c r="A967" s="12"/>
+      <c r="A967" s="13"/>
     </row>
     <row r="968">
-      <c r="A968" s="12"/>
+      <c r="A968" s="13"/>
     </row>
     <row r="969">
-      <c r="A969" s="12"/>
+      <c r="A969" s="13"/>
     </row>
     <row r="970">
-      <c r="A970" s="12"/>
+      <c r="A970" s="13"/>
     </row>
     <row r="971">
-      <c r="A971" s="12"/>
+      <c r="A971" s="13"/>
     </row>
     <row r="972">
-      <c r="A972" s="12"/>
+      <c r="A972" s="13"/>
     </row>
     <row r="973">
-      <c r="A973" s="12"/>
+      <c r="A973" s="13"/>
     </row>
     <row r="974">
-      <c r="A974" s="12"/>
+      <c r="A974" s="13"/>
     </row>
     <row r="975">
-      <c r="A975" s="12"/>
+      <c r="A975" s="13"/>
     </row>
     <row r="976">
-      <c r="A976" s="12"/>
+      <c r="A976" s="13"/>
     </row>
     <row r="977">
-      <c r="A977" s="12"/>
+      <c r="A977" s="13"/>
     </row>
     <row r="978">
-      <c r="A978" s="12"/>
+      <c r="A978" s="13"/>
     </row>
     <row r="979">
-      <c r="A979" s="12"/>
+      <c r="A979" s="13"/>
     </row>
     <row r="980">
-      <c r="A980" s="12"/>
+      <c r="A980" s="13"/>
     </row>
     <row r="981">
-      <c r="A981" s="12"/>
+      <c r="A981" s="13"/>
     </row>
     <row r="982">
-      <c r="A982" s="12"/>
+      <c r="A982" s="13"/>
     </row>
     <row r="983">
-      <c r="A983" s="12"/>
+      <c r="A983" s="13"/>
     </row>
     <row r="984">
-      <c r="A984" s="12"/>
+      <c r="A984" s="13"/>
     </row>
     <row r="985">
-      <c r="A985" s="12"/>
+      <c r="A985" s="13"/>
     </row>
     <row r="986">
-      <c r="A986" s="12"/>
+      <c r="A986" s="13"/>
     </row>
     <row r="987">
-      <c r="A987" s="12"/>
+      <c r="A987" s="13"/>
     </row>
     <row r="988">
-      <c r="A988" s="12"/>
+      <c r="A988" s="13"/>
     </row>
     <row r="989">
-      <c r="A989" s="12"/>
+      <c r="A989" s="13"/>
     </row>
     <row r="990">
-      <c r="A990" s="12"/>
+      <c r="A990" s="13"/>
     </row>
     <row r="991">
-      <c r="A991" s="12"/>
+      <c r="A991" s="13"/>
     </row>
     <row r="992">
-      <c r="A992" s="12"/>
+      <c r="A992" s="13"/>
     </row>
     <row r="993">
-      <c r="A993" s="12"/>
+      <c r="A993" s="13"/>
     </row>
     <row r="994">
-      <c r="A994" s="12"/>
+      <c r="A994" s="13"/>
     </row>
     <row r="995">
-      <c r="A995" s="12"/>
+      <c r="A995" s="13"/>
     </row>
     <row r="996">
-      <c r="A996" s="12"/>
+      <c r="A996" s="13"/>
     </row>
     <row r="997">
-      <c r="A997" s="12"/>
+      <c r="A997" s="13"/>
     </row>
     <row r="998">
-      <c r="A998" s="12"/>
+      <c r="A998" s="13"/>
     </row>
     <row r="999">
-      <c r="A999" s="12"/>
+      <c r="A999" s="13"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="12"/>
+      <c r="A1000" s="13"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="12"/>
+      <c r="A1001" s="13"/>
     </row>
     <row r="1002">
-      <c r="A1002" s="12"/>
+      <c r="A1002" s="13"/>
     </row>
     <row r="1003">
-      <c r="A1003" s="12"/>
+      <c r="A1003" s="13"/>
     </row>
     <row r="1004">
-      <c r="A1004" s="12"/>
+      <c r="A1004" s="13"/>
     </row>
     <row r="1005">
-      <c r="A1005" s="12"/>
+      <c r="A1005" s="13"/>
     </row>
     <row r="1006">
-      <c r="A1006" s="12"/>
+      <c r="A1006" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$V$72"/>
@@ -10520,10 +10521,9 @@
     <hyperlink r:id="rId193" ref="N71"/>
     <hyperlink r:id="rId194" ref="O71"/>
     <hyperlink r:id="rId195" ref="P71"/>
-    <hyperlink r:id="rId196" ref="N72"/>
-    <hyperlink r:id="rId197" ref="O72"/>
-    <hyperlink r:id="rId198" ref="P72"/>
+    <hyperlink r:id="rId196" ref="O72"/>
+    <hyperlink r:id="rId197" ref="P72"/>
   </hyperlinks>
-  <drawing r:id="rId199"/>
+  <drawing r:id="rId198"/>
 </worksheet>
 </file>
--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -3463,7 +3463,7 @@
         <v>225</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>24</v>

--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Poster List" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Poster List'!$A$1:$V$72</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Poster List'!$A$1:$V$74</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="324">
   <si>
     <t>Date</t>
   </si>
@@ -327,6 +327,24 @@
     <t>In Austin's Physical Location</t>
   </si>
   <si>
+    <t>Primus</t>
+  </si>
+  <si>
+    <t>Don Pendleton</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>15/30</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/244095</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KmIylDFDmN37fyiv10iZIyAUA8EEC8VM/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Guns N' Roses</t>
   </si>
   <si>
@@ -444,6 +462,15 @@
     <t>https://drive.google.com/file/d/1cn8nnnrlL9PkWDtAgC7uucUu3dTCOYaq/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Elton John</t>
+  </si>
+  <si>
+    <t>David LaChapelle</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/301920</t>
+  </si>
+  <si>
     <t>KISS</t>
   </si>
   <si>
@@ -877,9 +904,6 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1nhnWVdsZGFIYWxQGq15GNVykvmGD7HzK/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Don Pendleton</t>
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/332084</t>
@@ -1015,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1037,6 +1061,7 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -2048,8 +2073,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1">
-        <v>42958.0</v>
+      <c r="A18" s="7">
+        <v>42934.0</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>104</v>
@@ -2058,12 +2083,14 @@
         <v>105</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
         <v>107</v>
       </c>
@@ -2079,89 +2106,83 @@
       <c r="K18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="O18" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="M18" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>43005.0</v>
+        <v>42958.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>25</v>
+      <c r="L19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M19" s="2">
+        <v>24.0</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>43018.0</v>
+        <v>43005.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>23</v>
@@ -2171,9 +2192,6 @@
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>25</v>
@@ -2182,34 +2200,34 @@
         <v>26</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>43238.0</v>
+        <v>43018.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>23</v>
@@ -2219,6 +2237,9 @@
       </c>
       <c r="K21" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>25</v>
@@ -2226,35 +2247,38 @@
       <c r="N21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P21" s="4" t="s">
-        <v>122</v>
+      <c r="O21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>43240.0</v>
+        <v>43238.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2268,38 +2292,35 @@
       <c r="N22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="P22" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>43347.0</v>
+        <v>43240.0</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2313,28 +2334,28 @@
       <c r="N23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O23" s="4" t="s">
-        <v>128</v>
+      <c r="O23" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>43405.0</v>
+        <v>43347.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
@@ -2352,20 +2373,17 @@
       <c r="K24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>133</v>
+      <c r="O24" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -2373,13 +2391,16 @@
         <v>43405.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
@@ -2389,13 +2410,16 @@
         <v>22</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>25</v>
@@ -2403,53 +2427,50 @@
       <c r="N25" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O25" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="P25" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>43493.0</v>
+        <v>43405.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="2">
-        <v>36.0</v>
+      <c r="M26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O26" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="P26" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27">
@@ -2460,7 +2481,7 @@
         <v>92</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>39</v>
@@ -2470,7 +2491,7 @@
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>22</v>
@@ -2479,33 +2500,33 @@
         <v>23</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>25</v>
+      <c r="M27" s="2">
+        <v>36.0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>141</v>
+      <c r="O27" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>43561.0</v>
+        <v>43493.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>39</v>
@@ -2518,91 +2539,90 @@
         <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="2">
-        <v>30.0</v>
+      <c r="M28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1">
-        <v>43595.0</v>
+      <c r="A29" s="7">
+        <v>43536.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="2"/>
+        <v>32</v>
+      </c>
       <c r="G29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>148</v>
+      <c r="O29" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>43733.0</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>104</v>
+        <v>43561.0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>23</v>
@@ -2613,53 +2633,44 @@
       <c r="K30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="M30" s="2">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P30" s="4" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>43788.0</v>
+        <v>43595.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>25</v>
@@ -2668,72 +2679,69 @@
         <v>26</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <v>43793.0</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>84</v>
+        <v>43733.0</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>25</v>
+        <v>161</v>
+      </c>
+      <c r="M32" s="2">
+        <v>23.0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="P32" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>43844.0</v>
+        <v>43788.0</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>32</v>
@@ -2752,10 +2760,10 @@
         <v>24</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>25</v>
@@ -2764,31 +2772,31 @@
         <v>26</v>
       </c>
       <c r="O33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="P33" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <v>43847.0</v>
+        <v>43793.0</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>22</v>
@@ -2797,91 +2805,100 @@
         <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M34" s="2">
-        <v>15.0</v>
+      <c r="L34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>43869.0</v>
+        <v>43844.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M35" s="2">
-        <v>31.0</v>
+      <c r="M35" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <v>44450.0</v>
+        <v>43847.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>23</v>
@@ -2890,113 +2907,114 @@
         <v>24</v>
       </c>
       <c r="M36" s="2">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O36" s="4" t="s">
-        <v>177</v>
+      <c r="O36" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1">
-        <v>44468.0</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>104</v>
+        <v>43869.0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>25</v>
+      <c r="L37" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M37" s="2">
+        <v>31.0</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P37" s="3" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="1">
-        <v>44511.0</v>
+        <v>44450.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>25</v>
+      <c r="M38" s="2">
+        <v>21.0</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O38" s="4" t="s">
+        <v>186</v>
+      </c>
       <c r="P38" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1">
-        <v>44519.0</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>187</v>
+        <v>44468.0</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>39</v>
@@ -3006,67 +3024,63 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M39" s="2">
-        <v>29.0</v>
+      <c r="M39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O39" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="P39" s="4" t="s">
+      <c r="P39" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <v>44614.0</v>
+        <v>44511.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G40" s="2" t="s">
-        <v>193</v>
+        <v>33</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>25</v>
@@ -3074,70 +3088,67 @@
       <c r="N40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O40" s="3" t="s">
+      <c r="P40" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>44640.0</v>
+        <v>44519.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>198</v>
+        <v>39</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>33</v>
+        <v>197</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>25</v>
+      <c r="M41" s="2">
+        <v>29.0</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O41" s="4" t="s">
+      <c r="O41" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="P41" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>44679.0</v>
+        <v>44614.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>32</v>
@@ -3150,93 +3161,94 @@
         <v>22</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M42" s="2">
-        <v>19.0</v>
+      <c r="L42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O42" s="4" t="s">
-        <v>203</v>
+      <c r="O42" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>44679.0</v>
+        <v>44640.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M43" s="2">
-        <v>20.0</v>
+      <c r="M43" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>44734.0</v>
+        <v>44679.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>22</v>
@@ -3245,33 +3257,33 @@
         <v>23</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>25</v>
+      <c r="M44" s="2">
+        <v>19.0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>209</v>
+      <c r="O44" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>44773.0</v>
+        <v>44679.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>211</v>
+        <v>37</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>39</v>
@@ -3281,10 +3293,10 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>23</v>
@@ -3296,52 +3308,54 @@
         <v>24</v>
       </c>
       <c r="M45" s="2">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="O45" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P45" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>44804.0</v>
+        <v>44734.0</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F46" s="2"/>
+      <c r="F46" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G46" s="2" t="s">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M46" s="2">
-        <v>33.0</v>
+      <c r="M46" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>26</v>
@@ -3355,29 +3369,29 @@
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>44866.0</v>
+        <v>44773.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>23</v>
@@ -3386,42 +3400,40 @@
         <v>24</v>
       </c>
       <c r="M47" s="2">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>45064.0</v>
+        <v>44804.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>111</v>
+        <v>225</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>23</v>
@@ -3433,34 +3445,37 @@
         <v>24</v>
       </c>
       <c r="M48" s="2">
-        <v>14.0</v>
+        <v>33.0</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P48" s="4" t="s">
-        <v>223</v>
+      <c r="O48" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <v>45067.0</v>
+        <v>44866.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>224</v>
+        <v>68</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>22</v>
@@ -3475,40 +3490,42 @@
         <v>24</v>
       </c>
       <c r="M49" s="2">
-        <v>17.0</v>
+        <v>26.0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <v>45142.0</v>
+        <v>45064.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>228</v>
+        <v>117</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G50" s="2" t="s">
-        <v>230</v>
+        <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
@@ -3519,34 +3536,28 @@
       <c r="K50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="M50" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O50" s="4" t="s">
+      <c r="P50" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>45144.0</v>
+        <v>45067.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>32</v>
@@ -3559,52 +3570,49 @@
         <v>22</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="M51" s="2">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O51" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="P51" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>45213.0</v>
+        <v>45142.0</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>23</v>
@@ -3615,41 +3623,41 @@
       <c r="K52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="2"/>
+      <c r="L52" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="M52" s="2">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="P52" s="3" t="s">
+      <c r="O52" s="4" t="s">
         <v>241</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <v>45228.0</v>
+        <v>45144.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>39</v>
+        <v>238</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>22</v>
@@ -3661,46 +3669,49 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="M53" s="2">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>45228.0</v>
+        <v>45213.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>247</v>
+        <v>33</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>23</v>
@@ -3708,28 +3719,29 @@
       <c r="K54" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="L54" s="2"/>
       <c r="M54" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O54" s="4" t="s">
-        <v>248</v>
+      <c r="O54" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>45239.0</v>
+        <v>45228.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>39</v>
@@ -3737,12 +3749,14 @@
       <c r="E55" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G55" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>23</v>
@@ -3754,43 +3768,43 @@
         <v>24</v>
       </c>
       <c r="M55" s="2">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="N55" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O55" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="P55" s="4" t="s">
+      <c r="O55" s="3" t="s">
         <v>253</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>45312.0</v>
+        <v>45228.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>23</v>
@@ -3799,43 +3813,43 @@
         <v>24</v>
       </c>
       <c r="M56" s="2">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O56" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="P56" s="4" t="s">
+      <c r="O56" s="4" t="s">
         <v>257</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <v>45312.0</v>
+        <v>45239.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>84</v>
+        <v>259</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>23</v>
@@ -3844,34 +3858,38 @@
         <v>24</v>
       </c>
       <c r="M57" s="2">
-        <v>27.0</v>
+        <v>10.0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>256</v>
+      <c r="O57" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <v>45340.0</v>
+        <v>45312.0</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="H58" s="2" t="s">
         <v>22</v>
       </c>
@@ -3884,41 +3902,41 @@
       <c r="K58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>25</v>
+      <c r="M58" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <v>45389.0</v>
+        <v>45312.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>33</v>
+        <v>267</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>24</v>
@@ -3930,38 +3948,34 @@
         <v>24</v>
       </c>
       <c r="M59" s="2">
-        <v>7.0</v>
+        <v>27.0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1">
-        <v>45389.0</v>
+        <v>45340.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H60" s="2" t="s">
         <v>22</v>
       </c>
@@ -3975,19 +3989,16 @@
         <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M60" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>26</v>
+        <v>270</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61">
@@ -3995,22 +4006,23 @@
         <v>45389.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>185</v>
+        <v>141</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>24</v>
@@ -4021,43 +4033,41 @@
       <c r="K61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>25</v>
+      <c r="M61" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1">
-        <v>45428.0</v>
+        <v>45389.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="F62" s="2"/>
       <c r="G62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>23</v>
@@ -4068,43 +4078,46 @@
       <c r="K62" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="L62" s="2" t="s">
+        <v>273</v>
+      </c>
       <c r="M62" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O62" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="P62" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1">
-        <v>45469.0</v>
+        <v>45389.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>279</v>
+        <v>194</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>23</v>
@@ -4112,41 +4125,43 @@
       <c r="K63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M63" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O63" s="4" t="s">
-        <v>280</v>
+      <c r="L63" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1">
-        <v>45469.0</v>
+        <v>45428.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F64" s="2"/>
+      <c r="F64" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G64" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>23</v>
@@ -4158,27 +4173,24 @@
         <v>24</v>
       </c>
       <c r="M64" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O64" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="P64" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
-        <v>45783.0</v>
+        <v>45469.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>39</v>
@@ -4186,8 +4198,11 @@
       <c r="E65" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="F65" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="G65" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>22</v>
@@ -4202,27 +4217,27 @@
         <v>24</v>
       </c>
       <c r="M65" s="2">
-        <v>38.0</v>
+        <v>3.0</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O65" s="3" t="s">
-        <v>286</v>
+      <c r="O65" s="4" t="s">
+        <v>289</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1">
-        <v>45790.0</v>
+        <v>45469.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>126</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>39</v>
@@ -4247,37 +4262,36 @@
         <v>24</v>
       </c>
       <c r="M66" s="2">
-        <v>32.0</v>
+        <v>6.0</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O66" s="3" t="s">
+      <c r="O66" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>290</v>
+      <c r="P66" s="4" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1">
-        <v>45808.0</v>
+        <v>45783.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F67" s="2"/>
+        <v>19</v>
+      </c>
       <c r="G67" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>22</v>
@@ -4291,41 +4305,38 @@
       <c r="K67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="M67" s="2">
-        <v>8.0</v>
+        <v>38.0</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="P67" s="3" t="s">
         <v>295</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1">
-        <v>45808.0</v>
+        <v>45790.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>296</v>
+        <v>105</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>22</v>
@@ -4340,37 +4351,37 @@
         <v>24</v>
       </c>
       <c r="M68" s="2">
-        <v>37.0</v>
+        <v>32.0</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O68" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="P68" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1">
-        <v>45896.0</v>
+        <v>45808.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2" t="s">
-        <v>33</v>
+        <v>300</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>22</v>
@@ -4384,40 +4395,44 @@
       <c r="K69" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="L69" s="2" t="s">
+        <v>301</v>
+      </c>
       <c r="M69" s="2">
-        <v>34.0</v>
+        <v>8.0</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O69" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="P69" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1">
-        <v>45905.0</v>
+        <v>45808.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>183</v>
+        <v>304</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>302</v>
-      </c>
+      <c r="F70" s="2"/>
       <c r="G70" s="2" t="s">
-        <v>33</v>
+        <v>305</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>23</v>
@@ -4428,43 +4443,38 @@
       <c r="K70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="M70" s="2">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <v>46113.0</v>
+        <v>45896.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="F71" s="2"/>
       <c r="G71" s="2" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>22</v>
@@ -4478,2869 +4488,2957 @@
       <c r="K71" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L71" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="M71" s="2">
-        <v>11.0</v>
+        <v>34.0</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O71" s="3" t="s">
+      <c r="P71" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1">
-        <v>46129.0</v>
+        <v>45905.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>311</v>
+        <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>312</v>
+        <v>192</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F72" s="2"/>
+      <c r="F72" s="2" t="s">
+        <v>310</v>
+      </c>
       <c r="G72" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="M72" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="P72" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H72" s="2" t="s">
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>46113.0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M72" s="2">
+      <c r="I73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="M73" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>46129.0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M74" s="2">
         <v>39.0</v>
       </c>
-      <c r="N72" s="8"/>
-      <c r="O72" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9"/>
+      <c r="N74" s="9"/>
+      <c r="O74" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="9"/>
+      <c r="A75" s="10"/>
     </row>
     <row r="76">
-      <c r="A76" s="9"/>
+      <c r="A76" s="10"/>
     </row>
     <row r="77">
-      <c r="A77" s="9"/>
+      <c r="A77" s="10"/>
     </row>
     <row r="78">
-      <c r="A78" s="9"/>
+      <c r="A78" s="10"/>
     </row>
     <row r="79">
-      <c r="A79" s="9"/>
+      <c r="A79" s="10"/>
     </row>
     <row r="80">
-      <c r="A80" s="9"/>
+      <c r="A80" s="10"/>
     </row>
     <row r="81">
-      <c r="A81" s="9"/>
+      <c r="A81" s="10"/>
     </row>
     <row r="82">
-      <c r="A82" s="9"/>
+      <c r="A82" s="10"/>
     </row>
     <row r="83">
-      <c r="A83" s="9"/>
+      <c r="A83" s="10"/>
     </row>
     <row r="84">
-      <c r="A84" s="9"/>
+      <c r="A84" s="10"/>
     </row>
     <row r="85">
-      <c r="A85" s="9"/>
+      <c r="A85" s="10"/>
     </row>
     <row r="86">
-      <c r="A86" s="9"/>
+      <c r="A86" s="10"/>
     </row>
     <row r="87">
-      <c r="A87" s="9"/>
+      <c r="A87" s="10"/>
     </row>
     <row r="88">
-      <c r="A88" s="9"/>
+      <c r="A88" s="10"/>
     </row>
     <row r="89">
-      <c r="A89" s="9"/>
+      <c r="A89" s="10"/>
     </row>
     <row r="90">
-      <c r="A90" s="9"/>
+      <c r="A90" s="10"/>
     </row>
     <row r="91">
-      <c r="A91" s="9"/>
+      <c r="A91" s="10"/>
     </row>
     <row r="92">
-      <c r="A92" s="9"/>
+      <c r="A92" s="10"/>
     </row>
     <row r="93">
-      <c r="A93" s="9"/>
+      <c r="A93" s="10"/>
     </row>
     <row r="94">
-      <c r="A94" s="9"/>
+      <c r="A94" s="10"/>
     </row>
     <row r="95">
-      <c r="A95" s="9"/>
+      <c r="A95" s="10"/>
     </row>
     <row r="96">
-      <c r="A96" s="9"/>
+      <c r="A96" s="10"/>
     </row>
     <row r="97">
-      <c r="A97" s="9"/>
+      <c r="A97" s="10"/>
     </row>
     <row r="98">
-      <c r="A98" s="9"/>
+      <c r="A98" s="10"/>
     </row>
     <row r="99">
-      <c r="A99" s="9"/>
+      <c r="A99" s="10"/>
     </row>
     <row r="100">
-      <c r="A100" s="9"/>
+      <c r="A100" s="10"/>
     </row>
     <row r="101">
-      <c r="A101" s="9"/>
+      <c r="A101" s="10"/>
     </row>
     <row r="102">
-      <c r="A102" s="9"/>
+      <c r="A102" s="10"/>
     </row>
     <row r="103">
-      <c r="A103" s="9"/>
+      <c r="A103" s="10"/>
     </row>
     <row r="104">
-      <c r="A104" s="9"/>
+      <c r="A104" s="10"/>
     </row>
     <row r="105">
-      <c r="A105" s="9"/>
+      <c r="A105" s="10"/>
     </row>
     <row r="106">
-      <c r="A106" s="9"/>
+      <c r="A106" s="10"/>
     </row>
     <row r="107">
-      <c r="A107" s="9"/>
+      <c r="A107" s="10"/>
     </row>
     <row r="108">
-      <c r="A108" s="9"/>
+      <c r="A108" s="10"/>
     </row>
     <row r="109">
-      <c r="A109" s="9"/>
+      <c r="A109" s="10"/>
     </row>
     <row r="110">
-      <c r="A110" s="9"/>
+      <c r="A110" s="10"/>
     </row>
     <row r="111">
-      <c r="A111" s="9"/>
+      <c r="A111" s="10"/>
     </row>
     <row r="112">
-      <c r="A112" s="9"/>
+      <c r="A112" s="10"/>
     </row>
     <row r="113">
-      <c r="A113" s="9"/>
+      <c r="A113" s="10"/>
     </row>
     <row r="114">
-      <c r="A114" s="9"/>
+      <c r="A114" s="10"/>
     </row>
     <row r="115">
-      <c r="A115" s="9"/>
+      <c r="A115" s="10"/>
     </row>
     <row r="116">
-      <c r="A116" s="9"/>
+      <c r="A116" s="10"/>
     </row>
     <row r="117">
-      <c r="A117" s="9"/>
+      <c r="A117" s="10"/>
     </row>
     <row r="118">
-      <c r="A118" s="9"/>
+      <c r="A118" s="10"/>
     </row>
     <row r="119">
-      <c r="A119" s="9"/>
+      <c r="A119" s="10"/>
     </row>
     <row r="120">
-      <c r="A120" s="9"/>
+      <c r="A120" s="10"/>
     </row>
     <row r="121">
-      <c r="A121" s="9"/>
+      <c r="A121" s="10"/>
     </row>
     <row r="122">
-      <c r="A122" s="9"/>
+      <c r="A122" s="10"/>
     </row>
     <row r="123">
-      <c r="A123" s="9"/>
+      <c r="A123" s="10"/>
     </row>
     <row r="124">
-      <c r="A124" s="9"/>
+      <c r="A124" s="10"/>
     </row>
     <row r="125">
-      <c r="A125" s="9"/>
+      <c r="A125" s="10"/>
     </row>
     <row r="126">
-      <c r="A126" s="9"/>
+      <c r="A126" s="10"/>
     </row>
     <row r="127">
-      <c r="A127" s="9"/>
+      <c r="A127" s="10"/>
     </row>
     <row r="128">
-      <c r="A128" s="9"/>
+      <c r="A128" s="10"/>
     </row>
     <row r="129">
-      <c r="A129" s="9"/>
+      <c r="A129" s="10"/>
     </row>
     <row r="130">
-      <c r="A130" s="9"/>
+      <c r="A130" s="10"/>
     </row>
     <row r="131">
-      <c r="A131" s="9"/>
+      <c r="A131" s="10"/>
     </row>
     <row r="132">
-      <c r="A132" s="9"/>
+      <c r="A132" s="10"/>
     </row>
     <row r="133">
-      <c r="A133" s="9"/>
+      <c r="A133" s="10"/>
     </row>
     <row r="134">
-      <c r="A134" s="9"/>
+      <c r="A134" s="10"/>
     </row>
     <row r="135">
-      <c r="A135" s="9"/>
+      <c r="A135" s="10"/>
     </row>
     <row r="136">
-      <c r="A136" s="9"/>
+      <c r="A136" s="10"/>
     </row>
     <row r="137">
-      <c r="A137" s="9"/>
+      <c r="A137" s="10"/>
     </row>
     <row r="138">
-      <c r="A138" s="9"/>
+      <c r="A138" s="10"/>
     </row>
     <row r="139">
-      <c r="A139" s="9"/>
+      <c r="A139" s="10"/>
     </row>
     <row r="140">
-      <c r="A140" s="9"/>
+      <c r="A140" s="10"/>
     </row>
     <row r="141">
-      <c r="A141" s="9"/>
+      <c r="A141" s="10"/>
     </row>
     <row r="142">
-      <c r="A142" s="9"/>
+      <c r="A142" s="10"/>
     </row>
     <row r="143">
-      <c r="A143" s="9"/>
+      <c r="A143" s="10"/>
     </row>
     <row r="144">
-      <c r="A144" s="9"/>
+      <c r="A144" s="10"/>
     </row>
     <row r="145">
-      <c r="A145" s="9"/>
+      <c r="A145" s="10"/>
     </row>
     <row r="146">
-      <c r="A146" s="9"/>
+      <c r="A146" s="10"/>
     </row>
     <row r="147">
-      <c r="A147" s="9"/>
+      <c r="A147" s="10"/>
     </row>
     <row r="148">
-      <c r="A148" s="9"/>
+      <c r="A148" s="10"/>
     </row>
     <row r="149">
-      <c r="A149" s="9"/>
+      <c r="A149" s="10"/>
     </row>
     <row r="150">
-      <c r="A150" s="9"/>
+      <c r="A150" s="10"/>
     </row>
     <row r="151">
-      <c r="A151" s="9"/>
+      <c r="A151" s="10"/>
     </row>
     <row r="152">
-      <c r="A152" s="9"/>
+      <c r="A152" s="10"/>
     </row>
     <row r="153">
-      <c r="A153" s="9"/>
+      <c r="A153" s="10"/>
     </row>
     <row r="154">
-      <c r="A154" s="9"/>
+      <c r="A154" s="10"/>
     </row>
     <row r="155">
-      <c r="A155" s="9"/>
+      <c r="A155" s="10"/>
     </row>
     <row r="156">
-      <c r="A156" s="9"/>
+      <c r="A156" s="10"/>
     </row>
     <row r="157">
-      <c r="A157" s="9"/>
+      <c r="A157" s="10"/>
     </row>
     <row r="158">
-      <c r="A158" s="9"/>
+      <c r="A158" s="10"/>
     </row>
     <row r="159">
-      <c r="A159" s="9"/>
+      <c r="A159" s="10"/>
     </row>
     <row r="160">
-      <c r="A160" s="9"/>
+      <c r="A160" s="10"/>
     </row>
     <row r="161">
-      <c r="A161" s="9"/>
+      <c r="A161" s="10"/>
     </row>
     <row r="162">
-      <c r="A162" s="9"/>
+      <c r="A162" s="10"/>
     </row>
     <row r="163">
-      <c r="A163" s="9"/>
+      <c r="A163" s="10"/>
     </row>
     <row r="164">
-      <c r="A164" s="9"/>
+      <c r="A164" s="10"/>
     </row>
     <row r="165">
-      <c r="A165" s="9"/>
+      <c r="A165" s="10"/>
     </row>
     <row r="166">
-      <c r="A166" s="9"/>
+      <c r="A166" s="10"/>
     </row>
     <row r="167">
-      <c r="A167" s="9"/>
+      <c r="A167" s="10"/>
     </row>
     <row r="168">
-      <c r="A168" s="9"/>
+      <c r="A168" s="10"/>
     </row>
     <row r="169">
-      <c r="A169" s="9"/>
+      <c r="A169" s="10"/>
     </row>
     <row r="170">
-      <c r="A170" s="9"/>
+      <c r="A170" s="10"/>
     </row>
     <row r="171">
-      <c r="A171" s="9"/>
+      <c r="A171" s="10"/>
     </row>
     <row r="172">
-      <c r="A172" s="9"/>
+      <c r="A172" s="10"/>
     </row>
     <row r="173">
-      <c r="A173" s="9"/>
+      <c r="A173" s="10"/>
     </row>
     <row r="174">
-      <c r="A174" s="9"/>
+      <c r="A174" s="10"/>
     </row>
     <row r="175">
-      <c r="A175" s="9"/>
+      <c r="A175" s="10"/>
     </row>
     <row r="176">
-      <c r="A176" s="9"/>
+      <c r="A176" s="10"/>
     </row>
     <row r="177">
-      <c r="A177" s="9"/>
+      <c r="A177" s="10"/>
     </row>
     <row r="178">
-      <c r="A178" s="9"/>
+      <c r="A178" s="10"/>
     </row>
     <row r="179">
-      <c r="A179" s="9"/>
+      <c r="A179" s="10"/>
     </row>
     <row r="180">
-      <c r="A180" s="9"/>
+      <c r="A180" s="10"/>
     </row>
     <row r="181">
-      <c r="A181" s="9"/>
+      <c r="A181" s="10"/>
     </row>
     <row r="182">
-      <c r="A182" s="9"/>
+      <c r="A182" s="10"/>
     </row>
     <row r="183">
-      <c r="A183" s="9"/>
+      <c r="A183" s="10"/>
     </row>
     <row r="184">
-      <c r="A184" s="9"/>
+      <c r="A184" s="10"/>
     </row>
     <row r="185">
-      <c r="A185" s="9"/>
+      <c r="A185" s="10"/>
     </row>
     <row r="186">
-      <c r="A186" s="9"/>
+      <c r="A186" s="10"/>
     </row>
     <row r="187">
-      <c r="A187" s="9"/>
+      <c r="A187" s="10"/>
     </row>
     <row r="188">
-      <c r="A188" s="9"/>
+      <c r="A188" s="10"/>
     </row>
     <row r="189">
-      <c r="A189" s="9"/>
+      <c r="A189" s="10"/>
     </row>
     <row r="190">
-      <c r="A190" s="9"/>
+      <c r="A190" s="10"/>
     </row>
     <row r="191">
-      <c r="A191" s="9"/>
+      <c r="A191" s="10"/>
     </row>
     <row r="192">
-      <c r="A192" s="9"/>
+      <c r="A192" s="10"/>
     </row>
     <row r="193">
-      <c r="A193" s="9"/>
+      <c r="A193" s="10"/>
     </row>
     <row r="194">
-      <c r="A194" s="9"/>
+      <c r="A194" s="10"/>
     </row>
     <row r="195">
-      <c r="A195" s="9"/>
+      <c r="A195" s="10"/>
     </row>
     <row r="196">
-      <c r="A196" s="9"/>
+      <c r="A196" s="10"/>
     </row>
     <row r="197">
-      <c r="A197" s="9"/>
+      <c r="A197" s="10"/>
     </row>
     <row r="198">
-      <c r="A198" s="9"/>
+      <c r="A198" s="10"/>
     </row>
     <row r="199">
-      <c r="A199" s="9"/>
+      <c r="A199" s="10"/>
     </row>
     <row r="200">
-      <c r="A200" s="9"/>
+      <c r="A200" s="10"/>
     </row>
     <row r="201">
-      <c r="A201" s="9"/>
+      <c r="A201" s="10"/>
     </row>
     <row r="202">
-      <c r="A202" s="9"/>
+      <c r="A202" s="10"/>
     </row>
     <row r="203">
-      <c r="A203" s="9"/>
+      <c r="A203" s="10"/>
     </row>
     <row r="204">
-      <c r="A204" s="9"/>
+      <c r="A204" s="10"/>
     </row>
     <row r="205">
-      <c r="A205" s="9"/>
+      <c r="A205" s="10"/>
     </row>
     <row r="206">
-      <c r="A206" s="9"/>
+      <c r="A206" s="10"/>
     </row>
     <row r="207">
-      <c r="A207" s="9"/>
+      <c r="A207" s="10"/>
     </row>
     <row r="208">
-      <c r="A208" s="9"/>
+      <c r="A208" s="10"/>
     </row>
     <row r="209">
-      <c r="A209" s="9"/>
+      <c r="A209" s="10"/>
     </row>
     <row r="210">
-      <c r="A210" s="9"/>
+      <c r="A210" s="10"/>
     </row>
     <row r="211">
-      <c r="A211" s="9"/>
+      <c r="A211" s="10"/>
     </row>
     <row r="212">
-      <c r="A212" s="9"/>
+      <c r="A212" s="10"/>
     </row>
     <row r="213">
-      <c r="A213" s="9"/>
+      <c r="A213" s="10"/>
     </row>
     <row r="214">
-      <c r="A214" s="9"/>
+      <c r="A214" s="10"/>
     </row>
     <row r="215">
-      <c r="A215" s="9"/>
+      <c r="A215" s="10"/>
     </row>
     <row r="216">
-      <c r="A216" s="9"/>
+      <c r="A216" s="10"/>
     </row>
     <row r="217">
-      <c r="A217" s="9"/>
+      <c r="A217" s="10"/>
     </row>
     <row r="218">
-      <c r="A218" s="9"/>
+      <c r="A218" s="10"/>
     </row>
     <row r="219">
-      <c r="A219" s="9"/>
+      <c r="A219" s="10"/>
     </row>
     <row r="220">
-      <c r="A220" s="9"/>
+      <c r="A220" s="10"/>
     </row>
     <row r="221">
-      <c r="A221" s="9"/>
+      <c r="A221" s="10"/>
     </row>
     <row r="222">
-      <c r="A222" s="9"/>
+      <c r="A222" s="10"/>
     </row>
     <row r="223">
-      <c r="A223" s="9"/>
+      <c r="A223" s="10"/>
     </row>
     <row r="224">
-      <c r="A224" s="9"/>
+      <c r="A224" s="10"/>
     </row>
     <row r="225">
-      <c r="A225" s="9"/>
+      <c r="A225" s="10"/>
     </row>
     <row r="226">
-      <c r="A226" s="9"/>
+      <c r="A226" s="10"/>
     </row>
     <row r="227">
-      <c r="A227" s="9"/>
+      <c r="A227" s="10"/>
     </row>
     <row r="228">
-      <c r="A228" s="9"/>
+      <c r="A228" s="10"/>
     </row>
     <row r="229">
-      <c r="A229" s="9"/>
+      <c r="A229" s="10"/>
     </row>
     <row r="230">
-      <c r="A230" s="9"/>
+      <c r="A230" s="10"/>
     </row>
     <row r="231">
-      <c r="A231" s="9"/>
+      <c r="A231" s="10"/>
     </row>
     <row r="232">
-      <c r="A232" s="9"/>
+      <c r="A232" s="10"/>
     </row>
     <row r="233">
-      <c r="A233" s="9"/>
+      <c r="A233" s="10"/>
     </row>
     <row r="234">
-      <c r="A234" s="9"/>
+      <c r="A234" s="10"/>
     </row>
     <row r="235">
-      <c r="A235" s="9"/>
+      <c r="A235" s="10"/>
     </row>
     <row r="236">
-      <c r="A236" s="9"/>
+      <c r="A236" s="10"/>
     </row>
     <row r="237">
-      <c r="A237" s="9"/>
+      <c r="A237" s="10"/>
     </row>
     <row r="238">
-      <c r="A238" s="9"/>
+      <c r="A238" s="10"/>
     </row>
     <row r="239">
-      <c r="A239" s="9"/>
+      <c r="A239" s="10"/>
     </row>
     <row r="240">
-      <c r="A240" s="9"/>
+      <c r="A240" s="10"/>
     </row>
     <row r="241">
-      <c r="A241" s="9"/>
+      <c r="A241" s="10"/>
     </row>
     <row r="242">
-      <c r="A242" s="9"/>
+      <c r="A242" s="10"/>
     </row>
     <row r="243">
-      <c r="A243" s="9"/>
+      <c r="A243" s="10"/>
     </row>
     <row r="244">
-      <c r="A244" s="9"/>
+      <c r="A244" s="10"/>
     </row>
     <row r="245">
-      <c r="A245" s="9"/>
+      <c r="A245" s="10"/>
     </row>
     <row r="246">
-      <c r="A246" s="9"/>
+      <c r="A246" s="10"/>
     </row>
     <row r="247">
-      <c r="A247" s="9"/>
+      <c r="A247" s="10"/>
     </row>
     <row r="248">
-      <c r="A248" s="9"/>
+      <c r="A248" s="10"/>
     </row>
     <row r="249">
-      <c r="A249" s="9"/>
+      <c r="A249" s="10"/>
     </row>
     <row r="250">
-      <c r="A250" s="9"/>
+      <c r="A250" s="10"/>
     </row>
     <row r="251">
-      <c r="A251" s="9"/>
+      <c r="A251" s="10"/>
     </row>
     <row r="252">
-      <c r="A252" s="9"/>
+      <c r="A252" s="10"/>
     </row>
     <row r="253">
-      <c r="A253" s="9"/>
+      <c r="A253" s="10"/>
     </row>
     <row r="254">
-      <c r="A254" s="9"/>
+      <c r="A254" s="10"/>
     </row>
     <row r="255">
-      <c r="A255" s="9"/>
+      <c r="A255" s="10"/>
     </row>
     <row r="256">
-      <c r="A256" s="9"/>
+      <c r="A256" s="10"/>
     </row>
     <row r="257">
-      <c r="A257" s="9"/>
+      <c r="A257" s="10"/>
     </row>
     <row r="258">
-      <c r="A258" s="9"/>
+      <c r="A258" s="10"/>
     </row>
     <row r="259">
-      <c r="A259" s="9"/>
+      <c r="A259" s="10"/>
     </row>
     <row r="260">
-      <c r="A260" s="9"/>
+      <c r="A260" s="10"/>
     </row>
     <row r="261">
-      <c r="A261" s="9"/>
+      <c r="A261" s="10"/>
     </row>
     <row r="262">
-      <c r="A262" s="9"/>
+      <c r="A262" s="10"/>
     </row>
     <row r="263">
-      <c r="A263" s="9"/>
+      <c r="A263" s="10"/>
     </row>
     <row r="264">
-      <c r="A264" s="9"/>
+      <c r="A264" s="10"/>
     </row>
     <row r="265">
-      <c r="A265" s="9"/>
+      <c r="A265" s="10"/>
     </row>
     <row r="266">
-      <c r="A266" s="9"/>
+      <c r="A266" s="10"/>
     </row>
     <row r="267">
-      <c r="A267" s="9"/>
+      <c r="A267" s="10"/>
     </row>
     <row r="268">
-      <c r="A268" s="9"/>
+      <c r="A268" s="10"/>
     </row>
     <row r="269">
-      <c r="A269" s="9"/>
+      <c r="A269" s="10"/>
     </row>
     <row r="270">
-      <c r="A270" s="9"/>
+      <c r="A270" s="10"/>
     </row>
     <row r="271">
-      <c r="A271" s="9"/>
+      <c r="A271" s="10"/>
     </row>
     <row r="272">
-      <c r="A272" s="9"/>
+      <c r="A272" s="10"/>
     </row>
     <row r="273">
-      <c r="A273" s="9"/>
+      <c r="A273" s="10"/>
     </row>
     <row r="274">
-      <c r="A274" s="9"/>
+      <c r="A274" s="10"/>
     </row>
     <row r="275">
-      <c r="A275" s="9"/>
+      <c r="A275" s="10"/>
     </row>
     <row r="276">
-      <c r="A276" s="9"/>
+      <c r="A276" s="10"/>
     </row>
     <row r="277">
-      <c r="A277" s="9"/>
+      <c r="A277" s="10"/>
     </row>
     <row r="278">
-      <c r="A278" s="9"/>
+      <c r="A278" s="10"/>
     </row>
     <row r="279">
-      <c r="A279" s="9"/>
+      <c r="A279" s="10"/>
     </row>
     <row r="280">
-      <c r="A280" s="9"/>
+      <c r="A280" s="10"/>
     </row>
     <row r="281">
-      <c r="A281" s="9"/>
+      <c r="A281" s="10"/>
     </row>
     <row r="282">
-      <c r="A282" s="9"/>
+      <c r="A282" s="10"/>
     </row>
     <row r="283">
-      <c r="A283" s="9"/>
+      <c r="A283" s="10"/>
     </row>
     <row r="284">
-      <c r="A284" s="9"/>
+      <c r="A284" s="10"/>
     </row>
     <row r="285">
-      <c r="A285" s="9"/>
+      <c r="A285" s="10"/>
     </row>
     <row r="286">
-      <c r="A286" s="9"/>
+      <c r="A286" s="10"/>
     </row>
     <row r="287">
-      <c r="A287" s="9"/>
+      <c r="A287" s="10"/>
     </row>
     <row r="288">
-      <c r="A288" s="9"/>
+      <c r="A288" s="10"/>
     </row>
     <row r="289">
-      <c r="A289" s="9"/>
+      <c r="A289" s="10"/>
     </row>
     <row r="290">
-      <c r="A290" s="9"/>
+      <c r="A290" s="10"/>
     </row>
     <row r="291">
-      <c r="A291" s="9"/>
+      <c r="A291" s="10"/>
     </row>
     <row r="292">
-      <c r="A292" s="9"/>
+      <c r="A292" s="10"/>
     </row>
     <row r="293">
-      <c r="A293" s="9"/>
+      <c r="A293" s="10"/>
     </row>
     <row r="294">
-      <c r="A294" s="9"/>
+      <c r="A294" s="10"/>
     </row>
     <row r="295">
-      <c r="A295" s="9"/>
+      <c r="A295" s="10"/>
     </row>
     <row r="296">
-      <c r="A296" s="9"/>
+      <c r="A296" s="10"/>
     </row>
     <row r="297">
-      <c r="A297" s="9"/>
+      <c r="A297" s="10"/>
     </row>
     <row r="298">
-      <c r="A298" s="9"/>
+      <c r="A298" s="10"/>
     </row>
     <row r="299">
-      <c r="A299" s="9"/>
+      <c r="A299" s="10"/>
     </row>
     <row r="300">
-      <c r="A300" s="9"/>
+      <c r="A300" s="10"/>
     </row>
     <row r="301">
-      <c r="A301" s="9"/>
+      <c r="A301" s="10"/>
     </row>
     <row r="302">
-      <c r="A302" s="9"/>
+      <c r="A302" s="10"/>
     </row>
     <row r="303">
-      <c r="A303" s="9"/>
+      <c r="A303" s="10"/>
     </row>
     <row r="304">
-      <c r="A304" s="9"/>
+      <c r="A304" s="10"/>
     </row>
     <row r="305">
-      <c r="A305" s="9"/>
+      <c r="A305" s="10"/>
     </row>
     <row r="306">
-      <c r="A306" s="9"/>
+      <c r="A306" s="10"/>
     </row>
     <row r="307">
-      <c r="A307" s="9"/>
+      <c r="A307" s="10"/>
     </row>
     <row r="308">
-      <c r="A308" s="9"/>
+      <c r="A308" s="10"/>
     </row>
     <row r="309">
-      <c r="A309" s="9"/>
+      <c r="A309" s="10"/>
     </row>
     <row r="310">
-      <c r="A310" s="9"/>
+      <c r="A310" s="10"/>
     </row>
     <row r="311">
-      <c r="A311" s="9"/>
+      <c r="A311" s="10"/>
     </row>
     <row r="312">
-      <c r="A312" s="9"/>
+      <c r="A312" s="10"/>
     </row>
     <row r="313">
-      <c r="A313" s="9"/>
+      <c r="A313" s="10"/>
     </row>
     <row r="314">
-      <c r="A314" s="9"/>
+      <c r="A314" s="10"/>
     </row>
     <row r="315">
-      <c r="A315" s="9"/>
+      <c r="A315" s="10"/>
     </row>
     <row r="316">
-      <c r="A316" s="9"/>
+      <c r="A316" s="10"/>
     </row>
     <row r="317">
-      <c r="A317" s="9"/>
+      <c r="A317" s="10"/>
     </row>
     <row r="318">
-      <c r="A318" s="9"/>
+      <c r="A318" s="10"/>
     </row>
     <row r="319">
-      <c r="A319" s="9"/>
+      <c r="A319" s="10"/>
     </row>
     <row r="320">
-      <c r="A320" s="9"/>
+      <c r="A320" s="10"/>
     </row>
     <row r="321">
-      <c r="A321" s="9"/>
+      <c r="A321" s="10"/>
     </row>
     <row r="322">
-      <c r="A322" s="9"/>
+      <c r="A322" s="10"/>
     </row>
     <row r="323">
-      <c r="A323" s="9"/>
+      <c r="A323" s="10"/>
     </row>
     <row r="324">
-      <c r="A324" s="9"/>
+      <c r="A324" s="10"/>
     </row>
     <row r="325">
-      <c r="A325" s="9"/>
+      <c r="A325" s="10"/>
     </row>
     <row r="326">
-      <c r="A326" s="9"/>
+      <c r="A326" s="10"/>
     </row>
     <row r="327">
-      <c r="A327" s="9"/>
+      <c r="A327" s="10"/>
     </row>
     <row r="328">
-      <c r="A328" s="9"/>
+      <c r="A328" s="10"/>
     </row>
     <row r="329">
-      <c r="A329" s="9"/>
+      <c r="A329" s="10"/>
     </row>
     <row r="330">
-      <c r="A330" s="9"/>
+      <c r="A330" s="10"/>
     </row>
     <row r="331">
-      <c r="A331" s="9"/>
+      <c r="A331" s="10"/>
     </row>
     <row r="332">
-      <c r="A332" s="9"/>
+      <c r="A332" s="10"/>
     </row>
     <row r="333">
-      <c r="A333" s="9"/>
+      <c r="A333" s="10"/>
     </row>
     <row r="334">
-      <c r="A334" s="9"/>
+      <c r="A334" s="10"/>
     </row>
     <row r="335">
-      <c r="A335" s="9"/>
+      <c r="A335" s="10"/>
     </row>
     <row r="336">
-      <c r="A336" s="9"/>
+      <c r="A336" s="10"/>
     </row>
     <row r="337">
-      <c r="A337" s="9"/>
+      <c r="A337" s="10"/>
     </row>
     <row r="338">
-      <c r="A338" s="9"/>
+      <c r="A338" s="10"/>
     </row>
     <row r="339">
-      <c r="A339" s="9"/>
+      <c r="A339" s="10"/>
     </row>
     <row r="340">
-      <c r="A340" s="9"/>
+      <c r="A340" s="10"/>
     </row>
     <row r="341">
-      <c r="A341" s="9"/>
+      <c r="A341" s="10"/>
     </row>
     <row r="342">
-      <c r="A342" s="9"/>
+      <c r="A342" s="10"/>
     </row>
     <row r="343">
-      <c r="A343" s="9"/>
+      <c r="A343" s="10"/>
     </row>
     <row r="344">
-      <c r="A344" s="9"/>
+      <c r="A344" s="10"/>
     </row>
     <row r="345">
-      <c r="A345" s="9"/>
+      <c r="A345" s="10"/>
     </row>
     <row r="346">
-      <c r="A346" s="9"/>
+      <c r="A346" s="10"/>
     </row>
     <row r="347">
-      <c r="A347" s="9"/>
+      <c r="A347" s="10"/>
     </row>
     <row r="348">
-      <c r="A348" s="9"/>
+      <c r="A348" s="10"/>
     </row>
     <row r="349">
-      <c r="A349" s="9"/>
+      <c r="A349" s="10"/>
     </row>
     <row r="350">
-      <c r="A350" s="9"/>
+      <c r="A350" s="10"/>
     </row>
     <row r="351">
-      <c r="A351" s="9"/>
+      <c r="A351" s="10"/>
     </row>
     <row r="352">
-      <c r="A352" s="9"/>
+      <c r="A352" s="10"/>
     </row>
     <row r="353">
-      <c r="A353" s="9"/>
+      <c r="A353" s="10"/>
     </row>
     <row r="354">
-      <c r="A354" s="9"/>
+      <c r="A354" s="10"/>
     </row>
     <row r="355">
-      <c r="A355" s="9"/>
+      <c r="A355" s="10"/>
     </row>
     <row r="356">
-      <c r="A356" s="9"/>
+      <c r="A356" s="10"/>
     </row>
     <row r="357">
-      <c r="A357" s="9"/>
+      <c r="A357" s="10"/>
     </row>
     <row r="358">
-      <c r="A358" s="9"/>
+      <c r="A358" s="10"/>
     </row>
     <row r="359">
-      <c r="A359" s="9"/>
+      <c r="A359" s="10"/>
     </row>
     <row r="360">
-      <c r="A360" s="9"/>
+      <c r="A360" s="10"/>
     </row>
     <row r="361">
-      <c r="A361" s="9"/>
+      <c r="A361" s="10"/>
     </row>
     <row r="362">
-      <c r="A362" s="9"/>
+      <c r="A362" s="10"/>
     </row>
     <row r="363">
-      <c r="A363" s="9"/>
+      <c r="A363" s="10"/>
     </row>
     <row r="364">
-      <c r="A364" s="9"/>
+      <c r="A364" s="10"/>
     </row>
     <row r="365">
-      <c r="A365" s="9"/>
+      <c r="A365" s="10"/>
     </row>
     <row r="366">
-      <c r="A366" s="9"/>
+      <c r="A366" s="10"/>
     </row>
     <row r="367">
-      <c r="A367" s="9"/>
+      <c r="A367" s="10"/>
     </row>
     <row r="368">
-      <c r="A368" s="9"/>
+      <c r="A368" s="10"/>
     </row>
     <row r="369">
-      <c r="A369" s="9"/>
+      <c r="A369" s="10"/>
     </row>
     <row r="370">
-      <c r="A370" s="9"/>
+      <c r="A370" s="10"/>
     </row>
     <row r="371">
-      <c r="A371" s="9"/>
+      <c r="A371" s="10"/>
     </row>
     <row r="372">
-      <c r="A372" s="9"/>
+      <c r="A372" s="10"/>
     </row>
     <row r="373">
-      <c r="A373" s="9"/>
+      <c r="A373" s="10"/>
     </row>
     <row r="374">
-      <c r="A374" s="9"/>
+      <c r="A374" s="10"/>
     </row>
     <row r="375">
-      <c r="A375" s="9"/>
+      <c r="A375" s="10"/>
     </row>
     <row r="376">
-      <c r="A376" s="9"/>
+      <c r="A376" s="10"/>
     </row>
     <row r="377">
-      <c r="A377" s="9"/>
+      <c r="A377" s="10"/>
     </row>
     <row r="378">
-      <c r="A378" s="9"/>
+      <c r="A378" s="10"/>
     </row>
     <row r="379">
-      <c r="A379" s="9"/>
+      <c r="A379" s="10"/>
     </row>
     <row r="380">
-      <c r="A380" s="9"/>
+      <c r="A380" s="10"/>
     </row>
     <row r="381">
-      <c r="A381" s="9"/>
+      <c r="A381" s="10"/>
     </row>
     <row r="382">
-      <c r="A382" s="9"/>
+      <c r="A382" s="10"/>
     </row>
     <row r="383">
-      <c r="A383" s="9"/>
+      <c r="A383" s="10"/>
     </row>
     <row r="384">
-      <c r="A384" s="9"/>
+      <c r="A384" s="10"/>
     </row>
     <row r="385">
-      <c r="A385" s="9"/>
+      <c r="A385" s="10"/>
     </row>
     <row r="386">
-      <c r="A386" s="9"/>
+      <c r="A386" s="10"/>
     </row>
     <row r="387">
-      <c r="A387" s="9"/>
+      <c r="A387" s="10"/>
     </row>
     <row r="388">
-      <c r="A388" s="9"/>
+      <c r="A388" s="10"/>
     </row>
     <row r="389">
-      <c r="A389" s="9"/>
+      <c r="A389" s="10"/>
     </row>
     <row r="390">
-      <c r="A390" s="9"/>
+      <c r="A390" s="10"/>
     </row>
     <row r="391">
-      <c r="A391" s="9"/>
+      <c r="A391" s="10"/>
     </row>
     <row r="392">
-      <c r="A392" s="9"/>
+      <c r="A392" s="10"/>
     </row>
     <row r="393">
-      <c r="A393" s="9"/>
+      <c r="A393" s="10"/>
     </row>
     <row r="394">
-      <c r="A394" s="9"/>
+      <c r="A394" s="10"/>
     </row>
     <row r="395">
-      <c r="A395" s="9"/>
+      <c r="A395" s="10"/>
     </row>
     <row r="396">
-      <c r="A396" s="9"/>
+      <c r="A396" s="10"/>
     </row>
     <row r="397">
-      <c r="A397" s="9"/>
+      <c r="A397" s="10"/>
     </row>
     <row r="398">
-      <c r="A398" s="9"/>
+      <c r="A398" s="10"/>
     </row>
     <row r="399">
-      <c r="A399" s="9"/>
+      <c r="A399" s="10"/>
     </row>
     <row r="400">
-      <c r="A400" s="9"/>
+      <c r="A400" s="10"/>
     </row>
     <row r="401">
-      <c r="A401" s="9"/>
+      <c r="A401" s="10"/>
     </row>
     <row r="402">
-      <c r="A402" s="9"/>
+      <c r="A402" s="10"/>
     </row>
     <row r="403">
-      <c r="A403" s="9"/>
+      <c r="A403" s="10"/>
     </row>
     <row r="404">
-      <c r="A404" s="9"/>
+      <c r="A404" s="10"/>
     </row>
     <row r="405">
-      <c r="A405" s="9"/>
+      <c r="A405" s="10"/>
     </row>
     <row r="406">
-      <c r="A406" s="9"/>
+      <c r="A406" s="10"/>
     </row>
     <row r="407">
-      <c r="A407" s="9"/>
+      <c r="A407" s="10"/>
     </row>
     <row r="408">
-      <c r="A408" s="9"/>
+      <c r="A408" s="10"/>
     </row>
     <row r="409">
-      <c r="A409" s="9"/>
+      <c r="A409" s="10"/>
     </row>
     <row r="410">
-      <c r="A410" s="9"/>
+      <c r="A410" s="10"/>
     </row>
     <row r="411">
-      <c r="A411" s="9"/>
+      <c r="A411" s="10"/>
     </row>
     <row r="412">
-      <c r="A412" s="9"/>
+      <c r="A412" s="10"/>
     </row>
     <row r="413">
-      <c r="A413" s="9"/>
+      <c r="A413" s="10"/>
     </row>
     <row r="414">
-      <c r="A414" s="9"/>
+      <c r="A414" s="10"/>
     </row>
     <row r="415">
-      <c r="A415" s="9"/>
+      <c r="A415" s="10"/>
     </row>
     <row r="416">
-      <c r="A416" s="9"/>
+      <c r="A416" s="10"/>
     </row>
     <row r="417">
-      <c r="A417" s="9"/>
+      <c r="A417" s="10"/>
     </row>
     <row r="418">
-      <c r="A418" s="9"/>
+      <c r="A418" s="10"/>
     </row>
     <row r="419">
-      <c r="A419" s="9"/>
+      <c r="A419" s="10"/>
     </row>
     <row r="420">
-      <c r="A420" s="9"/>
+      <c r="A420" s="10"/>
     </row>
     <row r="421">
-      <c r="A421" s="9"/>
+      <c r="A421" s="10"/>
     </row>
     <row r="422">
-      <c r="A422" s="9"/>
+      <c r="A422" s="10"/>
     </row>
     <row r="423">
-      <c r="A423" s="9"/>
+      <c r="A423" s="10"/>
     </row>
     <row r="424">
-      <c r="A424" s="9"/>
+      <c r="A424" s="10"/>
     </row>
     <row r="425">
-      <c r="A425" s="9"/>
+      <c r="A425" s="10"/>
     </row>
     <row r="426">
-      <c r="A426" s="9"/>
+      <c r="A426" s="10"/>
     </row>
     <row r="427">
-      <c r="A427" s="9"/>
+      <c r="A427" s="10"/>
     </row>
     <row r="428">
-      <c r="A428" s="9"/>
+      <c r="A428" s="10"/>
     </row>
     <row r="429">
-      <c r="A429" s="9"/>
+      <c r="A429" s="10"/>
     </row>
     <row r="430">
-      <c r="A430" s="9"/>
+      <c r="A430" s="10"/>
     </row>
     <row r="431">
-      <c r="A431" s="9"/>
+      <c r="A431" s="10"/>
     </row>
     <row r="432">
-      <c r="A432" s="9"/>
+      <c r="A432" s="10"/>
     </row>
     <row r="433">
-      <c r="A433" s="9"/>
+      <c r="A433" s="10"/>
     </row>
     <row r="434">
-      <c r="A434" s="9"/>
+      <c r="A434" s="10"/>
     </row>
     <row r="435">
-      <c r="A435" s="9"/>
+      <c r="A435" s="10"/>
     </row>
     <row r="436">
-      <c r="A436" s="9"/>
+      <c r="A436" s="10"/>
     </row>
     <row r="437">
-      <c r="A437" s="9"/>
+      <c r="A437" s="10"/>
     </row>
     <row r="438">
-      <c r="A438" s="9"/>
+      <c r="A438" s="10"/>
     </row>
     <row r="439">
-      <c r="A439" s="9"/>
+      <c r="A439" s="10"/>
     </row>
     <row r="440">
-      <c r="A440" s="9"/>
+      <c r="A440" s="10"/>
     </row>
     <row r="441">
-      <c r="A441" s="9"/>
+      <c r="A441" s="10"/>
     </row>
     <row r="442">
-      <c r="A442" s="9"/>
+      <c r="A442" s="10"/>
     </row>
     <row r="443">
-      <c r="A443" s="9"/>
+      <c r="A443" s="10"/>
     </row>
     <row r="444">
-      <c r="A444" s="9"/>
+      <c r="A444" s="10"/>
     </row>
     <row r="445">
-      <c r="A445" s="9"/>
+      <c r="A445" s="10"/>
     </row>
     <row r="446">
-      <c r="A446" s="9"/>
+      <c r="A446" s="10"/>
     </row>
     <row r="447">
-      <c r="A447" s="9"/>
+      <c r="A447" s="10"/>
     </row>
     <row r="448">
-      <c r="A448" s="9"/>
+      <c r="A448" s="10"/>
     </row>
     <row r="449">
-      <c r="A449" s="9"/>
+      <c r="A449" s="10"/>
     </row>
     <row r="450">
-      <c r="A450" s="9"/>
+      <c r="A450" s="10"/>
     </row>
     <row r="451">
-      <c r="A451" s="9"/>
+      <c r="A451" s="10"/>
     </row>
     <row r="452">
-      <c r="A452" s="9"/>
+      <c r="A452" s="10"/>
     </row>
     <row r="453">
-      <c r="A453" s="9"/>
+      <c r="A453" s="10"/>
     </row>
     <row r="454">
-      <c r="A454" s="9"/>
+      <c r="A454" s="10"/>
     </row>
     <row r="455">
-      <c r="A455" s="9"/>
+      <c r="A455" s="10"/>
     </row>
     <row r="456">
-      <c r="A456" s="9"/>
+      <c r="A456" s="10"/>
     </row>
     <row r="457">
-      <c r="A457" s="9"/>
+      <c r="A457" s="10"/>
     </row>
     <row r="458">
-      <c r="A458" s="9"/>
+      <c r="A458" s="10"/>
     </row>
     <row r="459">
-      <c r="A459" s="9"/>
+      <c r="A459" s="10"/>
     </row>
     <row r="460">
-      <c r="A460" s="9"/>
+      <c r="A460" s="10"/>
     </row>
     <row r="461">
-      <c r="A461" s="9"/>
+      <c r="A461" s="10"/>
     </row>
     <row r="462">
-      <c r="A462" s="9"/>
+      <c r="A462" s="10"/>
     </row>
     <row r="463">
-      <c r="A463" s="9"/>
+      <c r="A463" s="10"/>
     </row>
     <row r="464">
-      <c r="A464" s="9"/>
+      <c r="A464" s="10"/>
     </row>
     <row r="465">
-      <c r="A465" s="9"/>
+      <c r="A465" s="10"/>
     </row>
     <row r="466">
-      <c r="A466" s="9"/>
+      <c r="A466" s="10"/>
     </row>
     <row r="467">
-      <c r="A467" s="9"/>
+      <c r="A467" s="10"/>
     </row>
     <row r="468">
-      <c r="A468" s="9"/>
+      <c r="A468" s="10"/>
     </row>
     <row r="469">
-      <c r="A469" s="9"/>
+      <c r="A469" s="10"/>
     </row>
     <row r="470">
-      <c r="A470" s="9"/>
+      <c r="A470" s="10"/>
     </row>
     <row r="471">
-      <c r="A471" s="9"/>
+      <c r="A471" s="10"/>
     </row>
     <row r="472">
-      <c r="A472" s="9"/>
+      <c r="A472" s="10"/>
     </row>
     <row r="473">
-      <c r="A473" s="9"/>
+      <c r="A473" s="10"/>
     </row>
     <row r="474">
-      <c r="A474" s="9"/>
+      <c r="A474" s="10"/>
     </row>
     <row r="475">
-      <c r="A475" s="9"/>
+      <c r="A475" s="10"/>
     </row>
     <row r="476">
-      <c r="A476" s="9"/>
+      <c r="A476" s="10"/>
     </row>
     <row r="477">
-      <c r="A477" s="9"/>
+      <c r="A477" s="10"/>
     </row>
     <row r="478">
-      <c r="A478" s="9"/>
+      <c r="A478" s="10"/>
     </row>
     <row r="479">
-      <c r="A479" s="9"/>
+      <c r="A479" s="10"/>
     </row>
     <row r="480">
-      <c r="A480" s="9"/>
+      <c r="A480" s="10"/>
     </row>
     <row r="481">
-      <c r="A481" s="9"/>
+      <c r="A481" s="10"/>
     </row>
     <row r="482">
-      <c r="A482" s="9"/>
+      <c r="A482" s="10"/>
     </row>
     <row r="483">
-      <c r="A483" s="9"/>
+      <c r="A483" s="10"/>
     </row>
     <row r="484">
-      <c r="A484" s="9"/>
+      <c r="A484" s="10"/>
     </row>
     <row r="485">
-      <c r="A485" s="9"/>
+      <c r="A485" s="10"/>
     </row>
     <row r="486">
-      <c r="A486" s="9"/>
+      <c r="A486" s="10"/>
     </row>
     <row r="487">
-      <c r="A487" s="9"/>
+      <c r="A487" s="10"/>
     </row>
     <row r="488">
-      <c r="A488" s="9"/>
+      <c r="A488" s="10"/>
     </row>
     <row r="489">
-      <c r="A489" s="9"/>
+      <c r="A489" s="10"/>
     </row>
     <row r="490">
-      <c r="A490" s="9"/>
+      <c r="A490" s="10"/>
     </row>
     <row r="491">
-      <c r="A491" s="9"/>
+      <c r="A491" s="10"/>
     </row>
     <row r="492">
-      <c r="A492" s="9"/>
+      <c r="A492" s="10"/>
     </row>
     <row r="493">
-      <c r="A493" s="9"/>
+      <c r="A493" s="10"/>
     </row>
     <row r="494">
-      <c r="A494" s="9"/>
+      <c r="A494" s="10"/>
     </row>
     <row r="495">
-      <c r="A495" s="9"/>
+      <c r="A495" s="10"/>
     </row>
     <row r="496">
-      <c r="A496" s="9"/>
+      <c r="A496" s="10"/>
     </row>
     <row r="497">
-      <c r="A497" s="9"/>
+      <c r="A497" s="10"/>
     </row>
     <row r="498">
-      <c r="A498" s="9"/>
+      <c r="A498" s="10"/>
     </row>
     <row r="499">
-      <c r="A499" s="9"/>
+      <c r="A499" s="10"/>
     </row>
     <row r="500">
-      <c r="A500" s="9"/>
+      <c r="A500" s="10"/>
     </row>
     <row r="501">
-      <c r="A501" s="9"/>
+      <c r="A501" s="10"/>
     </row>
     <row r="502">
-      <c r="A502" s="9"/>
+      <c r="A502" s="10"/>
     </row>
     <row r="503">
-      <c r="A503" s="9"/>
+      <c r="A503" s="10"/>
     </row>
     <row r="504">
-      <c r="A504" s="9"/>
+      <c r="A504" s="10"/>
     </row>
     <row r="505">
-      <c r="A505" s="9"/>
+      <c r="A505" s="10"/>
     </row>
     <row r="506">
-      <c r="A506" s="9"/>
+      <c r="A506" s="10"/>
     </row>
     <row r="507">
-      <c r="A507" s="9"/>
+      <c r="A507" s="10"/>
     </row>
     <row r="508">
-      <c r="A508" s="9"/>
+      <c r="A508" s="10"/>
     </row>
     <row r="509">
-      <c r="A509" s="9"/>
+      <c r="A509" s="10"/>
     </row>
     <row r="510">
-      <c r="A510" s="9"/>
+      <c r="A510" s="10"/>
     </row>
     <row r="511">
-      <c r="A511" s="9"/>
+      <c r="A511" s="10"/>
     </row>
     <row r="512">
-      <c r="A512" s="9"/>
+      <c r="A512" s="10"/>
     </row>
     <row r="513">
-      <c r="A513" s="9"/>
+      <c r="A513" s="10"/>
     </row>
     <row r="514">
-      <c r="A514" s="9"/>
+      <c r="A514" s="10"/>
     </row>
     <row r="515">
-      <c r="A515" s="9"/>
+      <c r="A515" s="10"/>
     </row>
     <row r="516">
-      <c r="A516" s="9"/>
+      <c r="A516" s="10"/>
     </row>
     <row r="517">
-      <c r="A517" s="9"/>
+      <c r="A517" s="10"/>
     </row>
     <row r="518">
-      <c r="A518" s="9"/>
+      <c r="A518" s="10"/>
     </row>
     <row r="519">
-      <c r="A519" s="9"/>
+      <c r="A519" s="10"/>
     </row>
     <row r="520">
-      <c r="A520" s="9"/>
+      <c r="A520" s="10"/>
     </row>
     <row r="521">
-      <c r="A521" s="9"/>
+      <c r="A521" s="10"/>
     </row>
     <row r="522">
-      <c r="A522" s="9"/>
+      <c r="A522" s="10"/>
     </row>
     <row r="523">
-      <c r="A523" s="9"/>
+      <c r="A523" s="10"/>
     </row>
     <row r="524">
-      <c r="A524" s="9"/>
+      <c r="A524" s="10"/>
     </row>
     <row r="525">
-      <c r="A525" s="9"/>
+      <c r="A525" s="10"/>
     </row>
     <row r="526">
-      <c r="A526" s="9"/>
+      <c r="A526" s="10"/>
     </row>
     <row r="527">
-      <c r="A527" s="9"/>
+      <c r="A527" s="10"/>
     </row>
     <row r="528">
-      <c r="A528" s="9"/>
+      <c r="A528" s="10"/>
     </row>
     <row r="529">
-      <c r="A529" s="9"/>
+      <c r="A529" s="10"/>
     </row>
     <row r="530">
-      <c r="A530" s="9"/>
+      <c r="A530" s="10"/>
     </row>
     <row r="531">
-      <c r="A531" s="9"/>
+      <c r="A531" s="10"/>
     </row>
     <row r="532">
-      <c r="A532" s="9"/>
+      <c r="A532" s="10"/>
     </row>
     <row r="533">
-      <c r="A533" s="9"/>
+      <c r="A533" s="10"/>
     </row>
     <row r="534">
-      <c r="A534" s="9"/>
+      <c r="A534" s="10"/>
     </row>
     <row r="535">
-      <c r="A535" s="9"/>
+      <c r="A535" s="10"/>
     </row>
     <row r="536">
-      <c r="A536" s="9"/>
+      <c r="A536" s="10"/>
     </row>
     <row r="537">
-      <c r="A537" s="9"/>
+      <c r="A537" s="10"/>
     </row>
     <row r="538">
-      <c r="A538" s="9"/>
+      <c r="A538" s="10"/>
     </row>
     <row r="539">
-      <c r="A539" s="9"/>
+      <c r="A539" s="10"/>
     </row>
     <row r="540">
-      <c r="A540" s="9"/>
+      <c r="A540" s="10"/>
     </row>
     <row r="541">
-      <c r="A541" s="9"/>
+      <c r="A541" s="10"/>
     </row>
     <row r="542">
-      <c r="A542" s="9"/>
+      <c r="A542" s="10"/>
     </row>
     <row r="543">
-      <c r="A543" s="9"/>
+      <c r="A543" s="10"/>
     </row>
     <row r="544">
-      <c r="A544" s="9"/>
+      <c r="A544" s="10"/>
     </row>
     <row r="545">
-      <c r="A545" s="9"/>
+      <c r="A545" s="10"/>
     </row>
     <row r="546">
-      <c r="A546" s="9"/>
+      <c r="A546" s="10"/>
     </row>
     <row r="547">
-      <c r="A547" s="9"/>
+      <c r="A547" s="10"/>
     </row>
     <row r="548">
-      <c r="A548" s="9"/>
+      <c r="A548" s="10"/>
     </row>
     <row r="549">
-      <c r="A549" s="9"/>
+      <c r="A549" s="10"/>
     </row>
     <row r="550">
-      <c r="A550" s="9"/>
+      <c r="A550" s="10"/>
     </row>
     <row r="551">
-      <c r="A551" s="9"/>
+      <c r="A551" s="10"/>
     </row>
     <row r="552">
-      <c r="A552" s="9"/>
+      <c r="A552" s="10"/>
     </row>
     <row r="553">
-      <c r="A553" s="9"/>
+      <c r="A553" s="10"/>
     </row>
     <row r="554">
-      <c r="A554" s="9"/>
+      <c r="A554" s="10"/>
     </row>
     <row r="555">
-      <c r="A555" s="9"/>
+      <c r="A555" s="10"/>
     </row>
     <row r="556">
-      <c r="A556" s="9"/>
+      <c r="A556" s="10"/>
     </row>
     <row r="557">
-      <c r="A557" s="9"/>
+      <c r="A557" s="10"/>
     </row>
     <row r="558">
-      <c r="A558" s="9"/>
+      <c r="A558" s="10"/>
     </row>
     <row r="559">
-      <c r="A559" s="9"/>
+      <c r="A559" s="10"/>
     </row>
     <row r="560">
-      <c r="A560" s="9"/>
+      <c r="A560" s="10"/>
     </row>
     <row r="561">
-      <c r="A561" s="9"/>
+      <c r="A561" s="10"/>
     </row>
     <row r="562">
-      <c r="A562" s="9"/>
+      <c r="A562" s="10"/>
     </row>
     <row r="563">
-      <c r="A563" s="9"/>
+      <c r="A563" s="10"/>
     </row>
     <row r="564">
-      <c r="A564" s="9"/>
+      <c r="A564" s="10"/>
     </row>
     <row r="565">
-      <c r="A565" s="9"/>
+      <c r="A565" s="10"/>
     </row>
     <row r="566">
-      <c r="A566" s="9"/>
+      <c r="A566" s="10"/>
     </row>
     <row r="567">
-      <c r="A567" s="9"/>
+      <c r="A567" s="10"/>
     </row>
     <row r="568">
-      <c r="A568" s="9"/>
+      <c r="A568" s="10"/>
     </row>
     <row r="569">
-      <c r="A569" s="9"/>
+      <c r="A569" s="10"/>
     </row>
     <row r="570">
-      <c r="A570" s="9"/>
+      <c r="A570" s="10"/>
     </row>
     <row r="571">
-      <c r="A571" s="9"/>
+      <c r="A571" s="10"/>
     </row>
     <row r="572">
-      <c r="A572" s="9"/>
+      <c r="A572" s="10"/>
     </row>
     <row r="573">
-      <c r="A573" s="9"/>
+      <c r="A573" s="10"/>
     </row>
     <row r="574">
-      <c r="A574" s="9"/>
+      <c r="A574" s="10"/>
     </row>
     <row r="575">
-      <c r="A575" s="9"/>
+      <c r="A575" s="10"/>
     </row>
     <row r="576">
-      <c r="A576" s="9"/>
+      <c r="A576" s="10"/>
     </row>
     <row r="577">
-      <c r="A577" s="9"/>
+      <c r="A577" s="10"/>
     </row>
     <row r="578">
-      <c r="A578" s="9"/>
+      <c r="A578" s="10"/>
     </row>
     <row r="579">
-      <c r="A579" s="9"/>
+      <c r="A579" s="10"/>
     </row>
     <row r="580">
-      <c r="A580" s="9"/>
+      <c r="A580" s="10"/>
     </row>
     <row r="581">
-      <c r="A581" s="9"/>
+      <c r="A581" s="10"/>
     </row>
     <row r="582">
-      <c r="A582" s="9"/>
+      <c r="A582" s="10"/>
     </row>
     <row r="583">
-      <c r="A583" s="9"/>
+      <c r="A583" s="10"/>
     </row>
     <row r="584">
-      <c r="A584" s="9"/>
+      <c r="A584" s="10"/>
     </row>
     <row r="585">
-      <c r="A585" s="9"/>
+      <c r="A585" s="10"/>
     </row>
     <row r="586">
-      <c r="A586" s="9"/>
+      <c r="A586" s="10"/>
     </row>
     <row r="587">
-      <c r="A587" s="9"/>
+      <c r="A587" s="10"/>
     </row>
     <row r="588">
-      <c r="A588" s="9"/>
+      <c r="A588" s="10"/>
     </row>
     <row r="589">
-      <c r="A589" s="9"/>
+      <c r="A589" s="10"/>
     </row>
     <row r="590">
-      <c r="A590" s="9"/>
+      <c r="A590" s="10"/>
     </row>
     <row r="591">
-      <c r="A591" s="9"/>
+      <c r="A591" s="10"/>
     </row>
     <row r="592">
-      <c r="A592" s="9"/>
+      <c r="A592" s="10"/>
     </row>
     <row r="593">
-      <c r="A593" s="9"/>
+      <c r="A593" s="10"/>
     </row>
     <row r="594">
-      <c r="A594" s="9"/>
+      <c r="A594" s="10"/>
     </row>
     <row r="595">
-      <c r="A595" s="9"/>
+      <c r="A595" s="10"/>
     </row>
     <row r="596">
-      <c r="A596" s="9"/>
+      <c r="A596" s="10"/>
     </row>
     <row r="597">
-      <c r="A597" s="9"/>
+      <c r="A597" s="10"/>
     </row>
     <row r="598">
-      <c r="A598" s="9"/>
+      <c r="A598" s="10"/>
     </row>
     <row r="599">
-      <c r="A599" s="9"/>
+      <c r="A599" s="10"/>
     </row>
     <row r="600">
-      <c r="A600" s="9"/>
+      <c r="A600" s="10"/>
     </row>
     <row r="601">
-      <c r="A601" s="9"/>
+      <c r="A601" s="10"/>
     </row>
     <row r="602">
-      <c r="A602" s="9"/>
+      <c r="A602" s="10"/>
     </row>
     <row r="603">
-      <c r="A603" s="9"/>
+      <c r="A603" s="10"/>
     </row>
     <row r="604">
-      <c r="A604" s="9"/>
+      <c r="A604" s="10"/>
     </row>
     <row r="605">
-      <c r="A605" s="9"/>
+      <c r="A605" s="10"/>
     </row>
     <row r="606">
-      <c r="A606" s="9"/>
+      <c r="A606" s="10"/>
     </row>
     <row r="607">
-      <c r="A607" s="9"/>
+      <c r="A607" s="10"/>
     </row>
     <row r="608">
-      <c r="A608" s="9"/>
+      <c r="A608" s="10"/>
     </row>
     <row r="609">
-      <c r="A609" s="9"/>
+      <c r="A609" s="10"/>
     </row>
     <row r="610">
-      <c r="A610" s="9"/>
+      <c r="A610" s="10"/>
     </row>
     <row r="611">
-      <c r="A611" s="9"/>
+      <c r="A611" s="10"/>
     </row>
     <row r="612">
-      <c r="A612" s="9"/>
+      <c r="A612" s="10"/>
     </row>
     <row r="613">
-      <c r="A613" s="9"/>
+      <c r="A613" s="10"/>
     </row>
     <row r="614">
-      <c r="A614" s="9"/>
+      <c r="A614" s="10"/>
     </row>
     <row r="615">
-      <c r="A615" s="9"/>
+      <c r="A615" s="10"/>
     </row>
     <row r="616">
-      <c r="A616" s="9"/>
+      <c r="A616" s="10"/>
     </row>
     <row r="617">
-      <c r="A617" s="9"/>
+      <c r="A617" s="10"/>
     </row>
     <row r="618">
-      <c r="A618" s="9"/>
+      <c r="A618" s="10"/>
     </row>
     <row r="619">
-      <c r="A619" s="9"/>
+      <c r="A619" s="10"/>
     </row>
     <row r="620">
-      <c r="A620" s="9"/>
+      <c r="A620" s="10"/>
     </row>
     <row r="621">
-      <c r="A621" s="9"/>
+      <c r="A621" s="10"/>
     </row>
     <row r="622">
-      <c r="A622" s="9"/>
+      <c r="A622" s="10"/>
     </row>
     <row r="623">
-      <c r="A623" s="9"/>
+      <c r="A623" s="10"/>
     </row>
     <row r="624">
-      <c r="A624" s="9"/>
+      <c r="A624" s="10"/>
     </row>
     <row r="625">
-      <c r="A625" s="9"/>
+      <c r="A625" s="10"/>
     </row>
     <row r="626">
-      <c r="A626" s="9"/>
+      <c r="A626" s="10"/>
     </row>
     <row r="627">
-      <c r="A627" s="9"/>
+      <c r="A627" s="10"/>
     </row>
     <row r="628">
-      <c r="A628" s="9"/>
+      <c r="A628" s="10"/>
     </row>
     <row r="629">
-      <c r="A629" s="9"/>
+      <c r="A629" s="10"/>
     </row>
     <row r="630">
-      <c r="A630" s="9"/>
+      <c r="A630" s="10"/>
     </row>
     <row r="631">
-      <c r="A631" s="9"/>
+      <c r="A631" s="10"/>
     </row>
     <row r="632">
-      <c r="A632" s="9"/>
+      <c r="A632" s="10"/>
     </row>
     <row r="633">
-      <c r="A633" s="9"/>
+      <c r="A633" s="10"/>
     </row>
     <row r="634">
-      <c r="A634" s="9"/>
+      <c r="A634" s="10"/>
     </row>
     <row r="635">
-      <c r="A635" s="9"/>
+      <c r="A635" s="10"/>
     </row>
     <row r="636">
-      <c r="A636" s="9"/>
+      <c r="A636" s="10"/>
     </row>
     <row r="637">
-      <c r="A637" s="9"/>
+      <c r="A637" s="10"/>
     </row>
     <row r="638">
-      <c r="A638" s="9"/>
+      <c r="A638" s="10"/>
     </row>
     <row r="639">
-      <c r="A639" s="9"/>
+      <c r="A639" s="10"/>
     </row>
     <row r="640">
-      <c r="A640" s="9"/>
+      <c r="A640" s="10"/>
     </row>
     <row r="641">
-      <c r="A641" s="9"/>
+      <c r="A641" s="10"/>
     </row>
     <row r="642">
-      <c r="A642" s="9"/>
+      <c r="A642" s="10"/>
     </row>
     <row r="643">
-      <c r="A643" s="9"/>
+      <c r="A643" s="10"/>
     </row>
     <row r="644">
-      <c r="A644" s="9"/>
+      <c r="A644" s="10"/>
     </row>
     <row r="645">
-      <c r="A645" s="9"/>
+      <c r="A645" s="10"/>
     </row>
     <row r="646">
-      <c r="A646" s="9"/>
+      <c r="A646" s="10"/>
     </row>
     <row r="647">
-      <c r="A647" s="9"/>
+      <c r="A647" s="10"/>
     </row>
     <row r="648">
-      <c r="A648" s="9"/>
+      <c r="A648" s="10"/>
     </row>
     <row r="649">
-      <c r="A649" s="9"/>
+      <c r="A649" s="10"/>
     </row>
     <row r="650">
-      <c r="A650" s="9"/>
+      <c r="A650" s="10"/>
     </row>
     <row r="651">
-      <c r="A651" s="9"/>
+      <c r="A651" s="10"/>
     </row>
     <row r="652">
-      <c r="A652" s="9"/>
+      <c r="A652" s="10"/>
     </row>
     <row r="653">
-      <c r="A653" s="9"/>
+      <c r="A653" s="10"/>
     </row>
     <row r="654">
-      <c r="A654" s="9"/>
+      <c r="A654" s="10"/>
     </row>
     <row r="655">
-      <c r="A655" s="9"/>
+      <c r="A655" s="10"/>
     </row>
     <row r="656">
-      <c r="A656" s="9"/>
+      <c r="A656" s="10"/>
     </row>
     <row r="657">
-      <c r="A657" s="9"/>
+      <c r="A657" s="10"/>
     </row>
     <row r="658">
-      <c r="A658" s="9"/>
+      <c r="A658" s="10"/>
     </row>
     <row r="659">
-      <c r="A659" s="9"/>
+      <c r="A659" s="10"/>
     </row>
     <row r="660">
-      <c r="A660" s="9"/>
+      <c r="A660" s="10"/>
     </row>
     <row r="661">
-      <c r="A661" s="9"/>
+      <c r="A661" s="10"/>
     </row>
     <row r="662">
-      <c r="A662" s="9"/>
+      <c r="A662" s="10"/>
     </row>
     <row r="663">
-      <c r="A663" s="9"/>
+      <c r="A663" s="10"/>
     </row>
     <row r="664">
-      <c r="A664" s="9"/>
+      <c r="A664" s="10"/>
     </row>
     <row r="665">
-      <c r="A665" s="9"/>
+      <c r="A665" s="10"/>
     </row>
     <row r="666">
-      <c r="A666" s="9"/>
+      <c r="A666" s="10"/>
     </row>
     <row r="667">
-      <c r="A667" s="9"/>
+      <c r="A667" s="10"/>
     </row>
     <row r="668">
-      <c r="A668" s="9"/>
+      <c r="A668" s="10"/>
     </row>
     <row r="669">
-      <c r="A669" s="9"/>
+      <c r="A669" s="10"/>
     </row>
     <row r="670">
-      <c r="A670" s="9"/>
+      <c r="A670" s="10"/>
     </row>
     <row r="671">
-      <c r="A671" s="9"/>
+      <c r="A671" s="10"/>
     </row>
     <row r="672">
-      <c r="A672" s="9"/>
+      <c r="A672" s="10"/>
     </row>
     <row r="673">
-      <c r="A673" s="9"/>
+      <c r="A673" s="10"/>
     </row>
     <row r="674">
-      <c r="A674" s="9"/>
+      <c r="A674" s="10"/>
     </row>
     <row r="675">
-      <c r="A675" s="9"/>
+      <c r="A675" s="10"/>
     </row>
     <row r="676">
-      <c r="A676" s="9"/>
+      <c r="A676" s="10"/>
     </row>
     <row r="677">
-      <c r="A677" s="9"/>
+      <c r="A677" s="10"/>
     </row>
     <row r="678">
-      <c r="A678" s="9"/>
+      <c r="A678" s="10"/>
     </row>
     <row r="679">
-      <c r="A679" s="9"/>
+      <c r="A679" s="10"/>
     </row>
     <row r="680">
-      <c r="A680" s="9"/>
+      <c r="A680" s="10"/>
     </row>
     <row r="681">
-      <c r="A681" s="9"/>
+      <c r="A681" s="10"/>
     </row>
     <row r="682">
-      <c r="A682" s="9"/>
+      <c r="A682" s="10"/>
     </row>
     <row r="683">
-      <c r="A683" s="9"/>
+      <c r="A683" s="10"/>
     </row>
     <row r="684">
-      <c r="A684" s="9"/>
+      <c r="A684" s="10"/>
     </row>
     <row r="685">
-      <c r="A685" s="9"/>
+      <c r="A685" s="10"/>
     </row>
     <row r="686">
-      <c r="A686" s="9"/>
+      <c r="A686" s="10"/>
     </row>
     <row r="687">
-      <c r="A687" s="9"/>
+      <c r="A687" s="10"/>
     </row>
     <row r="688">
-      <c r="A688" s="9"/>
+      <c r="A688" s="10"/>
     </row>
     <row r="689">
-      <c r="A689" s="9"/>
+      <c r="A689" s="10"/>
     </row>
     <row r="690">
-      <c r="A690" s="9"/>
+      <c r="A690" s="10"/>
     </row>
     <row r="691">
-      <c r="A691" s="9"/>
+      <c r="A691" s="10"/>
     </row>
     <row r="692">
-      <c r="A692" s="9"/>
+      <c r="A692" s="10"/>
     </row>
     <row r="693">
-      <c r="A693" s="9"/>
+      <c r="A693" s="10"/>
     </row>
     <row r="694">
-      <c r="A694" s="9"/>
+      <c r="A694" s="10"/>
     </row>
     <row r="695">
-      <c r="A695" s="9"/>
+      <c r="A695" s="10"/>
     </row>
     <row r="696">
-      <c r="A696" s="9"/>
+      <c r="A696" s="10"/>
     </row>
     <row r="697">
-      <c r="A697" s="9"/>
+      <c r="A697" s="10"/>
     </row>
     <row r="698">
-      <c r="A698" s="9"/>
+      <c r="A698" s="10"/>
     </row>
     <row r="699">
-      <c r="A699" s="9"/>
+      <c r="A699" s="10"/>
     </row>
     <row r="700">
-      <c r="A700" s="9"/>
+      <c r="A700" s="10"/>
     </row>
     <row r="701">
-      <c r="A701" s="9"/>
+      <c r="A701" s="10"/>
     </row>
     <row r="702">
-      <c r="A702" s="9"/>
+      <c r="A702" s="10"/>
     </row>
     <row r="703">
-      <c r="A703" s="9"/>
+      <c r="A703" s="10"/>
     </row>
     <row r="704">
-      <c r="A704" s="9"/>
+      <c r="A704" s="10"/>
     </row>
     <row r="705">
-      <c r="A705" s="9"/>
+      <c r="A705" s="10"/>
     </row>
     <row r="706">
-      <c r="A706" s="9"/>
+      <c r="A706" s="10"/>
     </row>
     <row r="707">
-      <c r="A707" s="9"/>
+      <c r="A707" s="10"/>
     </row>
     <row r="708">
-      <c r="A708" s="9"/>
+      <c r="A708" s="10"/>
     </row>
     <row r="709">
-      <c r="A709" s="9"/>
+      <c r="A709" s="10"/>
     </row>
     <row r="710">
-      <c r="A710" s="9"/>
+      <c r="A710" s="10"/>
     </row>
     <row r="711">
-      <c r="A711" s="9"/>
+      <c r="A711" s="10"/>
     </row>
     <row r="712">
-      <c r="A712" s="9"/>
+      <c r="A712" s="10"/>
     </row>
     <row r="713">
-      <c r="A713" s="9"/>
+      <c r="A713" s="10"/>
     </row>
     <row r="714">
-      <c r="A714" s="9"/>
+      <c r="A714" s="10"/>
     </row>
     <row r="715">
-      <c r="A715" s="9"/>
+      <c r="A715" s="10"/>
     </row>
     <row r="716">
-      <c r="A716" s="9"/>
+      <c r="A716" s="10"/>
     </row>
     <row r="717">
-      <c r="A717" s="9"/>
+      <c r="A717" s="10"/>
     </row>
     <row r="718">
-      <c r="A718" s="9"/>
+      <c r="A718" s="10"/>
     </row>
     <row r="719">
-      <c r="A719" s="9"/>
+      <c r="A719" s="10"/>
     </row>
     <row r="720">
-      <c r="A720" s="9"/>
+      <c r="A720" s="10"/>
     </row>
     <row r="721">
-      <c r="A721" s="9"/>
+      <c r="A721" s="10"/>
     </row>
     <row r="722">
-      <c r="A722" s="9"/>
+      <c r="A722" s="10"/>
     </row>
     <row r="723">
-      <c r="A723" s="9"/>
+      <c r="A723" s="10"/>
     </row>
     <row r="724">
-      <c r="A724" s="9"/>
+      <c r="A724" s="10"/>
     </row>
     <row r="725">
-      <c r="A725" s="9"/>
+      <c r="A725" s="10"/>
     </row>
     <row r="726">
-      <c r="A726" s="9"/>
+      <c r="A726" s="10"/>
     </row>
     <row r="727">
-      <c r="A727" s="9"/>
+      <c r="A727" s="10"/>
     </row>
     <row r="728">
-      <c r="A728" s="9"/>
+      <c r="A728" s="10"/>
     </row>
     <row r="729">
-      <c r="A729" s="9"/>
+      <c r="A729" s="10"/>
     </row>
     <row r="730">
-      <c r="A730" s="9"/>
+      <c r="A730" s="10"/>
     </row>
     <row r="731">
-      <c r="A731" s="9"/>
+      <c r="A731" s="10"/>
     </row>
     <row r="732">
-      <c r="A732" s="9"/>
+      <c r="A732" s="10"/>
     </row>
     <row r="733">
-      <c r="A733" s="9"/>
+      <c r="A733" s="10"/>
     </row>
     <row r="734">
-      <c r="A734" s="9"/>
+      <c r="A734" s="10"/>
     </row>
     <row r="735">
-      <c r="A735" s="9"/>
+      <c r="A735" s="10"/>
     </row>
     <row r="736">
-      <c r="A736" s="9"/>
+      <c r="A736" s="10"/>
     </row>
     <row r="737">
-      <c r="A737" s="9"/>
+      <c r="A737" s="10"/>
     </row>
     <row r="738">
-      <c r="A738" s="9"/>
+      <c r="A738" s="10"/>
     </row>
     <row r="739">
-      <c r="A739" s="9"/>
+      <c r="A739" s="10"/>
     </row>
     <row r="740">
-      <c r="A740" s="9"/>
+      <c r="A740" s="10"/>
     </row>
     <row r="741">
-      <c r="A741" s="9"/>
+      <c r="A741" s="10"/>
     </row>
     <row r="742">
-      <c r="A742" s="9"/>
+      <c r="A742" s="10"/>
     </row>
     <row r="743">
-      <c r="A743" s="9"/>
+      <c r="A743" s="10"/>
     </row>
     <row r="744">
-      <c r="A744" s="9"/>
+      <c r="A744" s="10"/>
     </row>
     <row r="745">
-      <c r="A745" s="9"/>
+      <c r="A745" s="10"/>
     </row>
     <row r="746">
-      <c r="A746" s="9"/>
+      <c r="A746" s="10"/>
     </row>
     <row r="747">
-      <c r="A747" s="9"/>
+      <c r="A747" s="10"/>
     </row>
     <row r="748">
-      <c r="A748" s="9"/>
+      <c r="A748" s="10"/>
     </row>
     <row r="749">
-      <c r="A749" s="9"/>
+      <c r="A749" s="10"/>
     </row>
     <row r="750">
-      <c r="A750" s="9"/>
+      <c r="A750" s="10"/>
     </row>
     <row r="751">
-      <c r="A751" s="9"/>
+      <c r="A751" s="10"/>
     </row>
     <row r="752">
-      <c r="A752" s="9"/>
+      <c r="A752" s="10"/>
     </row>
     <row r="753">
-      <c r="A753" s="9"/>
+      <c r="A753" s="10"/>
     </row>
     <row r="754">
-      <c r="A754" s="9"/>
+      <c r="A754" s="10"/>
     </row>
     <row r="755">
-      <c r="A755" s="9"/>
+      <c r="A755" s="10"/>
     </row>
     <row r="756">
-      <c r="A756" s="9"/>
+      <c r="A756" s="10"/>
     </row>
     <row r="757">
-      <c r="A757" s="9"/>
+      <c r="A757" s="10"/>
     </row>
     <row r="758">
-      <c r="A758" s="9"/>
+      <c r="A758" s="10"/>
     </row>
     <row r="759">
-      <c r="A759" s="9"/>
+      <c r="A759" s="10"/>
     </row>
     <row r="760">
-      <c r="A760" s="9"/>
+      <c r="A760" s="10"/>
     </row>
     <row r="761">
-      <c r="A761" s="9"/>
+      <c r="A761" s="10"/>
     </row>
     <row r="762">
-      <c r="A762" s="9"/>
+      <c r="A762" s="10"/>
     </row>
     <row r="763">
-      <c r="A763" s="9"/>
+      <c r="A763" s="10"/>
     </row>
     <row r="764">
-      <c r="A764" s="9"/>
+      <c r="A764" s="10"/>
     </row>
     <row r="765">
-      <c r="A765" s="9"/>
+      <c r="A765" s="10"/>
     </row>
     <row r="766">
-      <c r="A766" s="9"/>
+      <c r="A766" s="10"/>
     </row>
     <row r="767">
-      <c r="A767" s="9"/>
+      <c r="A767" s="10"/>
     </row>
     <row r="768">
-      <c r="A768" s="9"/>
+      <c r="A768" s="10"/>
     </row>
     <row r="769">
-      <c r="A769" s="9"/>
+      <c r="A769" s="10"/>
     </row>
     <row r="770">
-      <c r="A770" s="9"/>
+      <c r="A770" s="10"/>
     </row>
     <row r="771">
-      <c r="A771" s="9"/>
+      <c r="A771" s="10"/>
     </row>
     <row r="772">
-      <c r="A772" s="9"/>
+      <c r="A772" s="10"/>
     </row>
     <row r="773">
-      <c r="A773" s="9"/>
+      <c r="A773" s="10"/>
     </row>
     <row r="774">
-      <c r="A774" s="9"/>
+      <c r="A774" s="10"/>
     </row>
     <row r="775">
-      <c r="A775" s="9"/>
+      <c r="A775" s="10"/>
     </row>
     <row r="776">
-      <c r="A776" s="9"/>
+      <c r="A776" s="10"/>
     </row>
     <row r="777">
-      <c r="A777" s="9"/>
+      <c r="A777" s="10"/>
     </row>
     <row r="778">
-      <c r="A778" s="9"/>
+      <c r="A778" s="10"/>
     </row>
     <row r="779">
-      <c r="A779" s="9"/>
+      <c r="A779" s="10"/>
     </row>
     <row r="780">
-      <c r="A780" s="9"/>
+      <c r="A780" s="10"/>
     </row>
     <row r="781">
-      <c r="A781" s="9"/>
+      <c r="A781" s="10"/>
     </row>
     <row r="782">
-      <c r="A782" s="9"/>
+      <c r="A782" s="10"/>
     </row>
     <row r="783">
-      <c r="A783" s="9"/>
+      <c r="A783" s="10"/>
     </row>
     <row r="784">
-      <c r="A784" s="9"/>
+      <c r="A784" s="10"/>
     </row>
     <row r="785">
-      <c r="A785" s="9"/>
+      <c r="A785" s="10"/>
     </row>
     <row r="786">
-      <c r="A786" s="9"/>
+      <c r="A786" s="10"/>
     </row>
     <row r="787">
-      <c r="A787" s="9"/>
+      <c r="A787" s="10"/>
     </row>
     <row r="788">
-      <c r="A788" s="9"/>
+      <c r="A788" s="10"/>
     </row>
     <row r="789">
-      <c r="A789" s="9"/>
+      <c r="A789" s="10"/>
     </row>
     <row r="790">
-      <c r="A790" s="9"/>
+      <c r="A790" s="10"/>
     </row>
     <row r="791">
-      <c r="A791" s="9"/>
+      <c r="A791" s="10"/>
     </row>
     <row r="792">
-      <c r="A792" s="9"/>
+      <c r="A792" s="10"/>
     </row>
     <row r="793">
-      <c r="A793" s="9"/>
+      <c r="A793" s="10"/>
     </row>
     <row r="794">
-      <c r="A794" s="9"/>
+      <c r="A794" s="10"/>
     </row>
     <row r="795">
-      <c r="A795" s="9"/>
+      <c r="A795" s="10"/>
     </row>
     <row r="796">
-      <c r="A796" s="9"/>
+      <c r="A796" s="10"/>
     </row>
     <row r="797">
-      <c r="A797" s="9"/>
+      <c r="A797" s="10"/>
     </row>
     <row r="798">
-      <c r="A798" s="9"/>
+      <c r="A798" s="10"/>
     </row>
     <row r="799">
-      <c r="A799" s="9"/>
+      <c r="A799" s="10"/>
     </row>
     <row r="800">
-      <c r="A800" s="9"/>
+      <c r="A800" s="10"/>
     </row>
     <row r="801">
-      <c r="A801" s="9"/>
+      <c r="A801" s="10"/>
     </row>
     <row r="802">
-      <c r="A802" s="9"/>
+      <c r="A802" s="10"/>
     </row>
     <row r="803">
-      <c r="A803" s="9"/>
+      <c r="A803" s="10"/>
     </row>
     <row r="804">
-      <c r="A804" s="9"/>
+      <c r="A804" s="10"/>
     </row>
     <row r="805">
-      <c r="A805" s="9"/>
+      <c r="A805" s="10"/>
     </row>
     <row r="806">
-      <c r="A806" s="9"/>
+      <c r="A806" s="10"/>
     </row>
     <row r="807">
-      <c r="A807" s="9"/>
+      <c r="A807" s="10"/>
     </row>
     <row r="808">
-      <c r="A808" s="9"/>
+      <c r="A808" s="10"/>
     </row>
     <row r="809">
-      <c r="A809" s="9"/>
+      <c r="A809" s="10"/>
     </row>
     <row r="810">
-      <c r="A810" s="9"/>
+      <c r="A810" s="10"/>
     </row>
     <row r="811">
-      <c r="A811" s="9"/>
+      <c r="A811" s="10"/>
     </row>
     <row r="812">
-      <c r="A812" s="9"/>
+      <c r="A812" s="10"/>
     </row>
     <row r="813">
-      <c r="A813" s="9"/>
+      <c r="A813" s="10"/>
     </row>
     <row r="814">
-      <c r="A814" s="9"/>
+      <c r="A814" s="10"/>
     </row>
     <row r="815">
-      <c r="A815" s="9"/>
+      <c r="A815" s="10"/>
     </row>
     <row r="816">
-      <c r="A816" s="9"/>
+      <c r="A816" s="10"/>
     </row>
     <row r="817">
-      <c r="A817" s="9"/>
+      <c r="A817" s="10"/>
     </row>
     <row r="818">
-      <c r="A818" s="9"/>
+      <c r="A818" s="10"/>
     </row>
     <row r="819">
-      <c r="A819" s="9"/>
+      <c r="A819" s="10"/>
     </row>
     <row r="820">
-      <c r="A820" s="9"/>
+      <c r="A820" s="10"/>
     </row>
     <row r="821">
-      <c r="A821" s="9"/>
+      <c r="A821" s="10"/>
     </row>
     <row r="822">
-      <c r="A822" s="9"/>
+      <c r="A822" s="10"/>
     </row>
     <row r="823">
-      <c r="A823" s="9"/>
+      <c r="A823" s="10"/>
     </row>
     <row r="824">
-      <c r="A824" s="9"/>
+      <c r="A824" s="10"/>
     </row>
     <row r="825">
-      <c r="A825" s="9"/>
+      <c r="A825" s="10"/>
     </row>
     <row r="826">
-      <c r="A826" s="9"/>
+      <c r="A826" s="10"/>
     </row>
     <row r="827">
-      <c r="A827" s="9"/>
+      <c r="A827" s="10"/>
     </row>
     <row r="828">
-      <c r="A828" s="9"/>
+      <c r="A828" s="10"/>
     </row>
     <row r="829">
-      <c r="A829" s="9"/>
+      <c r="A829" s="10"/>
     </row>
     <row r="830">
-      <c r="A830" s="9"/>
+      <c r="A830" s="10"/>
     </row>
     <row r="831">
-      <c r="A831" s="9"/>
+      <c r="A831" s="10"/>
     </row>
     <row r="832">
-      <c r="A832" s="9"/>
+      <c r="A832" s="10"/>
     </row>
     <row r="833">
-      <c r="A833" s="9"/>
+      <c r="A833" s="10"/>
     </row>
     <row r="834">
-      <c r="A834" s="9"/>
+      <c r="A834" s="10"/>
     </row>
     <row r="835">
-      <c r="A835" s="9"/>
+      <c r="A835" s="10"/>
     </row>
     <row r="836">
-      <c r="A836" s="9"/>
+      <c r="A836" s="10"/>
     </row>
     <row r="837">
-      <c r="A837" s="9"/>
+      <c r="A837" s="10"/>
     </row>
     <row r="838">
-      <c r="A838" s="9"/>
+      <c r="A838" s="10"/>
     </row>
     <row r="839">
-      <c r="A839" s="9"/>
+      <c r="A839" s="10"/>
     </row>
     <row r="840">
-      <c r="A840" s="9"/>
+      <c r="A840" s="10"/>
     </row>
     <row r="841">
-      <c r="A841" s="9"/>
+      <c r="A841" s="10"/>
     </row>
     <row r="842">
-      <c r="A842" s="9"/>
+      <c r="A842" s="10"/>
     </row>
     <row r="843">
-      <c r="A843" s="9"/>
+      <c r="A843" s="10"/>
     </row>
     <row r="844">
-      <c r="A844" s="9"/>
+      <c r="A844" s="10"/>
     </row>
     <row r="845">
-      <c r="A845" s="9"/>
+      <c r="A845" s="10"/>
     </row>
     <row r="846">
-      <c r="A846" s="9"/>
+      <c r="A846" s="10"/>
     </row>
     <row r="847">
-      <c r="A847" s="9"/>
+      <c r="A847" s="10"/>
     </row>
     <row r="848">
-      <c r="A848" s="9"/>
+      <c r="A848" s="10"/>
     </row>
     <row r="849">
-      <c r="A849" s="9"/>
+      <c r="A849" s="10"/>
     </row>
     <row r="850">
-      <c r="A850" s="9"/>
+      <c r="A850" s="10"/>
     </row>
     <row r="851">
-      <c r="A851" s="9"/>
+      <c r="A851" s="10"/>
     </row>
     <row r="852">
-      <c r="A852" s="9"/>
+      <c r="A852" s="10"/>
     </row>
     <row r="853">
-      <c r="A853" s="9"/>
+      <c r="A853" s="10"/>
     </row>
     <row r="854">
-      <c r="A854" s="9"/>
+      <c r="A854" s="10"/>
     </row>
     <row r="855">
-      <c r="A855" s="9"/>
+      <c r="A855" s="10"/>
     </row>
     <row r="856">
-      <c r="A856" s="9"/>
+      <c r="A856" s="10"/>
     </row>
     <row r="857">
-      <c r="A857" s="9"/>
+      <c r="A857" s="10"/>
     </row>
     <row r="858">
-      <c r="A858" s="9"/>
+      <c r="A858" s="10"/>
     </row>
     <row r="859">
-      <c r="A859" s="9"/>
+      <c r="A859" s="10"/>
     </row>
     <row r="860">
-      <c r="A860" s="9"/>
+      <c r="A860" s="10"/>
     </row>
     <row r="861">
-      <c r="A861" s="9"/>
+      <c r="A861" s="10"/>
     </row>
     <row r="862">
-      <c r="A862" s="9"/>
+      <c r="A862" s="10"/>
     </row>
     <row r="863">
-      <c r="A863" s="9"/>
+      <c r="A863" s="10"/>
     </row>
     <row r="864">
-      <c r="A864" s="9"/>
+      <c r="A864" s="10"/>
     </row>
     <row r="865">
-      <c r="A865" s="9"/>
+      <c r="A865" s="10"/>
     </row>
     <row r="866">
-      <c r="A866" s="9"/>
+      <c r="A866" s="10"/>
     </row>
     <row r="867">
-      <c r="A867" s="9"/>
+      <c r="A867" s="10"/>
     </row>
     <row r="868">
-      <c r="A868" s="9"/>
+      <c r="A868" s="10"/>
     </row>
     <row r="869">
-      <c r="A869" s="9"/>
+      <c r="A869" s="10"/>
     </row>
     <row r="870">
-      <c r="A870" s="9"/>
+      <c r="A870" s="10"/>
     </row>
     <row r="871">
-      <c r="A871" s="9"/>
+      <c r="A871" s="10"/>
     </row>
     <row r="872">
-      <c r="A872" s="9"/>
+      <c r="A872" s="10"/>
     </row>
     <row r="873">
-      <c r="A873" s="9"/>
+      <c r="A873" s="10"/>
     </row>
     <row r="874">
-      <c r="A874" s="9"/>
+      <c r="A874" s="10"/>
     </row>
     <row r="875">
-      <c r="A875" s="9"/>
+      <c r="A875" s="10"/>
     </row>
     <row r="876">
-      <c r="A876" s="9"/>
+      <c r="A876" s="10"/>
     </row>
     <row r="877">
-      <c r="A877" s="9"/>
+      <c r="A877" s="10"/>
     </row>
     <row r="878">
-      <c r="A878" s="9"/>
+      <c r="A878" s="10"/>
     </row>
     <row r="879">
-      <c r="A879" s="9"/>
+      <c r="A879" s="10"/>
     </row>
     <row r="880">
-      <c r="A880" s="9"/>
+      <c r="A880" s="10"/>
     </row>
     <row r="881">
-      <c r="A881" s="9"/>
+      <c r="A881" s="10"/>
     </row>
     <row r="882">
-      <c r="A882" s="9"/>
+      <c r="A882" s="10"/>
     </row>
     <row r="883">
-      <c r="A883" s="9"/>
+      <c r="A883" s="10"/>
     </row>
     <row r="884">
-      <c r="A884" s="9"/>
+      <c r="A884" s="10"/>
     </row>
     <row r="885">
-      <c r="A885" s="9"/>
+      <c r="A885" s="10"/>
     </row>
     <row r="886">
-      <c r="A886" s="9"/>
+      <c r="A886" s="10"/>
     </row>
     <row r="887">
-      <c r="A887" s="9"/>
+      <c r="A887" s="10"/>
     </row>
     <row r="888">
-      <c r="A888" s="9"/>
+      <c r="A888" s="10"/>
     </row>
     <row r="889">
-      <c r="A889" s="9"/>
+      <c r="A889" s="10"/>
     </row>
     <row r="890">
-      <c r="A890" s="9"/>
+      <c r="A890" s="10"/>
     </row>
     <row r="891">
-      <c r="A891" s="9"/>
+      <c r="A891" s="10"/>
     </row>
     <row r="892">
-      <c r="A892" s="9"/>
+      <c r="A892" s="10"/>
     </row>
     <row r="893">
-      <c r="A893" s="9"/>
+      <c r="A893" s="10"/>
     </row>
     <row r="894">
-      <c r="A894" s="9"/>
+      <c r="A894" s="10"/>
     </row>
     <row r="895">
-      <c r="A895" s="9"/>
+      <c r="A895" s="10"/>
     </row>
     <row r="896">
-      <c r="A896" s="9"/>
+      <c r="A896" s="10"/>
     </row>
     <row r="897">
-      <c r="A897" s="9"/>
+      <c r="A897" s="10"/>
     </row>
     <row r="898">
-      <c r="A898" s="9"/>
+      <c r="A898" s="10"/>
     </row>
     <row r="899">
-      <c r="A899" s="9"/>
+      <c r="A899" s="10"/>
     </row>
     <row r="900">
-      <c r="A900" s="9"/>
+      <c r="A900" s="10"/>
     </row>
     <row r="901">
-      <c r="A901" s="9"/>
+      <c r="A901" s="10"/>
     </row>
     <row r="902">
-      <c r="A902" s="9"/>
+      <c r="A902" s="10"/>
     </row>
     <row r="903">
-      <c r="A903" s="9"/>
+      <c r="A903" s="10"/>
     </row>
     <row r="904">
-      <c r="A904" s="9"/>
+      <c r="A904" s="10"/>
     </row>
     <row r="905">
-      <c r="A905" s="9"/>
+      <c r="A905" s="10"/>
     </row>
     <row r="906">
-      <c r="A906" s="9"/>
+      <c r="A906" s="10"/>
     </row>
     <row r="907">
-      <c r="A907" s="9"/>
+      <c r="A907" s="10"/>
     </row>
     <row r="908">
-      <c r="A908" s="9"/>
+      <c r="A908" s="10"/>
     </row>
     <row r="909">
-      <c r="A909" s="9"/>
+      <c r="A909" s="10"/>
     </row>
     <row r="910">
-      <c r="A910" s="9"/>
+      <c r="A910" s="10"/>
     </row>
     <row r="911">
-      <c r="A911" s="9"/>
+      <c r="A911" s="10"/>
     </row>
     <row r="912">
-      <c r="A912" s="9"/>
+      <c r="A912" s="10"/>
     </row>
     <row r="913">
-      <c r="A913" s="9"/>
+      <c r="A913" s="10"/>
     </row>
     <row r="914">
-      <c r="A914" s="9"/>
+      <c r="A914" s="10"/>
     </row>
     <row r="915">
-      <c r="A915" s="9"/>
+      <c r="A915" s="10"/>
     </row>
     <row r="916">
-      <c r="A916" s="9"/>
+      <c r="A916" s="10"/>
     </row>
     <row r="917">
-      <c r="A917" s="9"/>
+      <c r="A917" s="10"/>
     </row>
     <row r="918">
-      <c r="A918" s="9"/>
+      <c r="A918" s="10"/>
     </row>
     <row r="919">
-      <c r="A919" s="9"/>
+      <c r="A919" s="10"/>
     </row>
     <row r="920">
-      <c r="A920" s="9"/>
+      <c r="A920" s="10"/>
     </row>
     <row r="921">
-      <c r="A921" s="9"/>
+      <c r="A921" s="10"/>
     </row>
     <row r="922">
-      <c r="A922" s="9"/>
+      <c r="A922" s="10"/>
     </row>
     <row r="923">
-      <c r="A923" s="9"/>
+      <c r="A923" s="10"/>
     </row>
     <row r="924">
-      <c r="A924" s="9"/>
+      <c r="A924" s="10"/>
     </row>
     <row r="925">
-      <c r="A925" s="9"/>
+      <c r="A925" s="10"/>
     </row>
     <row r="926">
-      <c r="A926" s="9"/>
+      <c r="A926" s="10"/>
     </row>
     <row r="927">
-      <c r="A927" s="9"/>
+      <c r="A927" s="10"/>
     </row>
     <row r="928">
-      <c r="A928" s="9"/>
+      <c r="A928" s="10"/>
     </row>
     <row r="929">
-      <c r="A929" s="9"/>
+      <c r="A929" s="10"/>
     </row>
     <row r="930">
-      <c r="A930" s="9"/>
+      <c r="A930" s="10"/>
     </row>
     <row r="931">
-      <c r="A931" s="9"/>
+      <c r="A931" s="10"/>
     </row>
     <row r="932">
-      <c r="A932" s="9"/>
+      <c r="A932" s="10"/>
     </row>
     <row r="933">
-      <c r="A933" s="9"/>
+      <c r="A933" s="10"/>
     </row>
     <row r="934">
-      <c r="A934" s="9"/>
+      <c r="A934" s="10"/>
     </row>
     <row r="935">
-      <c r="A935" s="9"/>
+      <c r="A935" s="10"/>
     </row>
     <row r="936">
-      <c r="A936" s="9"/>
+      <c r="A936" s="10"/>
     </row>
     <row r="937">
-      <c r="A937" s="9"/>
+      <c r="A937" s="10"/>
     </row>
     <row r="938">
-      <c r="A938" s="9"/>
+      <c r="A938" s="10"/>
     </row>
     <row r="939">
-      <c r="A939" s="9"/>
+      <c r="A939" s="10"/>
     </row>
     <row r="940">
-      <c r="A940" s="9"/>
+      <c r="A940" s="10"/>
     </row>
     <row r="941">
-      <c r="A941" s="9"/>
+      <c r="A941" s="10"/>
     </row>
     <row r="942">
-      <c r="A942" s="9"/>
+      <c r="A942" s="10"/>
     </row>
     <row r="943">
-      <c r="A943" s="9"/>
+      <c r="A943" s="10"/>
     </row>
     <row r="944">
-      <c r="A944" s="9"/>
+      <c r="A944" s="10"/>
     </row>
     <row r="945">
-      <c r="A945" s="9"/>
+      <c r="A945" s="10"/>
     </row>
     <row r="946">
-      <c r="A946" s="9"/>
+      <c r="A946" s="10"/>
     </row>
     <row r="947">
-      <c r="A947" s="9"/>
+      <c r="A947" s="10"/>
     </row>
     <row r="948">
-      <c r="A948" s="9"/>
+      <c r="A948" s="10"/>
     </row>
     <row r="949">
-      <c r="A949" s="9"/>
+      <c r="A949" s="10"/>
     </row>
     <row r="950">
-      <c r="A950" s="9"/>
+      <c r="A950" s="10"/>
     </row>
     <row r="951">
-      <c r="A951" s="9"/>
+      <c r="A951" s="10"/>
     </row>
     <row r="952">
-      <c r="A952" s="9"/>
+      <c r="A952" s="10"/>
     </row>
     <row r="953">
-      <c r="A953" s="9"/>
+      <c r="A953" s="10"/>
     </row>
     <row r="954">
-      <c r="A954" s="9"/>
+      <c r="A954" s="10"/>
     </row>
     <row r="955">
-      <c r="A955" s="9"/>
+      <c r="A955" s="10"/>
     </row>
     <row r="956">
-      <c r="A956" s="9"/>
+      <c r="A956" s="10"/>
     </row>
     <row r="957">
-      <c r="A957" s="9"/>
+      <c r="A957" s="10"/>
     </row>
     <row r="958">
-      <c r="A958" s="9"/>
+      <c r="A958" s="10"/>
     </row>
     <row r="959">
-      <c r="A959" s="9"/>
+      <c r="A959" s="10"/>
     </row>
     <row r="960">
-      <c r="A960" s="9"/>
+      <c r="A960" s="10"/>
     </row>
     <row r="961">
-      <c r="A961" s="9"/>
+      <c r="A961" s="10"/>
     </row>
     <row r="962">
-      <c r="A962" s="9"/>
+      <c r="A962" s="10"/>
     </row>
     <row r="963">
-      <c r="A963" s="9"/>
+      <c r="A963" s="10"/>
     </row>
     <row r="964">
-      <c r="A964" s="9"/>
+      <c r="A964" s="10"/>
     </row>
     <row r="965">
-      <c r="A965" s="9"/>
+      <c r="A965" s="10"/>
     </row>
     <row r="966">
-      <c r="A966" s="9"/>
+      <c r="A966" s="10"/>
     </row>
     <row r="967">
-      <c r="A967" s="9"/>
+      <c r="A967" s="10"/>
     </row>
     <row r="968">
-      <c r="A968" s="9"/>
+      <c r="A968" s="10"/>
     </row>
     <row r="969">
-      <c r="A969" s="9"/>
+      <c r="A969" s="10"/>
     </row>
     <row r="970">
-      <c r="A970" s="9"/>
+      <c r="A970" s="10"/>
     </row>
     <row r="971">
-      <c r="A971" s="9"/>
+      <c r="A971" s="10"/>
     </row>
     <row r="972">
-      <c r="A972" s="9"/>
+      <c r="A972" s="10"/>
     </row>
     <row r="973">
-      <c r="A973" s="9"/>
+      <c r="A973" s="10"/>
     </row>
     <row r="974">
-      <c r="A974" s="9"/>
+      <c r="A974" s="10"/>
     </row>
     <row r="975">
-      <c r="A975" s="9"/>
+      <c r="A975" s="10"/>
     </row>
     <row r="976">
-      <c r="A976" s="9"/>
+      <c r="A976" s="10"/>
     </row>
     <row r="977">
-      <c r="A977" s="9"/>
+      <c r="A977" s="10"/>
     </row>
     <row r="978">
-      <c r="A978" s="9"/>
+      <c r="A978" s="10"/>
     </row>
     <row r="979">
-      <c r="A979" s="9"/>
+      <c r="A979" s="10"/>
     </row>
     <row r="980">
-      <c r="A980" s="9"/>
+      <c r="A980" s="10"/>
     </row>
     <row r="981">
-      <c r="A981" s="9"/>
+      <c r="A981" s="10"/>
     </row>
     <row r="982">
-      <c r="A982" s="9"/>
+      <c r="A982" s="10"/>
     </row>
     <row r="983">
-      <c r="A983" s="9"/>
+      <c r="A983" s="10"/>
     </row>
     <row r="984">
-      <c r="A984" s="9"/>
+      <c r="A984" s="10"/>
     </row>
     <row r="985">
-      <c r="A985" s="9"/>
+      <c r="A985" s="10"/>
     </row>
     <row r="986">
-      <c r="A986" s="9"/>
+      <c r="A986" s="10"/>
     </row>
     <row r="987">
-      <c r="A987" s="9"/>
+      <c r="A987" s="10"/>
     </row>
     <row r="988">
-      <c r="A988" s="9"/>
+      <c r="A988" s="10"/>
     </row>
     <row r="989">
-      <c r="A989" s="9"/>
+      <c r="A989" s="10"/>
     </row>
     <row r="990">
-      <c r="A990" s="9"/>
+      <c r="A990" s="10"/>
     </row>
     <row r="991">
-      <c r="A991" s="9"/>
+      <c r="A991" s="10"/>
     </row>
     <row r="992">
-      <c r="A992" s="9"/>
+      <c r="A992" s="10"/>
     </row>
     <row r="993">
-      <c r="A993" s="9"/>
+      <c r="A993" s="10"/>
     </row>
     <row r="994">
-      <c r="A994" s="9"/>
+      <c r="A994" s="10"/>
     </row>
     <row r="995">
-      <c r="A995" s="9"/>
+      <c r="A995" s="10"/>
     </row>
     <row r="996">
-      <c r="A996" s="9"/>
+      <c r="A996" s="10"/>
     </row>
     <row r="997">
-      <c r="A997" s="9"/>
+      <c r="A997" s="10"/>
     </row>
     <row r="998">
-      <c r="A998" s="9"/>
+      <c r="A998" s="10"/>
     </row>
     <row r="999">
-      <c r="A999" s="9"/>
+      <c r="A999" s="10"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="9"/>
+      <c r="A1000" s="10"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="9"/>
+      <c r="A1001" s="10"/>
     </row>
     <row r="1002">
-      <c r="A1002" s="9"/>
+      <c r="A1002" s="10"/>
     </row>
     <row r="1003">
-      <c r="A1003" s="9"/>
+      <c r="A1003" s="10"/>
     </row>
     <row r="1004">
-      <c r="A1004" s="9"/>
+      <c r="A1004" s="10"/>
     </row>
     <row r="1005">
-      <c r="A1005" s="9"/>
+      <c r="A1005" s="10"/>
     </row>
     <row r="1006">
-      <c r="A1006" s="9"/>
+      <c r="A1006" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$V$72"/>
+  <autoFilter ref="$A$1:$V$74"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="N2"/>
     <hyperlink r:id="rId2" ref="O2"/>
@@ -7389,157 +7487,161 @@
     <hyperlink r:id="rId45" ref="P16"/>
     <hyperlink r:id="rId46" ref="O17"/>
     <hyperlink r:id="rId47" ref="P17"/>
-    <hyperlink r:id="rId48" ref="N18"/>
-    <hyperlink r:id="rId49" ref="O18"/>
-    <hyperlink r:id="rId50" ref="P18"/>
-    <hyperlink r:id="rId51" ref="N19"/>
-    <hyperlink r:id="rId52" ref="O19"/>
-    <hyperlink r:id="rId53" ref="P19"/>
-    <hyperlink r:id="rId54" ref="N20"/>
-    <hyperlink r:id="rId55" ref="O20"/>
-    <hyperlink r:id="rId56" ref="P20"/>
-    <hyperlink r:id="rId57" ref="N21"/>
+    <hyperlink r:id="rId48" ref="O18"/>
+    <hyperlink r:id="rId49" ref="P18"/>
+    <hyperlink r:id="rId50" ref="N19"/>
+    <hyperlink r:id="rId51" ref="O19"/>
+    <hyperlink r:id="rId52" ref="P19"/>
+    <hyperlink r:id="rId53" ref="N20"/>
+    <hyperlink r:id="rId54" ref="O20"/>
+    <hyperlink r:id="rId55" ref="P20"/>
+    <hyperlink r:id="rId56" ref="N21"/>
+    <hyperlink r:id="rId57" ref="O21"/>
     <hyperlink r:id="rId58" ref="P21"/>
     <hyperlink r:id="rId59" ref="N22"/>
-    <hyperlink r:id="rId60" ref="O22"/>
-    <hyperlink r:id="rId61" ref="P22"/>
-    <hyperlink r:id="rId62" ref="N23"/>
-    <hyperlink r:id="rId63" ref="O23"/>
-    <hyperlink r:id="rId64" ref="P23"/>
-    <hyperlink r:id="rId65" ref="N24"/>
-    <hyperlink r:id="rId66" ref="O24"/>
-    <hyperlink r:id="rId67" ref="P24"/>
-    <hyperlink r:id="rId68" ref="N25"/>
+    <hyperlink r:id="rId60" ref="P22"/>
+    <hyperlink r:id="rId61" ref="N23"/>
+    <hyperlink r:id="rId62" ref="O23"/>
+    <hyperlink r:id="rId63" ref="P23"/>
+    <hyperlink r:id="rId64" ref="N24"/>
+    <hyperlink r:id="rId65" ref="O24"/>
+    <hyperlink r:id="rId66" ref="P24"/>
+    <hyperlink r:id="rId67" ref="N25"/>
+    <hyperlink r:id="rId68" ref="O25"/>
     <hyperlink r:id="rId69" ref="P25"/>
     <hyperlink r:id="rId70" ref="N26"/>
-    <hyperlink r:id="rId71" ref="O26"/>
-    <hyperlink r:id="rId72" ref="P26"/>
-    <hyperlink r:id="rId73" ref="N27"/>
-    <hyperlink r:id="rId74" ref="O27"/>
-    <hyperlink r:id="rId75" ref="P27"/>
-    <hyperlink r:id="rId76" ref="N28"/>
-    <hyperlink r:id="rId77" ref="N29"/>
+    <hyperlink r:id="rId71" ref="P26"/>
+    <hyperlink r:id="rId72" ref="N27"/>
+    <hyperlink r:id="rId73" ref="O27"/>
+    <hyperlink r:id="rId74" ref="P27"/>
+    <hyperlink r:id="rId75" ref="N28"/>
+    <hyperlink r:id="rId76" ref="O28"/>
+    <hyperlink r:id="rId77" ref="P28"/>
     <hyperlink r:id="rId78" ref="O29"/>
     <hyperlink r:id="rId79" ref="P29"/>
     <hyperlink r:id="rId80" ref="N30"/>
-    <hyperlink r:id="rId81" ref="P30"/>
-    <hyperlink r:id="rId82" ref="N31"/>
-    <hyperlink r:id="rId83" ref="O31"/>
-    <hyperlink r:id="rId84" ref="P31"/>
-    <hyperlink r:id="rId85" ref="N32"/>
-    <hyperlink r:id="rId86" ref="O32"/>
-    <hyperlink r:id="rId87" ref="P32"/>
-    <hyperlink r:id="rId88" ref="N33"/>
-    <hyperlink r:id="rId89" ref="O33"/>
-    <hyperlink r:id="rId90" ref="P33"/>
-    <hyperlink r:id="rId91" ref="N34"/>
-    <hyperlink r:id="rId92" ref="O34"/>
-    <hyperlink r:id="rId93" ref="P34"/>
-    <hyperlink r:id="rId94" ref="N35"/>
+    <hyperlink r:id="rId81" ref="N31"/>
+    <hyperlink r:id="rId82" ref="O31"/>
+    <hyperlink r:id="rId83" ref="P31"/>
+    <hyperlink r:id="rId84" ref="N32"/>
+    <hyperlink r:id="rId85" ref="P32"/>
+    <hyperlink r:id="rId86" ref="N33"/>
+    <hyperlink r:id="rId87" ref="O33"/>
+    <hyperlink r:id="rId88" ref="P33"/>
+    <hyperlink r:id="rId89" ref="N34"/>
+    <hyperlink r:id="rId90" ref="O34"/>
+    <hyperlink r:id="rId91" ref="P34"/>
+    <hyperlink r:id="rId92" ref="N35"/>
+    <hyperlink r:id="rId93" ref="O35"/>
+    <hyperlink r:id="rId94" ref="P35"/>
     <hyperlink r:id="rId95" ref="N36"/>
     <hyperlink r:id="rId96" ref="O36"/>
     <hyperlink r:id="rId97" ref="P36"/>
     <hyperlink r:id="rId98" ref="N37"/>
-    <hyperlink r:id="rId99" ref="P37"/>
-    <hyperlink r:id="rId100" ref="N38"/>
+    <hyperlink r:id="rId99" ref="N38"/>
+    <hyperlink r:id="rId100" ref="O38"/>
     <hyperlink r:id="rId101" ref="P38"/>
     <hyperlink r:id="rId102" ref="N39"/>
-    <hyperlink r:id="rId103" ref="O39"/>
-    <hyperlink r:id="rId104" ref="P39"/>
-    <hyperlink r:id="rId105" ref="N40"/>
-    <hyperlink r:id="rId106" ref="O40"/>
-    <hyperlink r:id="rId107" ref="P40"/>
-    <hyperlink r:id="rId108" ref="N41"/>
-    <hyperlink r:id="rId109" ref="O41"/>
-    <hyperlink r:id="rId110" ref="P41"/>
-    <hyperlink r:id="rId111" ref="N42"/>
-    <hyperlink r:id="rId112" ref="O42"/>
-    <hyperlink r:id="rId113" ref="P42"/>
-    <hyperlink r:id="rId114" ref="N43"/>
-    <hyperlink r:id="rId115" ref="O43"/>
-    <hyperlink r:id="rId116" ref="P43"/>
-    <hyperlink r:id="rId117" ref="N44"/>
-    <hyperlink r:id="rId118" ref="O44"/>
-    <hyperlink r:id="rId119" ref="P44"/>
-    <hyperlink r:id="rId120" ref="N45"/>
-    <hyperlink r:id="rId121" ref="O45"/>
-    <hyperlink r:id="rId122" ref="P45"/>
-    <hyperlink r:id="rId123" ref="N46"/>
-    <hyperlink r:id="rId124" ref="O46"/>
-    <hyperlink r:id="rId125" ref="P46"/>
-    <hyperlink r:id="rId126" ref="N47"/>
-    <hyperlink r:id="rId127" ref="O47"/>
-    <hyperlink r:id="rId128" ref="P47"/>
-    <hyperlink r:id="rId129" ref="N48"/>
-    <hyperlink r:id="rId130" ref="P48"/>
-    <hyperlink r:id="rId131" ref="N49"/>
-    <hyperlink r:id="rId132" ref="O49"/>
-    <hyperlink r:id="rId133" ref="P49"/>
-    <hyperlink r:id="rId134" ref="N50"/>
-    <hyperlink r:id="rId135" ref="O50"/>
-    <hyperlink r:id="rId136" ref="P50"/>
-    <hyperlink r:id="rId137" ref="N51"/>
-    <hyperlink r:id="rId138" ref="O51"/>
-    <hyperlink r:id="rId139" ref="P51"/>
-    <hyperlink r:id="rId140" ref="N52"/>
-    <hyperlink r:id="rId141" ref="O52"/>
-    <hyperlink r:id="rId142" ref="P52"/>
-    <hyperlink r:id="rId143" ref="N53"/>
-    <hyperlink r:id="rId144" ref="O53"/>
-    <hyperlink r:id="rId145" ref="P53"/>
-    <hyperlink r:id="rId146" ref="N54"/>
-    <hyperlink r:id="rId147" ref="O54"/>
-    <hyperlink r:id="rId148" ref="P54"/>
-    <hyperlink r:id="rId149" ref="N55"/>
-    <hyperlink r:id="rId150" ref="O55"/>
-    <hyperlink r:id="rId151" ref="P55"/>
-    <hyperlink r:id="rId152" ref="N56"/>
-    <hyperlink r:id="rId153" ref="O56"/>
-    <hyperlink r:id="rId154" ref="P56"/>
-    <hyperlink r:id="rId155" ref="N57"/>
-    <hyperlink r:id="rId156" ref="O57"/>
-    <hyperlink r:id="rId157" ref="P57"/>
-    <hyperlink r:id="rId158" ref="O58"/>
-    <hyperlink r:id="rId159" ref="P58"/>
-    <hyperlink r:id="rId160" ref="N59"/>
-    <hyperlink r:id="rId161" ref="O59"/>
-    <hyperlink r:id="rId162" ref="P59"/>
-    <hyperlink r:id="rId163" ref="N60"/>
-    <hyperlink r:id="rId164" ref="O60"/>
-    <hyperlink r:id="rId165" ref="P60"/>
-    <hyperlink r:id="rId166" ref="O61"/>
-    <hyperlink r:id="rId167" ref="P61"/>
-    <hyperlink r:id="rId168" ref="N62"/>
+    <hyperlink r:id="rId103" ref="P39"/>
+    <hyperlink r:id="rId104" ref="N40"/>
+    <hyperlink r:id="rId105" ref="P40"/>
+    <hyperlink r:id="rId106" ref="N41"/>
+    <hyperlink r:id="rId107" ref="O41"/>
+    <hyperlink r:id="rId108" ref="P41"/>
+    <hyperlink r:id="rId109" ref="N42"/>
+    <hyperlink r:id="rId110" ref="O42"/>
+    <hyperlink r:id="rId111" ref="P42"/>
+    <hyperlink r:id="rId112" ref="N43"/>
+    <hyperlink r:id="rId113" ref="O43"/>
+    <hyperlink r:id="rId114" ref="P43"/>
+    <hyperlink r:id="rId115" ref="N44"/>
+    <hyperlink r:id="rId116" ref="O44"/>
+    <hyperlink r:id="rId117" ref="P44"/>
+    <hyperlink r:id="rId118" ref="N45"/>
+    <hyperlink r:id="rId119" ref="O45"/>
+    <hyperlink r:id="rId120" ref="P45"/>
+    <hyperlink r:id="rId121" ref="N46"/>
+    <hyperlink r:id="rId122" ref="O46"/>
+    <hyperlink r:id="rId123" ref="P46"/>
+    <hyperlink r:id="rId124" ref="N47"/>
+    <hyperlink r:id="rId125" ref="O47"/>
+    <hyperlink r:id="rId126" ref="P47"/>
+    <hyperlink r:id="rId127" ref="N48"/>
+    <hyperlink r:id="rId128" ref="O48"/>
+    <hyperlink r:id="rId129" ref="P48"/>
+    <hyperlink r:id="rId130" ref="N49"/>
+    <hyperlink r:id="rId131" ref="O49"/>
+    <hyperlink r:id="rId132" ref="P49"/>
+    <hyperlink r:id="rId133" ref="N50"/>
+    <hyperlink r:id="rId134" ref="P50"/>
+    <hyperlink r:id="rId135" ref="N51"/>
+    <hyperlink r:id="rId136" ref="O51"/>
+    <hyperlink r:id="rId137" ref="P51"/>
+    <hyperlink r:id="rId138" ref="N52"/>
+    <hyperlink r:id="rId139" ref="O52"/>
+    <hyperlink r:id="rId140" ref="P52"/>
+    <hyperlink r:id="rId141" ref="N53"/>
+    <hyperlink r:id="rId142" ref="O53"/>
+    <hyperlink r:id="rId143" ref="P53"/>
+    <hyperlink r:id="rId144" ref="N54"/>
+    <hyperlink r:id="rId145" ref="O54"/>
+    <hyperlink r:id="rId146" ref="P54"/>
+    <hyperlink r:id="rId147" ref="N55"/>
+    <hyperlink r:id="rId148" ref="O55"/>
+    <hyperlink r:id="rId149" ref="P55"/>
+    <hyperlink r:id="rId150" ref="N56"/>
+    <hyperlink r:id="rId151" ref="O56"/>
+    <hyperlink r:id="rId152" ref="P56"/>
+    <hyperlink r:id="rId153" ref="N57"/>
+    <hyperlink r:id="rId154" ref="O57"/>
+    <hyperlink r:id="rId155" ref="P57"/>
+    <hyperlink r:id="rId156" ref="N58"/>
+    <hyperlink r:id="rId157" ref="O58"/>
+    <hyperlink r:id="rId158" ref="P58"/>
+    <hyperlink r:id="rId159" ref="N59"/>
+    <hyperlink r:id="rId160" ref="O59"/>
+    <hyperlink r:id="rId161" ref="P59"/>
+    <hyperlink r:id="rId162" ref="O60"/>
+    <hyperlink r:id="rId163" ref="P60"/>
+    <hyperlink r:id="rId164" ref="N61"/>
+    <hyperlink r:id="rId165" ref="O61"/>
+    <hyperlink r:id="rId166" ref="P61"/>
+    <hyperlink r:id="rId167" ref="N62"/>
+    <hyperlink r:id="rId168" ref="O62"/>
     <hyperlink r:id="rId169" ref="P62"/>
-    <hyperlink r:id="rId170" ref="N63"/>
-    <hyperlink r:id="rId171" ref="O63"/>
-    <hyperlink r:id="rId172" ref="P63"/>
-    <hyperlink r:id="rId173" ref="N64"/>
-    <hyperlink r:id="rId174" ref="O64"/>
-    <hyperlink r:id="rId175" ref="P64"/>
-    <hyperlink r:id="rId176" ref="N65"/>
-    <hyperlink r:id="rId177" ref="O65"/>
-    <hyperlink r:id="rId178" ref="P65"/>
-    <hyperlink r:id="rId179" ref="N66"/>
-    <hyperlink r:id="rId180" ref="O66"/>
-    <hyperlink r:id="rId181" ref="P66"/>
-    <hyperlink r:id="rId182" ref="N67"/>
-    <hyperlink r:id="rId183" ref="O67"/>
-    <hyperlink r:id="rId184" ref="P67"/>
-    <hyperlink r:id="rId185" ref="N68"/>
-    <hyperlink r:id="rId186" ref="O68"/>
-    <hyperlink r:id="rId187" ref="P68"/>
-    <hyperlink r:id="rId188" ref="N69"/>
-    <hyperlink r:id="rId189" ref="P69"/>
-    <hyperlink r:id="rId190" ref="N70"/>
-    <hyperlink r:id="rId191" ref="O70"/>
-    <hyperlink r:id="rId192" ref="P70"/>
-    <hyperlink r:id="rId193" ref="N71"/>
-    <hyperlink r:id="rId194" ref="O71"/>
-    <hyperlink r:id="rId195" ref="P71"/>
-    <hyperlink r:id="rId196" ref="O72"/>
-    <hyperlink r:id="rId197" ref="P72"/>
+    <hyperlink r:id="rId170" ref="O63"/>
+    <hyperlink r:id="rId171" ref="P63"/>
+    <hyperlink r:id="rId172" ref="N64"/>
+    <hyperlink r:id="rId173" ref="P64"/>
+    <hyperlink r:id="rId174" ref="N65"/>
+    <hyperlink r:id="rId175" ref="O65"/>
+    <hyperlink r:id="rId176" ref="P65"/>
+    <hyperlink r:id="rId177" ref="N66"/>
+    <hyperlink r:id="rId178" ref="O66"/>
+    <hyperlink r:id="rId179" ref="P66"/>
+    <hyperlink r:id="rId180" ref="N67"/>
+    <hyperlink r:id="rId181" ref="O67"/>
+    <hyperlink r:id="rId182" ref="P67"/>
+    <hyperlink r:id="rId183" ref="N68"/>
+    <hyperlink r:id="rId184" ref="O68"/>
+    <hyperlink r:id="rId185" ref="P68"/>
+    <hyperlink r:id="rId186" ref="N69"/>
+    <hyperlink r:id="rId187" ref="O69"/>
+    <hyperlink r:id="rId188" ref="P69"/>
+    <hyperlink r:id="rId189" ref="N70"/>
+    <hyperlink r:id="rId190" ref="O70"/>
+    <hyperlink r:id="rId191" ref="P70"/>
+    <hyperlink r:id="rId192" ref="N71"/>
+    <hyperlink r:id="rId193" ref="P71"/>
+    <hyperlink r:id="rId194" ref="N72"/>
+    <hyperlink r:id="rId195" ref="O72"/>
+    <hyperlink r:id="rId196" ref="P72"/>
+    <hyperlink r:id="rId197" ref="N73"/>
+    <hyperlink r:id="rId198" ref="O73"/>
+    <hyperlink r:id="rId199" ref="P73"/>
+    <hyperlink r:id="rId200" ref="O74"/>
+    <hyperlink r:id="rId201" ref="P74"/>
   </hyperlinks>
-  <drawing r:id="rId198"/>
+  <drawing r:id="rId202"/>
 </worksheet>
 </file>
--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="325">
   <si>
     <t>Date</t>
   </si>
@@ -469,6 +469,9 @@
   </si>
   <si>
     <t>https://expressobeans.com/public/detail.php/301920</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qhtkrXebdTxDmKdGWpDHEcFOrOEQbjaW/view?usp=drive_link</t>
   </si>
   <si>
     <t>KISS</t>
@@ -2598,7 +2601,7 @@
         <v>151</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30">
@@ -2606,10 +2609,10 @@
         <v>43561.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>39</v>
@@ -2645,13 +2648,13 @@
         <v>43595.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>19</v>
@@ -2679,10 +2682,10 @@
         <v>26</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32">
@@ -2693,7 +2696,7 @@
         <v>110</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>79</v>
@@ -2703,7 +2706,7 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>22</v>
@@ -2718,7 +2721,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M32" s="2">
         <v>23.0</v>
@@ -2727,7 +2730,7 @@
         <v>26</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33">
@@ -2748,7 +2751,7 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>22</v>
@@ -2772,10 +2775,10 @@
         <v>26</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34">
@@ -2786,7 +2789,7 @@
         <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>39</v>
@@ -2796,7 +2799,7 @@
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>22</v>
@@ -2820,10 +2823,10 @@
         <v>26</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35">
@@ -2834,17 +2837,17 @@
         <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>22</v>
@@ -2859,7 +2862,7 @@
         <v>23</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>25</v>
@@ -2868,10 +2871,10 @@
         <v>26</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36">
@@ -2882,17 +2885,17 @@
         <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>22</v>
@@ -2913,10 +2916,10 @@
         <v>26</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37">
@@ -2924,13 +2927,13 @@
         <v>43869.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>32</v>
@@ -2952,7 +2955,7 @@
         <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M37" s="2">
         <v>31.0</v>
@@ -2966,10 +2969,10 @@
         <v>44450.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>39</v>
@@ -2979,7 +2982,7 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>34</v>
@@ -3000,10 +3003,10 @@
         <v>26</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39">
@@ -3014,7 +3017,7 @@
         <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>39</v>
@@ -3024,7 +3027,7 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>22</v>
@@ -3045,7 +3048,7 @@
         <v>26</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40">
@@ -3053,19 +3056,19 @@
         <v>44511.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>33</v>
@@ -3089,7 +3092,7 @@
         <v>26</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41">
@@ -3097,10 +3100,10 @@
         <v>44519.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>39</v>
@@ -3110,7 +3113,7 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>34</v>
@@ -3131,10 +3134,10 @@
         <v>26</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
@@ -3145,17 +3148,17 @@
         <v>84</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>22</v>
@@ -3170,7 +3173,7 @@
         <v>24</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>25</v>
@@ -3179,10 +3182,10 @@
         <v>26</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43">
@@ -3193,10 +3196,10 @@
         <v>84</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>32</v>
@@ -3224,10 +3227,10 @@
         <v>26</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44">
@@ -3238,7 +3241,7 @@
         <v>37</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>39</v>
@@ -3248,7 +3251,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>22</v>
@@ -3269,10 +3272,10 @@
         <v>26</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45">
@@ -3283,7 +3286,7 @@
         <v>37</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>39</v>
@@ -3293,7 +3296,7 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>22</v>
@@ -3314,10 +3317,10 @@
         <v>26</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46">
@@ -3328,19 +3331,19 @@
         <v>77</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>22</v>
@@ -3361,10 +3364,10 @@
         <v>26</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47">
@@ -3372,10 +3375,10 @@
         <v>44773.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>39</v>
@@ -3406,10 +3409,10 @@
         <v>26</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48">
@@ -3417,13 +3420,13 @@
         <v>44804.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>32</v>
@@ -3451,10 +3454,10 @@
         <v>26</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49">
@@ -3475,7 +3478,7 @@
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>22</v>
@@ -3496,10 +3499,10 @@
         <v>26</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50">
@@ -3507,19 +3510,19 @@
         <v>45064.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>33</v>
@@ -3543,7 +3546,7 @@
         <v>26</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51">
@@ -3554,17 +3557,17 @@
         <v>84</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>22</v>
@@ -3585,10 +3588,10 @@
         <v>26</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52">
@@ -3599,17 +3602,17 @@
         <v>92</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>22</v>
@@ -3624,7 +3627,7 @@
         <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M52" s="2">
         <v>12.0</v>
@@ -3633,10 +3636,10 @@
         <v>26</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53">
@@ -3647,17 +3650,17 @@
         <v>92</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>22</v>
@@ -3672,7 +3675,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M53" s="2">
         <v>13.0</v>
@@ -3681,10 +3684,10 @@
         <v>26</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54">
@@ -3692,13 +3695,13 @@
         <v>45213.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>32</v>
@@ -3727,10 +3730,10 @@
         <v>26</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55">
@@ -3738,10 +3741,10 @@
         <v>45228.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>39</v>
@@ -3750,7 +3753,7 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>33</v>
@@ -3774,10 +3777,10 @@
         <v>26</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="56">
@@ -3785,10 +3788,10 @@
         <v>45228.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>39</v>
@@ -3798,7 +3801,7 @@
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>34</v>
@@ -3819,10 +3822,10 @@
         <v>26</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57">
@@ -3830,10 +3833,10 @@
         <v>45239.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>39</v>
@@ -3864,10 +3867,10 @@
         <v>26</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58">
@@ -3878,7 +3881,7 @@
         <v>84</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>79</v>
@@ -3888,7 +3891,7 @@
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>22</v>
@@ -3909,10 +3912,10 @@
         <v>26</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59">
@@ -3923,7 +3926,7 @@
         <v>84</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>79</v>
@@ -3933,7 +3936,7 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>22</v>
@@ -3954,10 +3957,10 @@
         <v>26</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60">
@@ -3968,10 +3971,10 @@
         <v>84</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>32</v>
@@ -3989,16 +3992,16 @@
         <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61">
@@ -4006,10 +4009,10 @@
         <v>45389.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>39</v>
@@ -4040,10 +4043,10 @@
         <v>26</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62">
@@ -4051,10 +4054,10 @@
         <v>45389.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>39</v>
@@ -4079,7 +4082,7 @@
         <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M62" s="2">
         <v>9.0</v>
@@ -4088,10 +4091,10 @@
         <v>26</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63">
@@ -4099,10 +4102,10 @@
         <v>45389.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
@@ -4111,7 +4114,7 @@
         <v>32</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>22</v>
@@ -4126,16 +4129,16 @@
         <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64">
@@ -4143,10 +4146,10 @@
         <v>45428.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>126</v>
@@ -4155,7 +4158,7 @@
         <v>32</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>33</v>
@@ -4179,7 +4182,7 @@
         <v>26</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65">
@@ -4187,10 +4190,10 @@
         <v>45469.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>39</v>
@@ -4199,10 +4202,10 @@
         <v>19</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>22</v>
@@ -4223,10 +4226,10 @@
         <v>26</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -4234,10 +4237,10 @@
         <v>45469.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>39</v>
@@ -4268,10 +4271,10 @@
         <v>26</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67">
@@ -4279,10 +4282,10 @@
         <v>45783.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>39</v>
@@ -4291,7 +4294,7 @@
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>22</v>
@@ -4312,10 +4315,10 @@
         <v>26</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68">
@@ -4357,10 +4360,10 @@
         <v>26</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69">
@@ -4371,7 +4374,7 @@
         <v>92</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>79</v>
@@ -4381,7 +4384,7 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>22</v>
@@ -4396,7 +4399,7 @@
         <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M69" s="2">
         <v>8.0</v>
@@ -4405,10 +4408,10 @@
         <v>26</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="70">
@@ -4419,7 +4422,7 @@
         <v>92</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>79</v>
@@ -4429,7 +4432,7 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>22</v>
@@ -4450,24 +4453,24 @@
         <v>26</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <v>45896.0</v>
+        <v>45897.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>32</v>
@@ -4495,7 +4498,7 @@
         <v>26</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72">
@@ -4506,7 +4509,7 @@
         <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>39</v>
@@ -4515,7 +4518,7 @@
         <v>32</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>33</v>
@@ -4533,7 +4536,7 @@
         <v>24</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M72" s="2">
         <v>35.0</v>
@@ -4542,10 +4545,10 @@
         <v>26</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73">
@@ -4556,19 +4559,19 @@
         <v>77</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>22</v>
@@ -4583,7 +4586,7 @@
         <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M73" s="2">
         <v>11.0</v>
@@ -4592,10 +4595,10 @@
         <v>26</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74">
@@ -4603,20 +4606,20 @@
         <v>46129.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>22</v>
@@ -4635,10 +4638,10 @@
       </c>
       <c r="N74" s="9"/>
       <c r="O74" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75">

--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Poster List" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Poster List'!$A$1:$V$74</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Poster List'!$A$1:$V$88</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="392">
   <si>
     <t>Date</t>
   </si>
@@ -171,6 +171,9 @@
     <t>https://drive.google.com/file/d/1Cdr6HCwHruHIvXDnshMWKLxGb07QuRnk/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Nine Inch Nails / Soundgarden</t>
+  </si>
+  <si>
     <t>Ames Brothers</t>
   </si>
   <si>
@@ -828,6 +831,9 @@
     <t>Korin Faught</t>
   </si>
   <si>
+    <t>177/750</t>
+  </si>
+  <si>
     <t>Big Poster</t>
   </si>
   <si>
@@ -861,6 +867,9 @@
     <t>Mark Dean Veca</t>
   </si>
   <si>
+    <t>33/75</t>
+  </si>
+  <si>
     <t>https://expressobeans.com/public/detail.php/322926</t>
   </si>
   <si>
@@ -988,14 +997,207 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1t0V2HQrDpkYGYF8XyljYkxtAdmIzeFDj/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Daniel Martin Diaz</t>
+  </si>
+  <si>
+    <t>Metallic Gold Ink</t>
+  </si>
+  <si>
+    <t>7/150</t>
+  </si>
+  <si>
+    <t>Existential Reckoning Release Poster</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Q0dGsuVfBWpKT9WQDMysnGyqqo1tDkMJ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Byzewski </t>
+  </si>
+  <si>
+    <t>Round Foil</t>
+  </si>
+  <si>
+    <t>342/400</t>
+  </si>
+  <si>
+    <t>Billy D and the Hall of Feathered Serpents</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ms9EL_sm6TY6_PObmChJ6lMmUC-v8q9k/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/319935</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mUj97ydq36XEpNGB9Ta6XkyYghKcQfhB/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Jermaine Rogers</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>39/167</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/306423</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HmAi3hIe4Xu2TdAAI_XX45py7rZSewgg/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>68/425</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/307474</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1j8WfbmFpxo8ODSiZ3hlzUkS5_cGzMFbN/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Rush</t>
+  </si>
+  <si>
+    <t>Swirl Foil</t>
+  </si>
+  <si>
+    <t>58/60</t>
+  </si>
+  <si>
+    <t>Fly by Night 45th Anniversary</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NbxG_SNzjnD4WTmZP6plmFymPA8IcQfm/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Robert Bowen</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/209954</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1P9bhD_skRhlxv5dsZSi4deoZ2vkGzWkh/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Mr. Bungle</t>
+  </si>
+  <si>
+    <t>Trey Spurance</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>Night 1 Poster</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/316870</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zctq7NFbCW9kFtjaD4iYpEW327dcXuQw/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Night 2 Poster</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/316868</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lhIYa3ONjhygkm2FJ2LJhIdrfurQUmku/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Primus / Ween</t>
+  </si>
+  <si>
+    <t>Pot Leaf Foil</t>
+  </si>
+  <si>
+    <t>197/650</t>
+  </si>
+  <si>
+    <t>South Park 25th Anniversary</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/307782</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bE4Z-cx7oO9VCOg2MmoswcR-QyMgPVtF/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Pink Floyd</t>
+  </si>
+  <si>
+    <t>Cuyler Smith</t>
+  </si>
+  <si>
+    <t>3d Lenticular</t>
+  </si>
+  <si>
+    <t>73/250</t>
+  </si>
+  <si>
+    <t>Dark Side of the Moon</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18VkRWNuDBvdlw80Y6TXfHE5FX2BiWjKY/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Lizzo</t>
+  </si>
+  <si>
+    <t>Mike Tallman</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18yqAiVsklcCyOuzNp_1tvlR_CUrVjSw-/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Steve Thomas</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>Bonnaroo</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/225439</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1X_RmvN88PnkSxJuC3eQuLBdOtbOq0NXP/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Van Morrison</t>
+  </si>
+  <si>
+    <t>Neal Williams</t>
+  </si>
+  <si>
+    <t>Santa Barbara</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DTZfAI2-cr8zUjzmdGRyWAb6RWkPrzMD/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1066,7 +1268,7 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -1574,20 +1776,20 @@
         <v>41862.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>22</v>
@@ -1608,10 +1810,10 @@
         <v>26</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1619,10 +1821,10 @@
         <v>41899.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>31</v>
@@ -1653,10 +1855,10 @@
         <v>26</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -1667,7 +1869,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>31</v>
@@ -1676,10 +1878,10 @@
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>22</v>
@@ -1694,7 +1896,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>25</v>
@@ -1703,10 +1905,10 @@
         <v>26</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -1714,10 +1916,10 @@
         <v>42204.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -1726,10 +1928,10 @@
         <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>22</v>
@@ -1750,10 +1952,10 @@
         <v>26</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1764,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>39</v>
@@ -1774,7 +1976,7 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>22</v>
@@ -1795,10 +1997,10 @@
         <v>26</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -1806,20 +2008,20 @@
         <v>42318.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>22</v>
@@ -1834,7 +2036,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>25</v>
@@ -1843,10 +2045,10 @@
         <v>26</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -1854,20 +2056,20 @@
         <v>42395.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>22</v>
@@ -1888,10 +2090,10 @@
         <v>26</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1899,10 +2101,10 @@
         <v>42479.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -1933,10 +2135,10 @@
         <v>26</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1944,10 +2146,10 @@
         <v>42874.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>31</v>
@@ -1957,7 +2159,7 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>22</v>
@@ -1978,10 +2180,10 @@
         <v>26</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
@@ -1989,20 +2191,20 @@
         <v>42879.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>22</v>
@@ -2017,7 +2219,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M16" s="2">
         <v>22.0</v>
@@ -2026,10 +2228,10 @@
         <v>26</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -2037,20 +2239,20 @@
         <v>42879.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>22</v>
@@ -2065,14 +2267,14 @@
         <v>24</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
@@ -2080,10 +2282,10 @@
         <v>42934.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>39</v>
@@ -2092,10 +2294,10 @@
         <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>22</v>
@@ -2109,11 +2311,14 @@
       <c r="K18" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="N18" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="O18" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
@@ -2121,20 +2326,20 @@
         <v>42958.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>22</v>
@@ -2149,19 +2354,19 @@
         <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M19" s="2">
-        <v>24.0</v>
+        <v>40.0</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -2172,7 +2377,7 @@
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>31</v>
@@ -2203,10 +2408,10 @@
         <v>26</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21">
@@ -2217,10 +2422,10 @@
         <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>32</v>
@@ -2242,7 +2447,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>25</v>
@@ -2251,10 +2456,10 @@
         <v>26</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22">
@@ -2262,13 +2467,13 @@
         <v>43238.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>19</v>
@@ -2278,7 +2483,7 @@
         <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>23</v>
@@ -2296,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
@@ -2304,20 +2509,20 @@
         <v>43240.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>22</v>
@@ -2338,10 +2543,10 @@
         <v>26</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
@@ -2349,10 +2554,10 @@
         <v>43347.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>31</v>
@@ -2383,10 +2588,10 @@
         <v>26</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25">
@@ -2394,13 +2599,13 @@
         <v>43405.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
@@ -2422,7 +2627,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>25</v>
@@ -2431,10 +2636,10 @@
         <v>26</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
@@ -2442,13 +2647,13 @@
         <v>43405.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
@@ -2473,7 +2678,7 @@
         <v>26</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
@@ -2481,10 +2686,10 @@
         <v>43493.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>39</v>
@@ -2494,7 +2699,7 @@
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>22</v>
@@ -2515,10 +2720,10 @@
         <v>26</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28">
@@ -2526,10 +2731,10 @@
         <v>43493.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>39</v>
@@ -2560,10 +2765,10 @@
         <v>26</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
@@ -2571,10 +2776,10 @@
         <v>43536.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>39</v>
@@ -2598,10 +2803,10 @@
         <v>24</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30">
@@ -2609,10 +2814,10 @@
         <v>43561.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>39</v>
@@ -2648,13 +2853,13 @@
         <v>43595.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>19</v>
@@ -2664,7 +2869,7 @@
         <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
@@ -2682,10 +2887,10 @@
         <v>26</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32">
@@ -2693,20 +2898,20 @@
         <v>43733.0</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>22</v>
@@ -2721,7 +2926,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M32" s="2">
         <v>23.0</v>
@@ -2730,7 +2935,7 @@
         <v>26</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
@@ -2738,10 +2943,10 @@
         <v>43788.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
@@ -2751,7 +2956,7 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>22</v>
@@ -2766,7 +2971,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>25</v>
@@ -2775,10 +2980,10 @@
         <v>26</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34">
@@ -2786,10 +2991,10 @@
         <v>43793.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>39</v>
@@ -2799,7 +3004,7 @@
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>22</v>
@@ -2814,7 +3019,7 @@
         <v>24</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>25</v>
@@ -2823,10 +3028,10 @@
         <v>26</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35">
@@ -2834,20 +3039,20 @@
         <v>43844.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>22</v>
@@ -2862,7 +3067,7 @@
         <v>23</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>25</v>
@@ -2871,10 +3076,10 @@
         <v>26</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36">
@@ -2882,20 +3087,20 @@
         <v>43847.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>22</v>
@@ -2916,10 +3121,10 @@
         <v>26</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37">
@@ -2927,13 +3132,13 @@
         <v>43869.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>32</v>
@@ -2955,7 +3160,7 @@
         <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M37" s="2">
         <v>31.0</v>
@@ -2969,10 +3174,10 @@
         <v>44450.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>39</v>
@@ -2982,7 +3187,7 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>34</v>
@@ -3003,10 +3208,10 @@
         <v>26</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39">
@@ -3014,10 +3219,10 @@
         <v>44468.0</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>39</v>
@@ -3027,7 +3232,7 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>22</v>
@@ -3048,7 +3253,7 @@
         <v>26</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40">
@@ -3056,25 +3261,25 @@
         <v>44511.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
@@ -3092,7 +3297,7 @@
         <v>26</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41">
@@ -3100,10 +3305,10 @@
         <v>44519.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>39</v>
@@ -3113,7 +3318,7 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>34</v>
@@ -3134,10 +3339,10 @@
         <v>26</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42">
@@ -3145,20 +3350,20 @@
         <v>44614.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>22</v>
@@ -3173,7 +3378,7 @@
         <v>24</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>25</v>
@@ -3182,10 +3387,10 @@
         <v>26</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43">
@@ -3193,13 +3398,13 @@
         <v>44640.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>32</v>
@@ -3227,10 +3432,10 @@
         <v>26</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44">
@@ -3241,7 +3446,7 @@
         <v>37</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>39</v>
@@ -3251,7 +3456,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>22</v>
@@ -3272,10 +3477,10 @@
         <v>26</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45">
@@ -3286,7 +3491,7 @@
         <v>37</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>39</v>
@@ -3296,7 +3501,7 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>22</v>
@@ -3317,10 +3522,10 @@
         <v>26</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46">
@@ -3328,22 +3533,22 @@
         <v>44734.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>22</v>
@@ -3364,10 +3569,10 @@
         <v>26</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47">
@@ -3375,10 +3580,10 @@
         <v>44773.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>39</v>
@@ -3409,10 +3614,10 @@
         <v>26</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48">
@@ -3420,13 +3625,13 @@
         <v>44804.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>32</v>
@@ -3454,10 +3659,10 @@
         <v>26</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49">
@@ -3465,20 +3670,20 @@
         <v>44866.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>22</v>
@@ -3499,10 +3704,10 @@
         <v>26</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50">
@@ -3510,25 +3715,25 @@
         <v>45064.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
@@ -3546,7 +3751,7 @@
         <v>26</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51">
@@ -3554,20 +3759,20 @@
         <v>45067.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>22</v>
@@ -3588,10 +3793,10 @@
         <v>26</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
@@ -3599,20 +3804,20 @@
         <v>45142.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>22</v>
@@ -3627,7 +3832,7 @@
         <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M52" s="2">
         <v>12.0</v>
@@ -3636,10 +3841,10 @@
         <v>26</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53">
@@ -3647,20 +3852,20 @@
         <v>45144.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>22</v>
@@ -3675,7 +3880,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M53" s="2">
         <v>13.0</v>
@@ -3684,10 +3889,10 @@
         <v>26</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54">
@@ -3695,13 +3900,13 @@
         <v>45213.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>32</v>
@@ -3730,10 +3935,10 @@
         <v>26</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55">
@@ -3741,10 +3946,10 @@
         <v>45228.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>39</v>
@@ -3753,7 +3958,7 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>33</v>
@@ -3777,10 +3982,10 @@
         <v>26</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56">
@@ -3788,20 +3993,20 @@
         <v>45228.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>34</v>
@@ -3822,10 +4027,10 @@
         <v>26</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57">
@@ -3833,10 +4038,10 @@
         <v>45239.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>39</v>
@@ -3867,10 +4072,10 @@
         <v>26</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58">
@@ -3878,20 +4083,20 @@
         <v>45312.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>22</v>
@@ -3912,10 +4117,10 @@
         <v>26</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59">
@@ -3923,20 +4128,20 @@
         <v>45312.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>22</v>
@@ -3957,10 +4162,10 @@
         <v>26</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60">
@@ -3968,17 +4173,20 @@
         <v>45340.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="G60" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="H60" s="2" t="s">
         <v>22</v>
       </c>
@@ -3992,16 +4200,19 @@
         <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="N60" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="O60" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61">
@@ -4009,16 +4220,16 @@
         <v>45389.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2" t="s">
@@ -4043,10 +4254,10 @@
         <v>26</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62">
@@ -4054,10 +4265,10 @@
         <v>45389.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>39</v>
@@ -4082,7 +4293,7 @@
         <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M62" s="2">
         <v>9.0</v>
@@ -4091,10 +4302,10 @@
         <v>26</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63">
@@ -4102,10 +4313,10 @@
         <v>45389.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
@@ -4114,7 +4325,10 @@
         <v>32</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>22</v>
@@ -4129,16 +4343,19 @@
         <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="N63" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="O63" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64">
@@ -4146,25 +4363,25 @@
         <v>45428.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>23</v>
@@ -4182,7 +4399,7 @@
         <v>26</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65">
@@ -4190,10 +4407,10 @@
         <v>45469.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>39</v>
@@ -4202,10 +4419,10 @@
         <v>19</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>22</v>
@@ -4226,10 +4443,10 @@
         <v>26</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66">
@@ -4237,10 +4454,10 @@
         <v>45469.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>39</v>
@@ -4271,10 +4488,10 @@
         <v>26</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67">
@@ -4282,10 +4499,10 @@
         <v>45783.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>39</v>
@@ -4294,7 +4511,7 @@
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>22</v>
@@ -4315,10 +4532,10 @@
         <v>26</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68">
@@ -4326,10 +4543,10 @@
         <v>45790.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>39</v>
@@ -4360,10 +4577,10 @@
         <v>26</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69">
@@ -4371,20 +4588,20 @@
         <v>45808.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>22</v>
@@ -4399,7 +4616,7 @@
         <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M69" s="2">
         <v>8.0</v>
@@ -4408,10 +4625,10 @@
         <v>26</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70">
@@ -4419,20 +4636,20 @@
         <v>45808.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>22</v>
@@ -4453,10 +4670,10 @@
         <v>26</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71">
@@ -4464,13 +4681,13 @@
         <v>45897.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>32</v>
@@ -4498,7 +4715,7 @@
         <v>26</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72">
@@ -4509,7 +4726,7 @@
         <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>39</v>
@@ -4518,7 +4735,7 @@
         <v>32</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>33</v>
@@ -4536,7 +4753,7 @@
         <v>24</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M72" s="2">
         <v>35.0</v>
@@ -4545,10 +4762,10 @@
         <v>26</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="73">
@@ -4556,22 +4773,22 @@
         <v>46113.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>22</v>
@@ -4586,7 +4803,7 @@
         <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="M73" s="2">
         <v>11.0</v>
@@ -4595,10 +4812,10 @@
         <v>26</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74">
@@ -4606,20 +4823,20 @@
         <v>46129.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>22</v>
@@ -4636,55 +4853,598 @@
       <c r="M74" s="2">
         <v>39.0</v>
       </c>
-      <c r="N74" s="9"/>
+      <c r="N74" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="O74" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10"/>
+      <c r="A75" s="1">
+        <v>44134.0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="10"/>
+      <c r="A76" s="1">
+        <v>44303.0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="10"/>
+      <c r="A77" s="9">
+        <v>44682.0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="10"/>
+      <c r="A78" s="1">
+        <v>44713.0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="10"/>
+      <c r="A79" s="1">
+        <v>44705.0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="10"/>
+      <c r="A80" s="1">
+        <v>44054.0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="10"/>
+      <c r="A81" s="1">
+        <v>42178.0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="10"/>
+      <c r="A82" s="1">
+        <v>45065.0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O82" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="10"/>
+      <c r="A83" s="9">
+        <v>45066.0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="10"/>
+      <c r="A84" s="1">
+        <v>44782.0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="10"/>
+      <c r="A85" s="1">
+        <v>44710.0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="10"/>
+      <c r="A86" s="1">
+        <v>43753.0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="10"/>
+      <c r="A87" s="1">
+        <v>42532.0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="10"/>
+      <c r="A88" s="1">
+        <v>42658.0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10"/>
@@ -7441,7 +8201,7 @@
       <c r="A1006" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$V$74"/>
+  <autoFilter ref="$A$1:$V$88"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="N2"/>
     <hyperlink r:id="rId2" ref="O2"/>
@@ -7490,161 +8250,201 @@
     <hyperlink r:id="rId45" ref="P16"/>
     <hyperlink r:id="rId46" ref="O17"/>
     <hyperlink r:id="rId47" ref="P17"/>
-    <hyperlink r:id="rId48" ref="O18"/>
-    <hyperlink r:id="rId49" ref="P18"/>
-    <hyperlink r:id="rId50" ref="N19"/>
-    <hyperlink r:id="rId51" ref="O19"/>
-    <hyperlink r:id="rId52" ref="P19"/>
-    <hyperlink r:id="rId53" ref="N20"/>
-    <hyperlink r:id="rId54" ref="O20"/>
-    <hyperlink r:id="rId55" ref="P20"/>
-    <hyperlink r:id="rId56" ref="N21"/>
-    <hyperlink r:id="rId57" ref="O21"/>
-    <hyperlink r:id="rId58" ref="P21"/>
-    <hyperlink r:id="rId59" ref="N22"/>
-    <hyperlink r:id="rId60" ref="P22"/>
-    <hyperlink r:id="rId61" ref="N23"/>
-    <hyperlink r:id="rId62" ref="O23"/>
-    <hyperlink r:id="rId63" ref="P23"/>
-    <hyperlink r:id="rId64" ref="N24"/>
-    <hyperlink r:id="rId65" ref="O24"/>
-    <hyperlink r:id="rId66" ref="P24"/>
-    <hyperlink r:id="rId67" ref="N25"/>
-    <hyperlink r:id="rId68" ref="O25"/>
-    <hyperlink r:id="rId69" ref="P25"/>
-    <hyperlink r:id="rId70" ref="N26"/>
-    <hyperlink r:id="rId71" ref="P26"/>
-    <hyperlink r:id="rId72" ref="N27"/>
-    <hyperlink r:id="rId73" ref="O27"/>
-    <hyperlink r:id="rId74" ref="P27"/>
-    <hyperlink r:id="rId75" ref="N28"/>
-    <hyperlink r:id="rId76" ref="O28"/>
-    <hyperlink r:id="rId77" ref="P28"/>
-    <hyperlink r:id="rId78" ref="O29"/>
-    <hyperlink r:id="rId79" ref="P29"/>
-    <hyperlink r:id="rId80" ref="N30"/>
-    <hyperlink r:id="rId81" ref="N31"/>
-    <hyperlink r:id="rId82" ref="O31"/>
-    <hyperlink r:id="rId83" ref="P31"/>
-    <hyperlink r:id="rId84" ref="N32"/>
-    <hyperlink r:id="rId85" ref="P32"/>
-    <hyperlink r:id="rId86" ref="N33"/>
-    <hyperlink r:id="rId87" ref="O33"/>
-    <hyperlink r:id="rId88" ref="P33"/>
-    <hyperlink r:id="rId89" ref="N34"/>
-    <hyperlink r:id="rId90" ref="O34"/>
-    <hyperlink r:id="rId91" ref="P34"/>
-    <hyperlink r:id="rId92" ref="N35"/>
-    <hyperlink r:id="rId93" ref="O35"/>
-    <hyperlink r:id="rId94" ref="P35"/>
-    <hyperlink r:id="rId95" ref="N36"/>
-    <hyperlink r:id="rId96" ref="O36"/>
-    <hyperlink r:id="rId97" ref="P36"/>
-    <hyperlink r:id="rId98" ref="N37"/>
-    <hyperlink r:id="rId99" ref="N38"/>
-    <hyperlink r:id="rId100" ref="O38"/>
-    <hyperlink r:id="rId101" ref="P38"/>
-    <hyperlink r:id="rId102" ref="N39"/>
-    <hyperlink r:id="rId103" ref="P39"/>
-    <hyperlink r:id="rId104" ref="N40"/>
-    <hyperlink r:id="rId105" ref="P40"/>
-    <hyperlink r:id="rId106" ref="N41"/>
-    <hyperlink r:id="rId107" ref="O41"/>
-    <hyperlink r:id="rId108" ref="P41"/>
-    <hyperlink r:id="rId109" ref="N42"/>
-    <hyperlink r:id="rId110" ref="O42"/>
-    <hyperlink r:id="rId111" ref="P42"/>
-    <hyperlink r:id="rId112" ref="N43"/>
-    <hyperlink r:id="rId113" ref="O43"/>
-    <hyperlink r:id="rId114" ref="P43"/>
-    <hyperlink r:id="rId115" ref="N44"/>
-    <hyperlink r:id="rId116" ref="O44"/>
-    <hyperlink r:id="rId117" ref="P44"/>
-    <hyperlink r:id="rId118" ref="N45"/>
-    <hyperlink r:id="rId119" ref="O45"/>
-    <hyperlink r:id="rId120" ref="P45"/>
-    <hyperlink r:id="rId121" ref="N46"/>
-    <hyperlink r:id="rId122" ref="O46"/>
-    <hyperlink r:id="rId123" ref="P46"/>
-    <hyperlink r:id="rId124" ref="N47"/>
-    <hyperlink r:id="rId125" ref="O47"/>
-    <hyperlink r:id="rId126" ref="P47"/>
-    <hyperlink r:id="rId127" ref="N48"/>
-    <hyperlink r:id="rId128" ref="O48"/>
-    <hyperlink r:id="rId129" ref="P48"/>
-    <hyperlink r:id="rId130" ref="N49"/>
-    <hyperlink r:id="rId131" ref="O49"/>
-    <hyperlink r:id="rId132" ref="P49"/>
-    <hyperlink r:id="rId133" ref="N50"/>
-    <hyperlink r:id="rId134" ref="P50"/>
-    <hyperlink r:id="rId135" ref="N51"/>
-    <hyperlink r:id="rId136" ref="O51"/>
-    <hyperlink r:id="rId137" ref="P51"/>
-    <hyperlink r:id="rId138" ref="N52"/>
-    <hyperlink r:id="rId139" ref="O52"/>
-    <hyperlink r:id="rId140" ref="P52"/>
-    <hyperlink r:id="rId141" ref="N53"/>
-    <hyperlink r:id="rId142" ref="O53"/>
-    <hyperlink r:id="rId143" ref="P53"/>
-    <hyperlink r:id="rId144" ref="N54"/>
-    <hyperlink r:id="rId145" ref="O54"/>
-    <hyperlink r:id="rId146" ref="P54"/>
-    <hyperlink r:id="rId147" ref="N55"/>
-    <hyperlink r:id="rId148" ref="O55"/>
-    <hyperlink r:id="rId149" ref="P55"/>
-    <hyperlink r:id="rId150" ref="N56"/>
-    <hyperlink r:id="rId151" ref="O56"/>
-    <hyperlink r:id="rId152" ref="P56"/>
-    <hyperlink r:id="rId153" ref="N57"/>
-    <hyperlink r:id="rId154" ref="O57"/>
-    <hyperlink r:id="rId155" ref="P57"/>
-    <hyperlink r:id="rId156" ref="N58"/>
-    <hyperlink r:id="rId157" ref="O58"/>
-    <hyperlink r:id="rId158" ref="P58"/>
-    <hyperlink r:id="rId159" ref="N59"/>
-    <hyperlink r:id="rId160" ref="O59"/>
-    <hyperlink r:id="rId161" ref="P59"/>
-    <hyperlink r:id="rId162" ref="O60"/>
-    <hyperlink r:id="rId163" ref="P60"/>
-    <hyperlink r:id="rId164" ref="N61"/>
-    <hyperlink r:id="rId165" ref="O61"/>
-    <hyperlink r:id="rId166" ref="P61"/>
-    <hyperlink r:id="rId167" ref="N62"/>
-    <hyperlink r:id="rId168" ref="O62"/>
-    <hyperlink r:id="rId169" ref="P62"/>
-    <hyperlink r:id="rId170" ref="O63"/>
-    <hyperlink r:id="rId171" ref="P63"/>
-    <hyperlink r:id="rId172" ref="N64"/>
-    <hyperlink r:id="rId173" ref="P64"/>
-    <hyperlink r:id="rId174" ref="N65"/>
-    <hyperlink r:id="rId175" ref="O65"/>
-    <hyperlink r:id="rId176" ref="P65"/>
-    <hyperlink r:id="rId177" ref="N66"/>
-    <hyperlink r:id="rId178" ref="O66"/>
-    <hyperlink r:id="rId179" ref="P66"/>
-    <hyperlink r:id="rId180" ref="N67"/>
-    <hyperlink r:id="rId181" ref="O67"/>
-    <hyperlink r:id="rId182" ref="P67"/>
-    <hyperlink r:id="rId183" ref="N68"/>
-    <hyperlink r:id="rId184" ref="O68"/>
-    <hyperlink r:id="rId185" ref="P68"/>
-    <hyperlink r:id="rId186" ref="N69"/>
-    <hyperlink r:id="rId187" ref="O69"/>
-    <hyperlink r:id="rId188" ref="P69"/>
-    <hyperlink r:id="rId189" ref="N70"/>
-    <hyperlink r:id="rId190" ref="O70"/>
-    <hyperlink r:id="rId191" ref="P70"/>
-    <hyperlink r:id="rId192" ref="N71"/>
-    <hyperlink r:id="rId193" ref="P71"/>
-    <hyperlink r:id="rId194" ref="N72"/>
-    <hyperlink r:id="rId195" ref="O72"/>
-    <hyperlink r:id="rId196" ref="P72"/>
-    <hyperlink r:id="rId197" ref="N73"/>
-    <hyperlink r:id="rId198" ref="O73"/>
-    <hyperlink r:id="rId199" ref="P73"/>
-    <hyperlink r:id="rId200" ref="O74"/>
-    <hyperlink r:id="rId201" ref="P74"/>
+    <hyperlink r:id="rId48" ref="N18"/>
+    <hyperlink r:id="rId49" ref="O18"/>
+    <hyperlink r:id="rId50" ref="P18"/>
+    <hyperlink r:id="rId51" ref="N19"/>
+    <hyperlink r:id="rId52" ref="O19"/>
+    <hyperlink r:id="rId53" ref="P19"/>
+    <hyperlink r:id="rId54" ref="N20"/>
+    <hyperlink r:id="rId55" ref="O20"/>
+    <hyperlink r:id="rId56" ref="P20"/>
+    <hyperlink r:id="rId57" ref="N21"/>
+    <hyperlink r:id="rId58" ref="O21"/>
+    <hyperlink r:id="rId59" ref="P21"/>
+    <hyperlink r:id="rId60" ref="N22"/>
+    <hyperlink r:id="rId61" ref="P22"/>
+    <hyperlink r:id="rId62" ref="N23"/>
+    <hyperlink r:id="rId63" ref="O23"/>
+    <hyperlink r:id="rId64" ref="P23"/>
+    <hyperlink r:id="rId65" ref="N24"/>
+    <hyperlink r:id="rId66" ref="O24"/>
+    <hyperlink r:id="rId67" ref="P24"/>
+    <hyperlink r:id="rId68" ref="N25"/>
+    <hyperlink r:id="rId69" ref="O25"/>
+    <hyperlink r:id="rId70" ref="P25"/>
+    <hyperlink r:id="rId71" ref="N26"/>
+    <hyperlink r:id="rId72" ref="P26"/>
+    <hyperlink r:id="rId73" ref="N27"/>
+    <hyperlink r:id="rId74" ref="O27"/>
+    <hyperlink r:id="rId75" ref="P27"/>
+    <hyperlink r:id="rId76" ref="N28"/>
+    <hyperlink r:id="rId77" ref="O28"/>
+    <hyperlink r:id="rId78" ref="P28"/>
+    <hyperlink r:id="rId79" ref="O29"/>
+    <hyperlink r:id="rId80" ref="P29"/>
+    <hyperlink r:id="rId81" ref="N30"/>
+    <hyperlink r:id="rId82" ref="N31"/>
+    <hyperlink r:id="rId83" ref="O31"/>
+    <hyperlink r:id="rId84" ref="P31"/>
+    <hyperlink r:id="rId85" ref="N32"/>
+    <hyperlink r:id="rId86" ref="P32"/>
+    <hyperlink r:id="rId87" ref="N33"/>
+    <hyperlink r:id="rId88" ref="O33"/>
+    <hyperlink r:id="rId89" ref="P33"/>
+    <hyperlink r:id="rId90" ref="N34"/>
+    <hyperlink r:id="rId91" ref="O34"/>
+    <hyperlink r:id="rId92" ref="P34"/>
+    <hyperlink r:id="rId93" ref="N35"/>
+    <hyperlink r:id="rId94" ref="O35"/>
+    <hyperlink r:id="rId95" ref="P35"/>
+    <hyperlink r:id="rId96" ref="N36"/>
+    <hyperlink r:id="rId97" ref="O36"/>
+    <hyperlink r:id="rId98" ref="P36"/>
+    <hyperlink r:id="rId99" ref="N37"/>
+    <hyperlink r:id="rId100" ref="N38"/>
+    <hyperlink r:id="rId101" ref="O38"/>
+    <hyperlink r:id="rId102" ref="P38"/>
+    <hyperlink r:id="rId103" ref="N39"/>
+    <hyperlink r:id="rId104" ref="P39"/>
+    <hyperlink r:id="rId105" ref="N40"/>
+    <hyperlink r:id="rId106" ref="P40"/>
+    <hyperlink r:id="rId107" ref="N41"/>
+    <hyperlink r:id="rId108" ref="O41"/>
+    <hyperlink r:id="rId109" ref="P41"/>
+    <hyperlink r:id="rId110" ref="N42"/>
+    <hyperlink r:id="rId111" ref="O42"/>
+    <hyperlink r:id="rId112" ref="P42"/>
+    <hyperlink r:id="rId113" ref="N43"/>
+    <hyperlink r:id="rId114" ref="O43"/>
+    <hyperlink r:id="rId115" ref="P43"/>
+    <hyperlink r:id="rId116" ref="N44"/>
+    <hyperlink r:id="rId117" ref="O44"/>
+    <hyperlink r:id="rId118" ref="P44"/>
+    <hyperlink r:id="rId119" ref="N45"/>
+    <hyperlink r:id="rId120" ref="O45"/>
+    <hyperlink r:id="rId121" ref="P45"/>
+    <hyperlink r:id="rId122" ref="N46"/>
+    <hyperlink r:id="rId123" ref="O46"/>
+    <hyperlink r:id="rId124" ref="P46"/>
+    <hyperlink r:id="rId125" ref="N47"/>
+    <hyperlink r:id="rId126" ref="O47"/>
+    <hyperlink r:id="rId127" ref="P47"/>
+    <hyperlink r:id="rId128" ref="N48"/>
+    <hyperlink r:id="rId129" ref="O48"/>
+    <hyperlink r:id="rId130" ref="P48"/>
+    <hyperlink r:id="rId131" ref="N49"/>
+    <hyperlink r:id="rId132" ref="O49"/>
+    <hyperlink r:id="rId133" ref="P49"/>
+    <hyperlink r:id="rId134" ref="N50"/>
+    <hyperlink r:id="rId135" ref="P50"/>
+    <hyperlink r:id="rId136" ref="N51"/>
+    <hyperlink r:id="rId137" ref="O51"/>
+    <hyperlink r:id="rId138" ref="P51"/>
+    <hyperlink r:id="rId139" ref="N52"/>
+    <hyperlink r:id="rId140" ref="O52"/>
+    <hyperlink r:id="rId141" ref="P52"/>
+    <hyperlink r:id="rId142" ref="N53"/>
+    <hyperlink r:id="rId143" ref="O53"/>
+    <hyperlink r:id="rId144" ref="P53"/>
+    <hyperlink r:id="rId145" ref="N54"/>
+    <hyperlink r:id="rId146" ref="O54"/>
+    <hyperlink r:id="rId147" ref="P54"/>
+    <hyperlink r:id="rId148" ref="N55"/>
+    <hyperlink r:id="rId149" ref="O55"/>
+    <hyperlink r:id="rId150" ref="P55"/>
+    <hyperlink r:id="rId151" ref="N56"/>
+    <hyperlink r:id="rId152" ref="O56"/>
+    <hyperlink r:id="rId153" ref="P56"/>
+    <hyperlink r:id="rId154" ref="N57"/>
+    <hyperlink r:id="rId155" ref="O57"/>
+    <hyperlink r:id="rId156" ref="P57"/>
+    <hyperlink r:id="rId157" ref="N58"/>
+    <hyperlink r:id="rId158" ref="O58"/>
+    <hyperlink r:id="rId159" ref="P58"/>
+    <hyperlink r:id="rId160" ref="N59"/>
+    <hyperlink r:id="rId161" ref="O59"/>
+    <hyperlink r:id="rId162" ref="P59"/>
+    <hyperlink r:id="rId163" ref="N60"/>
+    <hyperlink r:id="rId164" ref="O60"/>
+    <hyperlink r:id="rId165" ref="P60"/>
+    <hyperlink r:id="rId166" ref="N61"/>
+    <hyperlink r:id="rId167" ref="O61"/>
+    <hyperlink r:id="rId168" ref="P61"/>
+    <hyperlink r:id="rId169" ref="N62"/>
+    <hyperlink r:id="rId170" ref="O62"/>
+    <hyperlink r:id="rId171" ref="P62"/>
+    <hyperlink r:id="rId172" ref="N63"/>
+    <hyperlink r:id="rId173" ref="O63"/>
+    <hyperlink r:id="rId174" ref="P63"/>
+    <hyperlink r:id="rId175" ref="N64"/>
+    <hyperlink r:id="rId176" ref="P64"/>
+    <hyperlink r:id="rId177" ref="N65"/>
+    <hyperlink r:id="rId178" ref="O65"/>
+    <hyperlink r:id="rId179" ref="P65"/>
+    <hyperlink r:id="rId180" ref="N66"/>
+    <hyperlink r:id="rId181" ref="O66"/>
+    <hyperlink r:id="rId182" ref="P66"/>
+    <hyperlink r:id="rId183" ref="N67"/>
+    <hyperlink r:id="rId184" ref="O67"/>
+    <hyperlink r:id="rId185" ref="P67"/>
+    <hyperlink r:id="rId186" ref="N68"/>
+    <hyperlink r:id="rId187" ref="O68"/>
+    <hyperlink r:id="rId188" ref="P68"/>
+    <hyperlink r:id="rId189" ref="N69"/>
+    <hyperlink r:id="rId190" ref="O69"/>
+    <hyperlink r:id="rId191" ref="P69"/>
+    <hyperlink r:id="rId192" ref="N70"/>
+    <hyperlink r:id="rId193" ref="O70"/>
+    <hyperlink r:id="rId194" ref="P70"/>
+    <hyperlink r:id="rId195" ref="N71"/>
+    <hyperlink r:id="rId196" ref="P71"/>
+    <hyperlink r:id="rId197" ref="N72"/>
+    <hyperlink r:id="rId198" ref="O72"/>
+    <hyperlink r:id="rId199" ref="P72"/>
+    <hyperlink r:id="rId200" ref="N73"/>
+    <hyperlink r:id="rId201" ref="O73"/>
+    <hyperlink r:id="rId202" ref="P73"/>
+    <hyperlink r:id="rId203" ref="N74"/>
+    <hyperlink r:id="rId204" ref="O74"/>
+    <hyperlink r:id="rId205" ref="P74"/>
+    <hyperlink r:id="rId206" ref="N75"/>
+    <hyperlink r:id="rId207" ref="P75"/>
+    <hyperlink r:id="rId208" ref="N76"/>
+    <hyperlink r:id="rId209" ref="P76"/>
+    <hyperlink r:id="rId210" ref="N77"/>
+    <hyperlink r:id="rId211" ref="O77"/>
+    <hyperlink r:id="rId212" ref="P77"/>
+    <hyperlink r:id="rId213" ref="N78"/>
+    <hyperlink r:id="rId214" ref="O78"/>
+    <hyperlink r:id="rId215" ref="P78"/>
+    <hyperlink r:id="rId216" ref="N79"/>
+    <hyperlink r:id="rId217" ref="O79"/>
+    <hyperlink r:id="rId218" ref="P79"/>
+    <hyperlink r:id="rId219" ref="N80"/>
+    <hyperlink r:id="rId220" ref="P80"/>
+    <hyperlink r:id="rId221" ref="N81"/>
+    <hyperlink r:id="rId222" ref="O81"/>
+    <hyperlink r:id="rId223" ref="P81"/>
+    <hyperlink r:id="rId224" ref="N82"/>
+    <hyperlink r:id="rId225" ref="O82"/>
+    <hyperlink r:id="rId226" ref="P82"/>
+    <hyperlink r:id="rId227" ref="N83"/>
+    <hyperlink r:id="rId228" ref="O83"/>
+    <hyperlink r:id="rId229" ref="P83"/>
+    <hyperlink r:id="rId230" ref="N84"/>
+    <hyperlink r:id="rId231" ref="O84"/>
+    <hyperlink r:id="rId232" ref="P84"/>
+    <hyperlink r:id="rId233" ref="N85"/>
+    <hyperlink r:id="rId234" ref="P85"/>
+    <hyperlink r:id="rId235" ref="N86"/>
+    <hyperlink r:id="rId236" ref="P86"/>
+    <hyperlink r:id="rId237" ref="N87"/>
+    <hyperlink r:id="rId238" ref="O87"/>
+    <hyperlink r:id="rId239" ref="P87"/>
+    <hyperlink r:id="rId240" ref="N88"/>
+    <hyperlink r:id="rId241" ref="P88"/>
   </hyperlinks>
-  <drawing r:id="rId202"/>
+  <drawing r:id="rId242"/>
 </worksheet>
 </file>
--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Poster List" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Poster List'!$A$1:$V$88</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Poster List'!$A$1:$V$89</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="396">
   <si>
     <t>Date</t>
   </si>
@@ -1189,6 +1189,18 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1DTZfAI2-cr8zUjzmdGRyWAb6RWkPrzMD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Bruno Mars</t>
+  </si>
+  <si>
+    <t>Andy Bird</t>
+  </si>
+  <si>
+    <t>Dana, Cheryl, Bill show</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YSz0Vz-OUK1tPrQpSZyiB_OfnW8iLOqD/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -5447,7 +5459,42 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10"/>
+      <c r="A89" s="1">
+        <v>46141.0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10"/>
@@ -8201,7 +8248,7 @@
       <c r="A1006" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$V$88"/>
+  <autoFilter ref="$A$1:$V$89"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="N2"/>
     <hyperlink r:id="rId2" ref="O2"/>
@@ -8444,7 +8491,8 @@
     <hyperlink r:id="rId239" ref="P87"/>
     <hyperlink r:id="rId240" ref="N88"/>
     <hyperlink r:id="rId241" ref="P88"/>
+    <hyperlink r:id="rId242" ref="P89"/>
   </hyperlinks>
-  <drawing r:id="rId242"/>
+  <drawing r:id="rId243"/>
 </worksheet>
 </file>
--- a/Poster Collection.xlsx
+++ b/Poster Collection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="397">
   <si>
     <t>Date</t>
   </si>
@@ -63,6 +63,9 @@
     <t>Stock Image</t>
   </si>
   <si>
+    <t>For Sale or Trade</t>
+  </si>
+  <si>
     <t>Faith No More</t>
   </si>
   <si>
@@ -219,6 +222,18 @@
     <t>https://drive.google.com/file/d/1fFctIb_RYxTDxFhpjmRfX3N5MCyJTUs0/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Robert Bowen</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/209954</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1P9bhD_skRhlxv5dsZSi4deoZ2vkGzWkh/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Foo Fighters</t>
   </si>
   <si>
@@ -294,6 +309,36 @@
     <t>https://drive.google.com/file/d/1Y-Rpnb-BhEi6cnj8J-uJogItdZFhIAUv/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Pearl Jam</t>
+  </si>
+  <si>
+    <t>Steve Thomas</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>Bonnaroo</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/225439</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1X_RmvN88PnkSxJuC3eQuLBdOtbOq0NXP/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Van Morrison</t>
+  </si>
+  <si>
+    <t>Neal Williams</t>
+  </si>
+  <si>
+    <t>Santa Barbara</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DTZfAI2-cr8zUjzmdGRyWAb6RWkPrzMD/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Metallica</t>
   </si>
   <si>
@@ -414,9 +459,6 @@
     <t>https://drive.google.com/file/d/1PPm8DH6HuJc3qBh95sAEMEBWcD5kEjiw/view?usp=drive_link</t>
   </si>
   <si>
-    <t>Pearl Jam</t>
-  </si>
-  <si>
     <t>Ian Williams</t>
   </si>
   <si>
@@ -510,6 +552,18 @@
     <t>https://drive.google.com/file/d/1ZcoDdTTyDQQRnSoGEHZSjDaQRhlPDjAr/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Lizzo</t>
+  </si>
+  <si>
+    <t>Mike Tallman</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18yqAiVsklcCyOuzNp_1tvlR_CUrVjSw-/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>428/750</t>
   </si>
   <si>
@@ -570,6 +624,51 @@
     <t>First concert with Lily</t>
   </si>
   <si>
+    <t>Rush</t>
+  </si>
+  <si>
+    <t>Swirl Foil</t>
+  </si>
+  <si>
+    <t>58/60</t>
+  </si>
+  <si>
+    <t>Fly by Night 45th Anniversary</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NbxG_SNzjnD4WTmZP6plmFymPA8IcQfm/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Daniel Martin Diaz</t>
+  </si>
+  <si>
+    <t>Metallic Gold Ink</t>
+  </si>
+  <si>
+    <t>7/150</t>
+  </si>
+  <si>
+    <t>Existential Reckoning Release Poster</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Q0dGsuVfBWpKT9WQDMysnGyqqo1tDkMJ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Byzewski </t>
+  </si>
+  <si>
+    <t>Round Foil</t>
+  </si>
+  <si>
+    <t>342/400</t>
+  </si>
+  <si>
+    <t>Billy D and the Hall of Feathered Serpents</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ms9EL_sm6TY6_PObmChJ6lMmUC-v8q9k/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>The Black Crowes</t>
   </si>
   <si>
@@ -666,6 +765,60 @@
     <t>15/250</t>
   </si>
   <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/319935</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mUj97ydq36XEpNGB9Ta6XkyYghKcQfhB/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>68/425</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/307474</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1j8WfbmFpxo8ODSiZ3hlzUkS5_cGzMFbN/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Pink Floyd</t>
+  </si>
+  <si>
+    <t>Cuyler Smith</t>
+  </si>
+  <si>
+    <t>3d Lenticular</t>
+  </si>
+  <si>
+    <t>73/250</t>
+  </si>
+  <si>
+    <t>Dark Side of the Moon</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18VkRWNuDBvdlw80Y6TXfHE5FX2BiWjKY/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Jermaine Rogers</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>39/167</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/306423</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HmAi3hIe4Xu2TdAAI_XX45py7rZSewgg/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Michael Hacker</t>
   </si>
   <si>
@@ -693,15 +846,30 @@
     <t>https://drive.google.com/file/d/1IaMV1J12N4wARQE3GhHl4F1JbjDClc2_/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Primus / Ween</t>
+  </si>
+  <si>
+    <t>Pot Leaf Foil</t>
+  </si>
+  <si>
+    <t>197/650</t>
+  </si>
+  <si>
+    <t>South Park 25th Anniversary</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/307782</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bE4Z-cx7oO9VCOg2MmoswcR-QyMgPVtF/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Rammstein</t>
   </si>
   <si>
     <t>Official / Zoran Bihac (Creative Dir)</t>
   </si>
   <si>
-    <t>Philadelphia</t>
-  </si>
-  <si>
     <t>https://expressobeans.com/public/detail.php/309873</t>
   </si>
   <si>
@@ -720,6 +888,33 @@
     <t>https://drive.google.com/file/d/11oBTGgWQYNDDksZWyi-0gVYj1MHQ7r-0/view?usp=drive_link</t>
   </si>
   <si>
+    <t>Mr. Bungle</t>
+  </si>
+  <si>
+    <t>Trey Spurance</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>Night 1 Poster</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/316870</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zctq7NFbCW9kFtjaD4iYpEW327dcXuQw/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Night 2 Poster</t>
+  </si>
+  <si>
+    <t>https://expressobeans.com/public/detail.php/316868</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lhIYa3ONjhygkm2FJ2LJhIdrfurQUmku/view?usp=drive_link</t>
+  </si>
+  <si>
     <t>Alex Kuno</t>
   </si>
   <si>
@@ -997,198 +1192,6 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1t0V2HQrDpkYGYF8XyljYkxtAdmIzeFDj/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Daniel Martin Diaz</t>
-  </si>
-  <si>
-    <t>Metallic Gold Ink</t>
-  </si>
-  <si>
-    <t>7/150</t>
-  </si>
-  <si>
-    <t>Existential Reckoning Release Poster</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Q0dGsuVfBWpKT9WQDMysnGyqqo1tDkMJ/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Byzewski </t>
-  </si>
-  <si>
-    <t>Round Foil</t>
-  </si>
-  <si>
-    <t>342/400</t>
-  </si>
-  <si>
-    <t>Billy D and the Hall of Feathered Serpents</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Ms9EL_sm6TY6_PObmChJ6lMmUC-v8q9k/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Franklin</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/319935</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1mUj97ydq36XEpNGB9Ta6XkyYghKcQfhB/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Jermaine Rogers</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>39/167</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/306423</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HmAi3hIe4Xu2TdAAI_XX45py7rZSewgg/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>68/425</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/307474</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1j8WfbmFpxo8ODSiZ3hlzUkS5_cGzMFbN/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Rush</t>
-  </si>
-  <si>
-    <t>Swirl Foil</t>
-  </si>
-  <si>
-    <t>58/60</t>
-  </si>
-  <si>
-    <t>Fly by Night 45th Anniversary</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1NbxG_SNzjnD4WTmZP6plmFymPA8IcQfm/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Robert Bowen</t>
-  </si>
-  <si>
-    <t>Hamburg</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/209954</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1P9bhD_skRhlxv5dsZSi4deoZ2vkGzWkh/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Mr. Bungle</t>
-  </si>
-  <si>
-    <t>Trey Spurance</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>Night 1 Poster</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/316870</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zctq7NFbCW9kFtjaD4iYpEW327dcXuQw/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Night 2 Poster</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/316868</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1lhIYa3ONjhygkm2FJ2LJhIdrfurQUmku/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Primus / Ween</t>
-  </si>
-  <si>
-    <t>Pot Leaf Foil</t>
-  </si>
-  <si>
-    <t>197/650</t>
-  </si>
-  <si>
-    <t>South Park 25th Anniversary</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/307782</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bE4Z-cx7oO9VCOg2MmoswcR-QyMgPVtF/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Pink Floyd</t>
-  </si>
-  <si>
-    <t>Cuyler Smith</t>
-  </si>
-  <si>
-    <t>3d Lenticular</t>
-  </si>
-  <si>
-    <t>73/250</t>
-  </si>
-  <si>
-    <t>Dark Side of the Moon</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/18VkRWNuDBvdlw80Y6TXfHE5FX2BiWjKY/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Lizzo</t>
-  </si>
-  <si>
-    <t>Mike Tallman</t>
-  </si>
-  <si>
-    <t>Denver</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/18yqAiVsklcCyOuzNp_1tvlR_CUrVjSw-/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Steve Thomas</t>
-  </si>
-  <si>
-    <t>Manchester</t>
-  </si>
-  <si>
-    <t>Bonnaroo</t>
-  </si>
-  <si>
-    <t>https://expressobeans.com/public/detail.php/225439</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1X_RmvN88PnkSxJuC3eQuLBdOtbOq0NXP/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Van Morrison</t>
-  </si>
-  <si>
-    <t>Neal Williams</t>
-  </si>
-  <si>
-    <t>Santa Barbara</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DTZfAI2-cr8zUjzmdGRyWAb6RWkPrzMD/view?usp=drive_link</t>
   </si>
   <si>
     <t>Bruno Mars</t>
@@ -1501,9 +1504,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="12" max="12" width="35.63"/>
-    <col customWidth="1" min="14" max="14" width="15.13"/>
-    <col customWidth="1" min="15" max="15" width="40.5"/>
+    <col hidden="1" min="8" max="9" width="12.63"/>
+    <col customWidth="1" hidden="1" min="12" max="12" width="35.63"/>
+    <col hidden="1" min="13" max="13" width="12.63"/>
+    <col customWidth="1" hidden="1" min="14" max="14" width="15.13"/>
+    <col customWidth="1" hidden="1" min="15" max="15" width="40.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1555,97 +1560,106 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" hidden="1">
       <c r="A2" s="1">
         <v>40364.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" hidden="1">
       <c r="A3" s="1">
         <v>41091.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -1653,44 +1667,47 @@
         <v>41568.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M4" s="2">
         <v>18.0</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -1698,647 +1715,677 @@
         <v>41669.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" s="2">
         <v>28.0</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" hidden="1">
       <c r="A6" s="1">
         <v>41832.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" hidden="1">
       <c r="A7" s="1">
         <v>41862.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" hidden="1">
       <c r="A8" s="1">
         <v>41899.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>62</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" hidden="1">
       <c r="A9" s="1">
         <v>42135.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>42204.0</v>
+        <v>42178.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="Q10" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="1">
+        <v>42204.0</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1">
-        <v>42216.0</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>78</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" hidden="1">
       <c r="A12" s="1">
-        <v>42318.0</v>
+        <v>42216.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="P12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="3" t="s">
+      <c r="Q12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="1">
+        <v>42318.0</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1">
-        <v>42395.0</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="M13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>88</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="Q13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" hidden="1">
       <c r="A14" s="1">
-        <v>42479.0</v>
+        <v>42395.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="1">
+        <v>42479.0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1">
-        <v>42874.0</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>95</v>
+        <v>27</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>42879.0</v>
+        <v>42532.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>33</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M16" s="2">
-        <v>22.0</v>
+        <v>101</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="4" t="s">
         <v>102</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>42879.0</v>
+        <v>42658.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" s="1">
+        <v>42874.0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="E18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7">
-        <v>42934.0</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="P18" s="4" t="s">
         <v>110</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>42958.0</v>
+        <v>42879.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>112</v>
@@ -2347,32 +2394,32 @@
         <v>113</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
         <v>114</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>115</v>
       </c>
       <c r="M19" s="2">
-        <v>40.0</v>
+        <v>22.0</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>116</v>
@@ -2380,598 +2427,646 @@
       <c r="P19" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="Q19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" hidden="1">
       <c r="A20" s="1">
-        <v>43005.0</v>
+        <v>42879.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="N20" s="6"/>
       <c r="O20" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7">
+        <v>42934.0</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1">
-        <v>43018.0</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="M21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="P21" s="4" t="s">
         <v>125</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>43238.0</v>
+        <v>42958.0</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>25</v>
+        <v>25</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="M22" s="2">
+        <v>40.0</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>27</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" hidden="1">
       <c r="A23" s="1">
-        <v>43240.0</v>
+        <v>43005.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>134</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" hidden="1">
       <c r="A24" s="1">
-        <v>43347.0</v>
+        <v>43018.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>27</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" hidden="1">
       <c r="A25" s="1">
-        <v>43405.0</v>
+        <v>43238.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" hidden="1">
+      <c r="A26" s="1">
+        <v>43240.0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>43405.0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" hidden="1">
+      <c r="A27" s="1">
+        <v>43347.0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>43493.0</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="2">
-        <v>36.0</v>
+        <v>25</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>150</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" hidden="1">
       <c r="A28" s="1">
-        <v>43493.0</v>
+        <v>43405.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" hidden="1">
+      <c r="A29" s="1">
+        <v>43405.0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N28" s="3" t="s">
+      <c r="I29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O28" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7">
-        <v>43536.0</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>152</v>
+      <c r="N29" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>43561.0</v>
+        <v>43493.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" hidden="1">
+      <c r="A31" s="1">
+        <v>43493.0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M30" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>43595.0</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7">
+        <v>43536.0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>43733.0</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="M32" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>43788.0</v>
+        <v>43561.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>24</v>
@@ -2980,94 +3075,88 @@
         <v>24</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>25</v>
+        <v>25</v>
+      </c>
+      <c r="M33" s="2">
+        <v>30.0</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>27</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" hidden="1">
       <c r="A34" s="1">
-        <v>43793.0</v>
+        <v>43595.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>43844.0</v>
-      </c>
-      <c r="B35" s="2" t="s">
+        <v>43733.0</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>24</v>
@@ -3076,309 +3165,332 @@
         <v>24</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>177</v>
+      </c>
+      <c r="M35" s="2">
+        <v>23.0</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <v>43847.0</v>
+        <v>43753.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" s="2"/>
+        <v>20</v>
+      </c>
       <c r="G36" s="2" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="2">
-        <v>15.0</v>
-      </c>
       <c r="N36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="P36" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="Q36" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" hidden="1">
       <c r="A37" s="1">
-        <v>43869.0</v>
+        <v>43788.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>154</v>
+        <v>90</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>33</v>
+        <v>183</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="M37" s="2">
-        <v>31.0</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="P37" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" hidden="1">
       <c r="A38" s="1">
-        <v>44450.0</v>
+        <v>43793.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>185</v>
+        <v>90</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>186</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
         <v>187</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M38" s="2">
-        <v>21.0</v>
+        <v>25</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="3" t="s">
         <v>188</v>
       </c>
       <c r="P38" s="4" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="Q38" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" hidden="1">
       <c r="A39" s="1">
-        <v>44468.0</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>111</v>
+        <v>43844.0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>190</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="L39" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="M39" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>192</v>
+        <v>27</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <v>44511.0</v>
+        <v>43847.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>33</v>
+        <v>198</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>25</v>
+        <v>25</v>
+      </c>
+      <c r="M40" s="2">
+        <v>15.0</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>44519.0</v>
+        <v>43869.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="M41" s="2">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>201</v>
+        <v>27</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>44614.0</v>
+        <v>44054.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>203</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="G42" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>24</v>
@@ -3390,46 +3502,42 @@
         <v>24</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="P42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="4" t="s">
         <v>207</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>44640.0</v>
+        <v>44134.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>24</v>
@@ -3437,1992 +3545,2143 @@
       <c r="K43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>25</v>
+      <c r="L43" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>211</v>
+        <v>27</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>44679.0</v>
+        <v>44303.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>39</v>
+        <v>213</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G44" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="2">
-        <v>19.0</v>
+      <c r="L44" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>215</v>
+        <v>27</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>44679.0</v>
+        <v>44450.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" hidden="1">
+      <c r="A46" s="1">
+        <v>44468.0</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M45" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="N45" s="3" t="s">
+      <c r="I46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O45" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1">
-        <v>44734.0</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="N46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" hidden="1">
+      <c r="A47" s="1">
+        <v>44511.0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1">
-        <v>44773.0</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M47" s="2">
-        <v>25.0</v>
-      </c>
       <c r="N47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>225</v>
+        <v>27</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>44804.0</v>
+        <v>44519.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>227</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" hidden="1">
+      <c r="A49" s="1">
+        <v>44614.0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M48" s="2">
-        <v>33.0</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1">
-        <v>44866.0</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" hidden="1">
+      <c r="A50" s="1">
+        <v>44640.0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M49" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="N49" s="3" t="s">
+      <c r="I50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1">
-        <v>45064.0</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M50" s="2">
-        <v>14.0</v>
-      </c>
       <c r="N50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>234</v>
+        <v>27</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>45067.0</v>
+        <v>44679.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M51" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>238</v>
+        <v>27</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>45142.0</v>
+        <v>44679.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9">
+        <v>44682.0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="M52" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1">
-        <v>45144.0</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="I53" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="M53" s="2">
-        <v>13.0</v>
+        <v>24</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="P53" s="3" t="s">
-        <v>248</v>
+        <v>27</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>45213.0</v>
+        <v>44705.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>249</v>
+        <v>38</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" s="2"/>
+        <v>33</v>
+      </c>
       <c r="G54" s="2" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2">
-        <v>4.0</v>
-      </c>
       <c r="N54" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>45228.0</v>
+        <v>44710.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>39</v>
+        <v>258</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>33</v>
+        <v>260</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M55" s="2">
-        <v>1.0</v>
+      <c r="L55" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>256</v>
+        <v>27</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>45228.0</v>
+        <v>44713.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F56" s="2"/>
+        <v>33</v>
+      </c>
       <c r="G56" s="2" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" hidden="1">
+      <c r="A57" s="1">
+        <v>44734.0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M56" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="N56" s="3" t="s">
+      <c r="I57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O56" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1">
-        <v>45239.0</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M57" s="2">
-        <v>10.0</v>
-      </c>
       <c r="N57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>264</v>
+        <v>27</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <v>45312.0</v>
+        <v>44773.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>85</v>
+        <v>273</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>266</v>
+        <v>34</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M58" s="2">
-        <v>16.0</v>
+        <v>25.0</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <v>45312.0</v>
+        <v>44782.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>85</v>
+        <v>277</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F59" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="G59" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M59" s="2">
-        <v>27.0</v>
+      <c r="L59" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>267</v>
+        <v>27</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1">
-        <v>45340.0</v>
+        <v>44804.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>25</v>
+        <v>25</v>
+      </c>
+      <c r="M60" s="2">
+        <v>33.0</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1">
-        <v>45389.0</v>
+        <v>44866.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2" t="s">
-        <v>33</v>
+        <v>287</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M61" s="2">
-        <v>7.0</v>
+        <v>26.0</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1">
-        <v>45389.0</v>
+        <v>45064.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>276</v>
+        <v>226</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>280</v>
+        <v>133</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F62" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="G62" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>276</v>
+        <v>25</v>
       </c>
       <c r="M62" s="2">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>281</v>
+        <v>27</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1">
-        <v>45389.0</v>
+        <v>45065.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>39</v>
+        <v>293</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>284</v>
+        <v>34</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9">
+        <v>45066.0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1">
-        <v>45428.0</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="I64" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M64" s="2">
-        <v>5.0</v>
+      <c r="L64" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>289</v>
+        <v>27</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
-        <v>45469.0</v>
+        <v>45067.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F65" s="2"/>
       <c r="G65" s="2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M65" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" s="4" t="s">
-        <v>293</v>
+        <v>27</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>302</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>294</v>
+        <v>303</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1">
-        <v>45469.0</v>
+        <v>45142.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>39</v>
+        <v>305</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2" t="s">
-        <v>33</v>
+        <v>306</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="M66" s="2">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>295</v>
+        <v>309</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1">
-        <v>45783.0</v>
+        <v>45144.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>296</v>
+        <v>108</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>39</v>
+        <v>305</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F67" s="2"/>
       <c r="G67" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="L67" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="M67" s="2">
-        <v>38.0</v>
+        <v>13.0</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>300</v>
+        <v>312</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1">
-        <v>45790.0</v>
+        <v>45213.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>133</v>
+        <v>314</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>106</v>
+        <v>315</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>39</v>
+        <v>197</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L68" s="2"/>
       <c r="M68" s="2">
-        <v>32.0</v>
+        <v>4.0</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>302</v>
+        <v>317</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1">
-        <v>45808.0</v>
+        <v>45228.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>93</v>
+        <v>318</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F69" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="G69" s="2" t="s">
-        <v>304</v>
+        <v>34</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>305</v>
+        <v>25</v>
       </c>
       <c r="M69" s="2">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>307</v>
+        <v>321</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1">
-        <v>45808.0</v>
+        <v>45228.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>93</v>
+        <v>318</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M70" s="2">
-        <v>37.0</v>
+        <v>2.0</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>310</v>
+        <v>27</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>324</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>311</v>
+        <v>325</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <v>45897.0</v>
+        <v>45239.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>194</v>
+        <v>327</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M71" s="2">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>313</v>
+        <v>27</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1">
-        <v>45905.0</v>
+        <v>45312.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>314</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F72" s="2"/>
       <c r="G72" s="2" t="s">
-        <v>33</v>
+        <v>331</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>315</v>
+        <v>25</v>
       </c>
       <c r="M72" s="2">
-        <v>35.0</v>
+        <v>16.0</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>317</v>
+        <v>332</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1">
-        <v>46113.0</v>
+        <v>45312.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>320</v>
+        <v>25</v>
       </c>
       <c r="M73" s="2">
-        <v>11.0</v>
+        <v>27.0</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1">
-        <v>46129.0</v>
+        <v>45340.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>323</v>
+        <v>90</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F74" s="2"/>
+        <v>33</v>
+      </c>
       <c r="G74" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M74" s="2">
-        <v>39.0</v>
+        <v>25</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>327</v>
+        <v>340</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1">
-        <v>44134.0</v>
+        <v>45389.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>329</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="2" t="s">
-        <v>330</v>
+        <v>34</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>331</v>
+        <v>25</v>
+      </c>
+      <c r="M75" s="2">
+        <v>7.0</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>332</v>
+        <v>344</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1">
-        <v>44303.0</v>
+        <v>45389.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>333</v>
+        <v>345</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>334</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="2" t="s">
-        <v>335</v>
+        <v>34</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M76" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1">
+        <v>45389.0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N76" s="3" t="s">
+      <c r="I77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P76" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="9">
-        <v>44682.0</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="N77" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O77" s="4" t="s">
-        <v>339</v>
+        <v>27</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1">
-        <v>44713.0</v>
+        <v>45428.0</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>342</v>
+        <v>142</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>343</v>
+        <v>34</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M78" s="2">
+        <v>5.0</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>344</v>
+        <v>27</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>345</v>
+        <v>354</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1">
-        <v>44705.0</v>
+        <v>45469.0</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>212</v>
+        <v>356</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M79" s="2">
+        <v>3.0</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="3" t="s">
-        <v>347</v>
+        <v>27</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>358</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>348</v>
+        <v>359</v>
+      </c>
+      <c r="Q79" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1">
-        <v>44054.0</v>
+        <v>45469.0</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>53</v>
+        <v>356</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>350</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F80" s="2"/>
       <c r="G80" s="2" t="s">
-        <v>351</v>
+        <v>34</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>352</v>
+        <v>25</v>
+      </c>
+      <c r="M80" s="2">
+        <v>6.0</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>358</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1">
-        <v>42178.0</v>
+        <v>45783.0</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>361</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>355</v>
+        <v>40</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>33</v>
+        <v>363</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M81" s="2">
+        <v>38.0</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>357</v>
+        <v>365</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1">
-        <v>45065.0</v>
+        <v>45790.0</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>359</v>
+        <v>121</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>360</v>
+        <v>40</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F82" s="2"/>
       <c r="G82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M82" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1">
+        <v>45808.0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H82" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J82" s="2" t="s">
+      <c r="F83" s="2"/>
+      <c r="G83" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O82" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="P82" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9">
-        <v>45066.0</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="I83" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
+      </c>
+      <c r="M83" s="2">
+        <v>8.0</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" s="4" t="s">
-        <v>365</v>
+        <v>27</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1">
-        <v>44782.0</v>
+        <v>45808.0</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>367</v>
+        <v>108</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>69</v>
+        <v>373</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>368</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F84" s="2"/>
       <c r="G84" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>370</v>
+        <v>25</v>
+      </c>
+      <c r="M84" s="2">
+        <v>37.0</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="P84" s="4" t="s">
-        <v>372</v>
+        <v>27</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="P84" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1">
-        <v>44710.0</v>
+        <v>45897.0</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>374</v>
+        <v>227</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>375</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F85" s="2"/>
       <c r="G85" s="2" t="s">
-        <v>376</v>
+        <v>34</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>377</v>
+        <v>25</v>
+      </c>
+      <c r="M85" s="2">
+        <v>34.0</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P85" s="3" t="s">
         <v>378</v>
+      </c>
+      <c r="Q85" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1">
-        <v>43753.0</v>
+        <v>45905.0</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="G86" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="M86" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O86" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N86" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P86" s="4" t="s">
+      <c r="P86" s="3" t="s">
         <v>382</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1">
-        <v>42532.0</v>
+        <v>46113.0</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>383</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H87" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>385</v>
       </c>
+      <c r="M87" s="2">
+        <v>11.0</v>
+      </c>
       <c r="N87" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O87" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="P87" s="4" t="s">
+      <c r="P87" s="3" t="s">
         <v>387</v>
+      </c>
+      <c r="Q87" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1">
-        <v>42658.0</v>
+        <v>46129.0</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>388</v>
@@ -5431,31 +5690,41 @@
         <v>389</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H88" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M88" s="2">
+        <v>39.0</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>391</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="89">
@@ -5463,37 +5732,40 @@
         <v>46141.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
+      </c>
+      <c r="Q89" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="90">
@@ -8248,7 +8520,13 @@
       <c r="A1006" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$V$89"/>
+  <autoFilter ref="$A$1:$V$89">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="No"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="N2"/>
     <hyperlink r:id="rId2" ref="O2"/>
@@ -8295,7 +8573,7 @@
     <hyperlink r:id="rId43" ref="N16"/>
     <hyperlink r:id="rId44" ref="O16"/>
     <hyperlink r:id="rId45" ref="P16"/>
-    <hyperlink r:id="rId46" ref="O17"/>
+    <hyperlink r:id="rId46" ref="N17"/>
     <hyperlink r:id="rId47" ref="P17"/>
     <hyperlink r:id="rId48" ref="N18"/>
     <hyperlink r:id="rId49" ref="O18"/>
@@ -8303,13 +8581,13 @@
     <hyperlink r:id="rId51" ref="N19"/>
     <hyperlink r:id="rId52" ref="O19"/>
     <hyperlink r:id="rId53" ref="P19"/>
-    <hyperlink r:id="rId54" ref="N20"/>
-    <hyperlink r:id="rId55" ref="O20"/>
-    <hyperlink r:id="rId56" ref="P20"/>
-    <hyperlink r:id="rId57" ref="N21"/>
-    <hyperlink r:id="rId58" ref="O21"/>
-    <hyperlink r:id="rId59" ref="P21"/>
-    <hyperlink r:id="rId60" ref="N22"/>
+    <hyperlink r:id="rId54" ref="O20"/>
+    <hyperlink r:id="rId55" ref="P20"/>
+    <hyperlink r:id="rId56" ref="N21"/>
+    <hyperlink r:id="rId57" ref="O21"/>
+    <hyperlink r:id="rId58" ref="P21"/>
+    <hyperlink r:id="rId59" ref="N22"/>
+    <hyperlink r:id="rId60" ref="O22"/>
     <hyperlink r:id="rId61" ref="P22"/>
     <hyperlink r:id="rId62" ref="N23"/>
     <hyperlink r:id="rId63" ref="O23"/>
@@ -8318,9 +8596,9 @@
     <hyperlink r:id="rId66" ref="O24"/>
     <hyperlink r:id="rId67" ref="P24"/>
     <hyperlink r:id="rId68" ref="N25"/>
-    <hyperlink r:id="rId69" ref="O25"/>
-    <hyperlink r:id="rId70" ref="P25"/>
-    <hyperlink r:id="rId71" ref="N26"/>
+    <hyperlink r:id="rId69" ref="P25"/>
+    <hyperlink r:id="rId70" ref="N26"/>
+    <hyperlink r:id="rId71" ref="O26"/>
     <hyperlink r:id="rId72" ref="P26"/>
     <hyperlink r:id="rId73" ref="N27"/>
     <hyperlink r:id="rId74" ref="O27"/>
@@ -8328,168 +8606,168 @@
     <hyperlink r:id="rId76" ref="N28"/>
     <hyperlink r:id="rId77" ref="O28"/>
     <hyperlink r:id="rId78" ref="P28"/>
-    <hyperlink r:id="rId79" ref="O29"/>
+    <hyperlink r:id="rId79" ref="N29"/>
     <hyperlink r:id="rId80" ref="P29"/>
     <hyperlink r:id="rId81" ref="N30"/>
-    <hyperlink r:id="rId82" ref="N31"/>
-    <hyperlink r:id="rId83" ref="O31"/>
-    <hyperlink r:id="rId84" ref="P31"/>
-    <hyperlink r:id="rId85" ref="N32"/>
-    <hyperlink r:id="rId86" ref="P32"/>
-    <hyperlink r:id="rId87" ref="N33"/>
-    <hyperlink r:id="rId88" ref="O33"/>
-    <hyperlink r:id="rId89" ref="P33"/>
+    <hyperlink r:id="rId82" ref="O30"/>
+    <hyperlink r:id="rId83" ref="P30"/>
+    <hyperlink r:id="rId84" ref="N31"/>
+    <hyperlink r:id="rId85" ref="O31"/>
+    <hyperlink r:id="rId86" ref="P31"/>
+    <hyperlink r:id="rId87" ref="O32"/>
+    <hyperlink r:id="rId88" ref="P32"/>
+    <hyperlink r:id="rId89" ref="N33"/>
     <hyperlink r:id="rId90" ref="N34"/>
     <hyperlink r:id="rId91" ref="O34"/>
     <hyperlink r:id="rId92" ref="P34"/>
     <hyperlink r:id="rId93" ref="N35"/>
-    <hyperlink r:id="rId94" ref="O35"/>
-    <hyperlink r:id="rId95" ref="P35"/>
-    <hyperlink r:id="rId96" ref="N36"/>
-    <hyperlink r:id="rId97" ref="O36"/>
-    <hyperlink r:id="rId98" ref="P36"/>
-    <hyperlink r:id="rId99" ref="N37"/>
+    <hyperlink r:id="rId94" ref="P35"/>
+    <hyperlink r:id="rId95" ref="N36"/>
+    <hyperlink r:id="rId96" ref="P36"/>
+    <hyperlink r:id="rId97" ref="N37"/>
+    <hyperlink r:id="rId98" ref="O37"/>
+    <hyperlink r:id="rId99" ref="P37"/>
     <hyperlink r:id="rId100" ref="N38"/>
     <hyperlink r:id="rId101" ref="O38"/>
     <hyperlink r:id="rId102" ref="P38"/>
     <hyperlink r:id="rId103" ref="N39"/>
-    <hyperlink r:id="rId104" ref="P39"/>
-    <hyperlink r:id="rId105" ref="N40"/>
-    <hyperlink r:id="rId106" ref="P40"/>
-    <hyperlink r:id="rId107" ref="N41"/>
-    <hyperlink r:id="rId108" ref="O41"/>
-    <hyperlink r:id="rId109" ref="P41"/>
+    <hyperlink r:id="rId104" ref="O39"/>
+    <hyperlink r:id="rId105" ref="P39"/>
+    <hyperlink r:id="rId106" ref="N40"/>
+    <hyperlink r:id="rId107" ref="O40"/>
+    <hyperlink r:id="rId108" ref="P40"/>
+    <hyperlink r:id="rId109" ref="N41"/>
     <hyperlink r:id="rId110" ref="N42"/>
-    <hyperlink r:id="rId111" ref="O42"/>
-    <hyperlink r:id="rId112" ref="P42"/>
-    <hyperlink r:id="rId113" ref="N43"/>
-    <hyperlink r:id="rId114" ref="O43"/>
-    <hyperlink r:id="rId115" ref="P43"/>
-    <hyperlink r:id="rId116" ref="N44"/>
-    <hyperlink r:id="rId117" ref="O44"/>
-    <hyperlink r:id="rId118" ref="P44"/>
-    <hyperlink r:id="rId119" ref="N45"/>
-    <hyperlink r:id="rId120" ref="O45"/>
-    <hyperlink r:id="rId121" ref="P45"/>
-    <hyperlink r:id="rId122" ref="N46"/>
-    <hyperlink r:id="rId123" ref="O46"/>
-    <hyperlink r:id="rId124" ref="P46"/>
-    <hyperlink r:id="rId125" ref="N47"/>
-    <hyperlink r:id="rId126" ref="O47"/>
-    <hyperlink r:id="rId127" ref="P47"/>
-    <hyperlink r:id="rId128" ref="N48"/>
-    <hyperlink r:id="rId129" ref="O48"/>
-    <hyperlink r:id="rId130" ref="P48"/>
-    <hyperlink r:id="rId131" ref="N49"/>
-    <hyperlink r:id="rId132" ref="O49"/>
-    <hyperlink r:id="rId133" ref="P49"/>
-    <hyperlink r:id="rId134" ref="N50"/>
-    <hyperlink r:id="rId135" ref="P50"/>
-    <hyperlink r:id="rId136" ref="N51"/>
-    <hyperlink r:id="rId137" ref="O51"/>
-    <hyperlink r:id="rId138" ref="P51"/>
-    <hyperlink r:id="rId139" ref="N52"/>
-    <hyperlink r:id="rId140" ref="O52"/>
-    <hyperlink r:id="rId141" ref="P52"/>
-    <hyperlink r:id="rId142" ref="N53"/>
-    <hyperlink r:id="rId143" ref="O53"/>
-    <hyperlink r:id="rId144" ref="P53"/>
-    <hyperlink r:id="rId145" ref="N54"/>
-    <hyperlink r:id="rId146" ref="O54"/>
-    <hyperlink r:id="rId147" ref="P54"/>
-    <hyperlink r:id="rId148" ref="N55"/>
-    <hyperlink r:id="rId149" ref="O55"/>
-    <hyperlink r:id="rId150" ref="P55"/>
-    <hyperlink r:id="rId151" ref="N56"/>
-    <hyperlink r:id="rId152" ref="O56"/>
-    <hyperlink r:id="rId153" ref="P56"/>
-    <hyperlink r:id="rId154" ref="N57"/>
-    <hyperlink r:id="rId155" ref="O57"/>
-    <hyperlink r:id="rId156" ref="P57"/>
-    <hyperlink r:id="rId157" ref="N58"/>
-    <hyperlink r:id="rId158" ref="O58"/>
-    <hyperlink r:id="rId159" ref="P58"/>
-    <hyperlink r:id="rId160" ref="N59"/>
-    <hyperlink r:id="rId161" ref="O59"/>
-    <hyperlink r:id="rId162" ref="P59"/>
-    <hyperlink r:id="rId163" ref="N60"/>
-    <hyperlink r:id="rId164" ref="O60"/>
-    <hyperlink r:id="rId165" ref="P60"/>
-    <hyperlink r:id="rId166" ref="N61"/>
-    <hyperlink r:id="rId167" ref="O61"/>
-    <hyperlink r:id="rId168" ref="P61"/>
-    <hyperlink r:id="rId169" ref="N62"/>
-    <hyperlink r:id="rId170" ref="O62"/>
-    <hyperlink r:id="rId171" ref="P62"/>
-    <hyperlink r:id="rId172" ref="N63"/>
-    <hyperlink r:id="rId173" ref="O63"/>
-    <hyperlink r:id="rId174" ref="P63"/>
-    <hyperlink r:id="rId175" ref="N64"/>
-    <hyperlink r:id="rId176" ref="P64"/>
-    <hyperlink r:id="rId177" ref="N65"/>
-    <hyperlink r:id="rId178" ref="O65"/>
-    <hyperlink r:id="rId179" ref="P65"/>
-    <hyperlink r:id="rId180" ref="N66"/>
-    <hyperlink r:id="rId181" ref="O66"/>
-    <hyperlink r:id="rId182" ref="P66"/>
-    <hyperlink r:id="rId183" ref="N67"/>
-    <hyperlink r:id="rId184" ref="O67"/>
-    <hyperlink r:id="rId185" ref="P67"/>
-    <hyperlink r:id="rId186" ref="N68"/>
-    <hyperlink r:id="rId187" ref="O68"/>
-    <hyperlink r:id="rId188" ref="P68"/>
-    <hyperlink r:id="rId189" ref="N69"/>
-    <hyperlink r:id="rId190" ref="O69"/>
-    <hyperlink r:id="rId191" ref="P69"/>
-    <hyperlink r:id="rId192" ref="N70"/>
-    <hyperlink r:id="rId193" ref="O70"/>
-    <hyperlink r:id="rId194" ref="P70"/>
-    <hyperlink r:id="rId195" ref="N71"/>
-    <hyperlink r:id="rId196" ref="P71"/>
-    <hyperlink r:id="rId197" ref="N72"/>
-    <hyperlink r:id="rId198" ref="O72"/>
-    <hyperlink r:id="rId199" ref="P72"/>
-    <hyperlink r:id="rId200" ref="N73"/>
-    <hyperlink r:id="rId201" ref="O73"/>
-    <hyperlink r:id="rId202" ref="P73"/>
-    <hyperlink r:id="rId203" ref="N74"/>
-    <hyperlink r:id="rId204" ref="O74"/>
-    <hyperlink r:id="rId205" ref="P74"/>
-    <hyperlink r:id="rId206" ref="N75"/>
-    <hyperlink r:id="rId207" ref="P75"/>
-    <hyperlink r:id="rId208" ref="N76"/>
-    <hyperlink r:id="rId209" ref="P76"/>
-    <hyperlink r:id="rId210" ref="N77"/>
-    <hyperlink r:id="rId211" ref="O77"/>
-    <hyperlink r:id="rId212" ref="P77"/>
-    <hyperlink r:id="rId213" ref="N78"/>
-    <hyperlink r:id="rId214" ref="O78"/>
-    <hyperlink r:id="rId215" ref="P78"/>
-    <hyperlink r:id="rId216" ref="N79"/>
-    <hyperlink r:id="rId217" ref="O79"/>
-    <hyperlink r:id="rId218" ref="P79"/>
-    <hyperlink r:id="rId219" ref="N80"/>
-    <hyperlink r:id="rId220" ref="P80"/>
-    <hyperlink r:id="rId221" ref="N81"/>
-    <hyperlink r:id="rId222" ref="O81"/>
-    <hyperlink r:id="rId223" ref="P81"/>
-    <hyperlink r:id="rId224" ref="N82"/>
-    <hyperlink r:id="rId225" ref="O82"/>
-    <hyperlink r:id="rId226" ref="P82"/>
-    <hyperlink r:id="rId227" ref="N83"/>
-    <hyperlink r:id="rId228" ref="O83"/>
-    <hyperlink r:id="rId229" ref="P83"/>
-    <hyperlink r:id="rId230" ref="N84"/>
-    <hyperlink r:id="rId231" ref="O84"/>
-    <hyperlink r:id="rId232" ref="P84"/>
-    <hyperlink r:id="rId233" ref="N85"/>
-    <hyperlink r:id="rId234" ref="P85"/>
-    <hyperlink r:id="rId235" ref="N86"/>
-    <hyperlink r:id="rId236" ref="P86"/>
-    <hyperlink r:id="rId237" ref="N87"/>
-    <hyperlink r:id="rId238" ref="O87"/>
-    <hyperlink r:id="rId239" ref="P87"/>
-    <hyperlink r:id="rId240" ref="N88"/>
+    <hyperlink r:id="rId111" ref="P42"/>
+    <hyperlink r:id="rId112" ref="N43"/>
+    <hyperlink r:id="rId113" ref="P43"/>
+    <hyperlink r:id="rId114" ref="N44"/>
+    <hyperlink r:id="rId115" ref="P44"/>
+    <hyperlink r:id="rId116" ref="N45"/>
+    <hyperlink r:id="rId117" ref="O45"/>
+    <hyperlink r:id="rId118" ref="P45"/>
+    <hyperlink r:id="rId119" ref="N46"/>
+    <hyperlink r:id="rId120" ref="P46"/>
+    <hyperlink r:id="rId121" ref="N47"/>
+    <hyperlink r:id="rId122" ref="P47"/>
+    <hyperlink r:id="rId123" ref="N48"/>
+    <hyperlink r:id="rId124" ref="O48"/>
+    <hyperlink r:id="rId125" ref="P48"/>
+    <hyperlink r:id="rId126" ref="N49"/>
+    <hyperlink r:id="rId127" ref="O49"/>
+    <hyperlink r:id="rId128" ref="P49"/>
+    <hyperlink r:id="rId129" ref="N50"/>
+    <hyperlink r:id="rId130" ref="O50"/>
+    <hyperlink r:id="rId131" ref="P50"/>
+    <hyperlink r:id="rId132" ref="N51"/>
+    <hyperlink r:id="rId133" ref="O51"/>
+    <hyperlink r:id="rId134" ref="P51"/>
+    <hyperlink r:id="rId135" ref="N52"/>
+    <hyperlink r:id="rId136" ref="O52"/>
+    <hyperlink r:id="rId137" ref="P52"/>
+    <hyperlink r:id="rId138" ref="N53"/>
+    <hyperlink r:id="rId139" ref="O53"/>
+    <hyperlink r:id="rId140" ref="P53"/>
+    <hyperlink r:id="rId141" ref="N54"/>
+    <hyperlink r:id="rId142" ref="O54"/>
+    <hyperlink r:id="rId143" ref="P54"/>
+    <hyperlink r:id="rId144" ref="N55"/>
+    <hyperlink r:id="rId145" ref="P55"/>
+    <hyperlink r:id="rId146" ref="N56"/>
+    <hyperlink r:id="rId147" ref="O56"/>
+    <hyperlink r:id="rId148" ref="P56"/>
+    <hyperlink r:id="rId149" ref="N57"/>
+    <hyperlink r:id="rId150" ref="O57"/>
+    <hyperlink r:id="rId151" ref="P57"/>
+    <hyperlink r:id="rId152" ref="N58"/>
+    <hyperlink r:id="rId153" ref="O58"/>
+    <hyperlink r:id="rId154" ref="P58"/>
+    <hyperlink r:id="rId155" ref="N59"/>
+    <hyperlink r:id="rId156" ref="O59"/>
+    <hyperlink r:id="rId157" ref="P59"/>
+    <hyperlink r:id="rId158" ref="N60"/>
+    <hyperlink r:id="rId159" ref="O60"/>
+    <hyperlink r:id="rId160" ref="P60"/>
+    <hyperlink r:id="rId161" ref="N61"/>
+    <hyperlink r:id="rId162" ref="O61"/>
+    <hyperlink r:id="rId163" ref="P61"/>
+    <hyperlink r:id="rId164" ref="N62"/>
+    <hyperlink r:id="rId165" ref="P62"/>
+    <hyperlink r:id="rId166" ref="N63"/>
+    <hyperlink r:id="rId167" ref="O63"/>
+    <hyperlink r:id="rId168" ref="P63"/>
+    <hyperlink r:id="rId169" ref="N64"/>
+    <hyperlink r:id="rId170" ref="O64"/>
+    <hyperlink r:id="rId171" ref="P64"/>
+    <hyperlink r:id="rId172" ref="N65"/>
+    <hyperlink r:id="rId173" ref="O65"/>
+    <hyperlink r:id="rId174" ref="P65"/>
+    <hyperlink r:id="rId175" ref="N66"/>
+    <hyperlink r:id="rId176" ref="O66"/>
+    <hyperlink r:id="rId177" ref="P66"/>
+    <hyperlink r:id="rId178" ref="N67"/>
+    <hyperlink r:id="rId179" ref="O67"/>
+    <hyperlink r:id="rId180" ref="P67"/>
+    <hyperlink r:id="rId181" ref="N68"/>
+    <hyperlink r:id="rId182" ref="O68"/>
+    <hyperlink r:id="rId183" ref="P68"/>
+    <hyperlink r:id="rId184" ref="N69"/>
+    <hyperlink r:id="rId185" ref="O69"/>
+    <hyperlink r:id="rId186" ref="P69"/>
+    <hyperlink r:id="rId187" ref="N70"/>
+    <hyperlink r:id="rId188" ref="O70"/>
+    <hyperlink r:id="rId189" ref="P70"/>
+    <hyperlink r:id="rId190" ref="N71"/>
+    <hyperlink r:id="rId191" ref="O71"/>
+    <hyperlink r:id="rId192" ref="P71"/>
+    <hyperlink r:id="rId193" ref="N72"/>
+    <hyperlink r:id="rId194" ref="O72"/>
+    <hyperlink r:id="rId195" ref="P72"/>
+    <hyperlink r:id="rId196" ref="N73"/>
+    <hyperlink r:id="rId197" ref="O73"/>
+    <hyperlink r:id="rId198" ref="P73"/>
+    <hyperlink r:id="rId199" ref="N74"/>
+    <hyperlink r:id="rId200" ref="O74"/>
+    <hyperlink r:id="rId201" ref="P74"/>
+    <hyperlink r:id="rId202" ref="N75"/>
+    <hyperlink r:id="rId203" ref="O75"/>
+    <hyperlink r:id="rId204" ref="P75"/>
+    <hyperlink r:id="rId205" ref="N76"/>
+    <hyperlink r:id="rId206" ref="O76"/>
+    <hyperlink r:id="rId207" ref="P76"/>
+    <hyperlink r:id="rId208" ref="N77"/>
+    <hyperlink r:id="rId209" ref="O77"/>
+    <hyperlink r:id="rId210" ref="P77"/>
+    <hyperlink r:id="rId211" ref="N78"/>
+    <hyperlink r:id="rId212" ref="P78"/>
+    <hyperlink r:id="rId213" ref="N79"/>
+    <hyperlink r:id="rId214" ref="O79"/>
+    <hyperlink r:id="rId215" ref="P79"/>
+    <hyperlink r:id="rId216" ref="N80"/>
+    <hyperlink r:id="rId217" ref="O80"/>
+    <hyperlink r:id="rId218" ref="P80"/>
+    <hyperlink r:id="rId219" ref="N81"/>
+    <hyperlink r:id="rId220" ref="O81"/>
+    <hyperlink r:id="rId221" ref="P81"/>
+    <hyperlink r:id="rId222" ref="N82"/>
+    <hyperlink r:id="rId223" ref="O82"/>
+    <hyperlink r:id="rId224" ref="P82"/>
+    <hyperlink r:id="rId225" ref="N83"/>
+    <hyperlink r:id="rId226" ref="O83"/>
+    <hyperlink r:id="rId227" ref="P83"/>
+    <hyperlink r:id="rId228" ref="N84"/>
+    <hyperlink r:id="rId229" ref="O84"/>
+    <hyperlink r:id="rId230" ref="P84"/>
+    <hyperlink r:id="rId231" ref="N85"/>
+    <hyperlink r:id="rId232" ref="P85"/>
+    <hyperlink r:id="rId233" ref="N86"/>
+    <hyperlink r:id="rId234" ref="O86"/>
+    <hyperlink r:id="rId235" ref="P86"/>
+    <hyperlink r:id="rId236" ref="N87"/>
+    <hyperlink r:id="rId237" ref="O87"/>
+    <hyperlink r:id="rId238" ref="P87"/>
+    <hyperlink r:id="rId239" ref="N88"/>
+    <hyperlink r:id="rId240" ref="O88"/>
     <hyperlink r:id="rId241" ref="P88"/>
     <hyperlink r:id="rId242" ref="P89"/>
   </hyperlinks>
